--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.66</v>
+        <v>2.37</v>
       </c>
       <c r="F14" t="n">
-        <v>12.05</v>
+        <v>11.29</v>
       </c>
       <c r="G14" t="n">
-        <v>214.7</v>
+        <v>229.7</v>
       </c>
       <c r="H14" t="n">
-        <v>96.8</v>
+        <v>94.8</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>18.13</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
-        <v>46.87</v>
+        <v>-44.73</v>
       </c>
       <c r="L14" t="n">
-        <v>50.25</v>
+        <v>44.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:19:15</t>
+          <t>06:18:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="F15" t="n">
-        <v>11.19</v>
+        <v>10.59</v>
       </c>
       <c r="G15" t="n">
-        <v>221.6</v>
+        <v>210.7</v>
       </c>
       <c r="H15" t="n">
-        <v>98.8</v>
+        <v>92.5</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>40.04</v>
+        <v>-3.41</v>
       </c>
       <c r="K15" t="n">
-        <v>40.51</v>
+        <v>-163.37</v>
       </c>
       <c r="L15" t="n">
-        <v>56.96</v>
+        <v>163.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:21:41</t>
+          <t>06:20:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="F16" t="n">
-        <v>11.56</v>
+        <v>11.35</v>
       </c>
       <c r="G16" t="n">
-        <v>233</v>
+        <v>218.6</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.66</v>
+        <v>-68.34</v>
       </c>
       <c r="K16" t="n">
-        <v>-24.56</v>
+        <v>-59.63</v>
       </c>
       <c r="L16" t="n">
-        <v>28.1</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:27:28</t>
+          <t>06:24:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.97</v>
+        <v>2.36</v>
       </c>
       <c r="F17" t="n">
-        <v>11.15</v>
+        <v>11.57</v>
       </c>
       <c r="G17" t="n">
-        <v>219.4</v>
+        <v>235.6</v>
       </c>
       <c r="H17" t="n">
-        <v>99.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>51.02</v>
+        <v>57.99</v>
       </c>
       <c r="K17" t="n">
-        <v>-132.14</v>
+        <v>255.85</v>
       </c>
       <c r="L17" t="n">
-        <v>141.64</v>
+        <v>262.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:29:10</t>
+          <t>06:27:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="F18" t="n">
-        <v>11.89</v>
+        <v>10.73</v>
       </c>
       <c r="G18" t="n">
-        <v>222.5</v>
+        <v>213.3</v>
       </c>
       <c r="H18" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-160.78</v>
+        <v>220.48</v>
       </c>
       <c r="K18" t="n">
-        <v>-58.76</v>
+        <v>-141.57</v>
       </c>
       <c r="L18" t="n">
-        <v>171.19</v>
+        <v>262.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:31:24</t>
+          <t>06:28:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.04</v>
+        <v>3.38</v>
       </c>
       <c r="F19" t="n">
-        <v>11.47</v>
+        <v>10.94</v>
       </c>
       <c r="G19" t="n">
-        <v>204.9</v>
+        <v>217.1</v>
       </c>
       <c r="H19" t="n">
-        <v>91.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>7.66</v>
+        <v>179.12</v>
       </c>
       <c r="K19" t="n">
-        <v>109.87</v>
+        <v>-20.27</v>
       </c>
       <c r="L19" t="n">
-        <v>110.14</v>
+        <v>180.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:36:01</t>
+          <t>06:33:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="F20" t="n">
-        <v>12.04</v>
+        <v>10.97</v>
       </c>
       <c r="G20" t="n">
-        <v>223.8</v>
+        <v>234.1</v>
       </c>
       <c r="H20" t="n">
-        <v>96.8</v>
+        <v>98.3</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>95.27</v>
+        <v>-36.89</v>
       </c>
       <c r="K20" t="n">
-        <v>141.96</v>
+        <v>-245.11</v>
       </c>
       <c r="L20" t="n">
-        <v>170.96</v>
+        <v>247.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:37:26</t>
+          <t>06:35:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.23</v>
+        <v>3.92</v>
       </c>
       <c r="F21" t="n">
-        <v>11.59</v>
+        <v>11.38</v>
       </c>
       <c r="G21" t="n">
-        <v>218.8</v>
+        <v>216.5</v>
       </c>
       <c r="H21" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-345.99</v>
+        <v>-328.46</v>
       </c>
       <c r="K21" t="n">
-        <v>-272.36</v>
+        <v>433.79</v>
       </c>
       <c r="L21" t="n">
-        <v>440.33</v>
+        <v>544.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:39:28</t>
+          <t>06:37:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="F22" t="n">
-        <v>11.67</v>
+        <v>10.9</v>
       </c>
       <c r="G22" t="n">
-        <v>211</v>
+        <v>221.8</v>
       </c>
       <c r="H22" t="n">
-        <v>93.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-136.52</v>
+        <v>-283.37</v>
       </c>
       <c r="K22" t="n">
-        <v>89.18000000000001</v>
+        <v>280.21</v>
       </c>
       <c r="L22" t="n">
-        <v>163.07</v>
+        <v>398.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:44:22</t>
+          <t>06:42:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.18</v>
+        <v>2.51</v>
       </c>
       <c r="F23" t="n">
-        <v>10.85</v>
+        <v>11.89</v>
       </c>
       <c r="G23" t="n">
-        <v>219.4</v>
+        <v>216.6</v>
       </c>
       <c r="H23" t="n">
-        <v>98.8</v>
+        <v>94.7</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-210.06</v>
+        <v>-136.79</v>
       </c>
       <c r="K23" t="n">
-        <v>-98.05</v>
+        <v>66.22</v>
       </c>
       <c r="L23" t="n">
-        <v>231.81</v>
+        <v>151.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:45:46</t>
+          <t>06:44:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.17</v>
+        <v>2.96</v>
       </c>
       <c r="F24" t="n">
-        <v>12.01</v>
+        <v>11.83</v>
       </c>
       <c r="G24" t="n">
-        <v>214.9</v>
+        <v>223.6</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>140.2</v>
+        <v>26.97</v>
       </c>
       <c r="K24" t="n">
-        <v>259.17</v>
+        <v>-173.82</v>
       </c>
       <c r="L24" t="n">
-        <v>294.66</v>
+        <v>175.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:47:14</t>
+          <t>06:46:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.58</v>
+        <v>4.34</v>
       </c>
       <c r="F25" t="n">
-        <v>11.92</v>
+        <v>10.86</v>
       </c>
       <c r="G25" t="n">
-        <v>215.7</v>
+        <v>225</v>
       </c>
       <c r="H25" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>57.9</v>
+        <v>-568.66</v>
       </c>
       <c r="K25" t="n">
-        <v>67.04000000000001</v>
+        <v>219.25</v>
       </c>
       <c r="L25" t="n">
-        <v>88.58</v>
+        <v>609.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:51:47</t>
+          <t>06:51:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="F26" t="n">
-        <v>11.22</v>
+        <v>11.81</v>
       </c>
       <c r="G26" t="n">
-        <v>211.5</v>
+        <v>217.8</v>
       </c>
       <c r="H26" t="n">
-        <v>98.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-393.07</v>
+        <v>291.53</v>
       </c>
       <c r="K26" t="n">
-        <v>240.04</v>
+        <v>-649.36</v>
       </c>
       <c r="L26" t="n">
-        <v>460.57</v>
+        <v>711.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:52:52</t>
+          <t>06:52:26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.68</v>
+        <v>3.08</v>
       </c>
       <c r="F27" t="n">
-        <v>12.05</v>
+        <v>12.1</v>
       </c>
       <c r="G27" t="n">
-        <v>217.9</v>
+        <v>210</v>
       </c>
       <c r="H27" t="n">
-        <v>97.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>58.39</v>
+        <v>-15.4</v>
       </c>
       <c r="K27" t="n">
-        <v>263.36</v>
+        <v>-156.74</v>
       </c>
       <c r="L27" t="n">
-        <v>269.76</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:55:21</t>
+          <t>06:53:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.34</v>
+        <v>3.1</v>
       </c>
       <c r="F28" t="n">
-        <v>11.58</v>
+        <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>227</v>
+        <v>220.6</v>
       </c>
       <c r="H28" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-43.63</v>
+        <v>-231.98</v>
       </c>
       <c r="K28" t="n">
-        <v>-191.26</v>
+        <v>-31.54</v>
       </c>
       <c r="L28" t="n">
-        <v>196.18</v>
+        <v>234.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:06:18</t>
+          <t>07:02:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.48</v>
+        <v>2.72</v>
       </c>
       <c r="F29" t="n">
-        <v>11.26</v>
+        <v>11.34</v>
       </c>
       <c r="G29" t="n">
-        <v>205.4</v>
+        <v>224.4</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>0.91</v>
+        <v>135.51</v>
       </c>
       <c r="K29" t="n">
-        <v>-114.66</v>
+        <v>-116.01</v>
       </c>
       <c r="L29" t="n">
-        <v>114.66</v>
+        <v>178.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:08:35</t>
+          <t>07:04:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="F30" t="n">
-        <v>11.65</v>
+        <v>11.24</v>
       </c>
       <c r="G30" t="n">
-        <v>217.9</v>
+        <v>237.7</v>
       </c>
       <c r="H30" t="n">
-        <v>92.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-103.33</v>
+        <v>111.52</v>
       </c>
       <c r="K30" t="n">
-        <v>-112.51</v>
+        <v>129.84</v>
       </c>
       <c r="L30" t="n">
-        <v>152.76</v>
+        <v>171.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:09:41</t>
+          <t>07:06:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="F31" t="n">
-        <v>11.52</v>
+        <v>12.13</v>
       </c>
       <c r="G31" t="n">
-        <v>224</v>
+        <v>227.7</v>
       </c>
       <c r="H31" t="n">
-        <v>97</v>
+        <v>98.7</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>128.13</v>
+        <v>26.65</v>
       </c>
       <c r="K31" t="n">
-        <v>103.1</v>
+        <v>143.66</v>
       </c>
       <c r="L31" t="n">
-        <v>164.47</v>
+        <v>146.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:15:33</t>
+          <t>07:11:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.82</v>
+        <v>2.93</v>
       </c>
       <c r="F32" t="n">
-        <v>11.93</v>
+        <v>10.86</v>
       </c>
       <c r="G32" t="n">
-        <v>217</v>
+        <v>205.2</v>
       </c>
       <c r="H32" t="n">
-        <v>95.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-109.52</v>
+        <v>68.94</v>
       </c>
       <c r="K32" t="n">
-        <v>-191.68</v>
+        <v>-170.5</v>
       </c>
       <c r="L32" t="n">
-        <v>220.76</v>
+        <v>183.91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:17:34</t>
+          <t>07:13:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.29</v>
+        <v>3.8</v>
       </c>
       <c r="F33" t="n">
-        <v>11.48</v>
+        <v>11.86</v>
       </c>
       <c r="G33" t="n">
-        <v>213.2</v>
+        <v>221.2</v>
       </c>
       <c r="H33" t="n">
-        <v>87.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>68.87</v>
+        <v>127.44</v>
       </c>
       <c r="K33" t="n">
-        <v>-98.19</v>
+        <v>102.58</v>
       </c>
       <c r="L33" t="n">
-        <v>119.93</v>
+        <v>163.59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:18:58</t>
+          <t>07:14:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="F34" t="n">
-        <v>11.43</v>
+        <v>11.36</v>
       </c>
       <c r="G34" t="n">
-        <v>229.8</v>
+        <v>219.5</v>
       </c>
       <c r="H34" t="n">
-        <v>92.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>151.88</v>
+        <v>-88.76000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>157.43</v>
+        <v>-32.39</v>
       </c>
       <c r="L34" t="n">
-        <v>218.75</v>
+        <v>94.48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:23:24</t>
+          <t>07:20:06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.32</v>
+        <v>3.85</v>
       </c>
       <c r="F35" t="n">
-        <v>11.49</v>
+        <v>11.21</v>
       </c>
       <c r="G35" t="n">
-        <v>213.7</v>
+        <v>225.7</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>416.17</v>
+        <v>-354.58</v>
       </c>
       <c r="K35" t="n">
-        <v>-11.29</v>
+        <v>312.02</v>
       </c>
       <c r="L35" t="n">
-        <v>416.32</v>
+        <v>472.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:25:35</t>
+          <t>07:21:39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="F36" t="n">
-        <v>12.76</v>
+        <v>11.25</v>
       </c>
       <c r="G36" t="n">
-        <v>216.2</v>
+        <v>210.3</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-196.27</v>
+        <v>-413.64</v>
       </c>
       <c r="K36" t="n">
-        <v>456.65</v>
+        <v>-395.68</v>
       </c>
       <c r="L36" t="n">
-        <v>497.04</v>
+        <v>572.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:27:25</t>
+          <t>07:23:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="F37" t="n">
-        <v>11.83</v>
+        <v>12.22</v>
       </c>
       <c r="G37" t="n">
-        <v>219.9</v>
+        <v>226.3</v>
       </c>
       <c r="H37" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>113.32</v>
+        <v>49.66</v>
       </c>
       <c r="K37" t="n">
-        <v>-126.03</v>
+        <v>-36.74</v>
       </c>
       <c r="L37" t="n">
-        <v>169.49</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:31:40</t>
+          <t>07:29:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="F38" t="n">
-        <v>11.75</v>
+        <v>11.71</v>
       </c>
       <c r="G38" t="n">
-        <v>212.2</v>
+        <v>227.6</v>
       </c>
       <c r="H38" t="n">
-        <v>95.3</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>405.84</v>
+        <v>-24.11</v>
       </c>
       <c r="K38" t="n">
-        <v>-380.89</v>
+        <v>-254.49</v>
       </c>
       <c r="L38" t="n">
-        <v>556.59</v>
+        <v>255.63</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:33:48</t>
+          <t>07:30:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.66</v>
+        <v>3.13</v>
       </c>
       <c r="F39" t="n">
-        <v>11.07</v>
+        <v>11.64</v>
       </c>
       <c r="G39" t="n">
-        <v>212.2</v>
+        <v>211.2</v>
       </c>
       <c r="H39" t="n">
-        <v>97.2</v>
+        <v>95.8</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>192.32</v>
+        <v>-559.12</v>
       </c>
       <c r="K39" t="n">
-        <v>273.18</v>
+        <v>-230.2</v>
       </c>
       <c r="L39" t="n">
-        <v>334.08</v>
+        <v>604.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:36:04</t>
+          <t>07:32:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.27</v>
+        <v>4.35</v>
       </c>
       <c r="F40" t="n">
-        <v>11.56</v>
+        <v>11.49</v>
       </c>
       <c r="G40" t="n">
-        <v>224.9</v>
+        <v>222.6</v>
       </c>
       <c r="H40" t="n">
-        <v>94.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-143.81</v>
+        <v>-243.72</v>
       </c>
       <c r="K40" t="n">
-        <v>8.470000000000001</v>
+        <v>-238.45</v>
       </c>
       <c r="L40" t="n">
-        <v>144.06</v>
+        <v>340.96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:40:31</t>
+          <t>07:37:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>10.86</v>
       </c>
       <c r="G41" t="n">
-        <v>213.9</v>
+        <v>217.9</v>
       </c>
       <c r="H41" t="n">
-        <v>96.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-426.66</v>
+        <v>767.25</v>
       </c>
       <c r="K41" t="n">
-        <v>309.43</v>
+        <v>353.43</v>
       </c>
       <c r="L41" t="n">
-        <v>527.0599999999999</v>
+        <v>844.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:42:48</t>
+          <t>07:39:55</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.43</v>
+        <v>3.74</v>
       </c>
       <c r="F42" t="n">
-        <v>12.09</v>
+        <v>11.13</v>
       </c>
       <c r="G42" t="n">
-        <v>217.6</v>
+        <v>221</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>30.53</v>
+        <v>252.75</v>
       </c>
       <c r="K42" t="n">
-        <v>55.4</v>
+        <v>-298.38</v>
       </c>
       <c r="L42" t="n">
-        <v>63.26</v>
+        <v>391.05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:44:32</t>
+          <t>07:41:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.71</v>
+        <v>3.52</v>
       </c>
       <c r="F43" t="n">
-        <v>11.7</v>
+        <v>11.41</v>
       </c>
       <c r="G43" t="n">
-        <v>222.4</v>
+        <v>223.7</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-124.4</v>
+        <v>22.97</v>
       </c>
       <c r="K43" t="n">
-        <v>-227.77</v>
+        <v>-818.1900000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>259.53</v>
+        <v>818.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:55:09</t>
+          <t>07:50:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.15</v>
+        <v>3.08</v>
       </c>
       <c r="F44" t="n">
-        <v>11.08</v>
+        <v>11.69</v>
       </c>
       <c r="G44" t="n">
-        <v>215.8</v>
+        <v>229</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>59.18</v>
+        <v>-100.44</v>
       </c>
       <c r="K44" t="n">
-        <v>192.31</v>
+        <v>-106.69</v>
       </c>
       <c r="L44" t="n">
-        <v>201.21</v>
+        <v>146.53</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:56:50</t>
+          <t>07:53:20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.91</v>
+        <v>4.1</v>
       </c>
       <c r="F45" t="n">
-        <v>11.43</v>
+        <v>11.48</v>
       </c>
       <c r="G45" t="n">
-        <v>240.9</v>
+        <v>210.9</v>
       </c>
       <c r="H45" t="n">
-        <v>98.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-17.06</v>
+        <v>37.8</v>
       </c>
       <c r="K45" t="n">
-        <v>-48.9</v>
+        <v>30.2</v>
       </c>
       <c r="L45" t="n">
-        <v>51.79</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:57:33</t>
+          <t>07:54:14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.9</v>
+        <v>3.59</v>
       </c>
       <c r="F46" t="n">
-        <v>12.35</v>
+        <v>11.24</v>
       </c>
       <c r="G46" t="n">
-        <v>218.8</v>
+        <v>219.5</v>
       </c>
       <c r="H46" t="n">
-        <v>99.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>52.38</v>
+        <v>15.76</v>
       </c>
       <c r="K46" t="n">
-        <v>-80.59</v>
+        <v>-130.87</v>
       </c>
       <c r="L46" t="n">
-        <v>96.12</v>
+        <v>131.82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:02:17</t>
+          <t>07:57:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="F47" t="n">
-        <v>11.69</v>
+        <v>11.27</v>
       </c>
       <c r="G47" t="n">
-        <v>220.6</v>
+        <v>202.9</v>
       </c>
       <c r="H47" t="n">
-        <v>89.5</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-7.04</v>
+        <v>-140.48</v>
       </c>
       <c r="K47" t="n">
-        <v>-69.64</v>
+        <v>-165.73</v>
       </c>
       <c r="L47" t="n">
-        <v>69.98999999999999</v>
+        <v>217.26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:04:31</t>
+          <t>08:00:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.99</v>
+        <v>3.34</v>
       </c>
       <c r="F48" t="n">
-        <v>11.13</v>
+        <v>11.61</v>
       </c>
       <c r="G48" t="n">
-        <v>209.5</v>
+        <v>235</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-96.67</v>
+        <v>-241.34</v>
       </c>
       <c r="K48" t="n">
-        <v>34.66</v>
+        <v>62.58</v>
       </c>
       <c r="L48" t="n">
-        <v>102.7</v>
+        <v>249.32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:06:05</t>
+          <t>08:02:15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="F49" t="n">
-        <v>11.22</v>
+        <v>11.95</v>
       </c>
       <c r="G49" t="n">
-        <v>218.3</v>
+        <v>222.3</v>
       </c>
       <c r="H49" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-57.1</v>
+        <v>-191.39</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.66</v>
+        <v>156.75</v>
       </c>
       <c r="L49" t="n">
-        <v>57.16</v>
+        <v>247.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:11:33</t>
+          <t>08:07:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="F50" t="n">
-        <v>11.61</v>
+        <v>11.69</v>
       </c>
       <c r="G50" t="n">
-        <v>212.3</v>
+        <v>221.6</v>
       </c>
       <c r="H50" t="n">
-        <v>99.5</v>
+        <v>91</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-33.09</v>
+        <v>-32.48</v>
       </c>
       <c r="K50" t="n">
-        <v>-15.24</v>
+        <v>-502.81</v>
       </c>
       <c r="L50" t="n">
-        <v>36.43</v>
+        <v>503.86</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:14:04</t>
+          <t>08:09:18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="F51" t="n">
-        <v>11.26</v>
+        <v>11.85</v>
       </c>
       <c r="G51" t="n">
-        <v>213.7</v>
+        <v>225</v>
       </c>
       <c r="H51" t="n">
-        <v>92.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-629.37</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>3.32</v>
+        <v>-146.78</v>
       </c>
       <c r="L51" t="n">
-        <v>629.38</v>
+        <v>160.29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:15:17</t>
+          <t>08:10:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.02</v>
+        <v>3.24</v>
       </c>
       <c r="F52" t="n">
-        <v>11.46</v>
+        <v>11.92</v>
       </c>
       <c r="G52" t="n">
-        <v>232.7</v>
+        <v>228.9</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>168.62</v>
+        <v>572.89</v>
       </c>
       <c r="K52" t="n">
-        <v>210.28</v>
+        <v>308.38</v>
       </c>
       <c r="L52" t="n">
-        <v>269.54</v>
+        <v>650.61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:19:01</t>
+          <t>08:15:37</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.13</v>
+        <v>3.2</v>
       </c>
       <c r="F53" t="n">
-        <v>11.85</v>
+        <v>12.61</v>
       </c>
       <c r="G53" t="n">
-        <v>224.3</v>
+        <v>233.7</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>1.78</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-128.11</v>
+        <v>195.24</v>
       </c>
       <c r="L53" t="n">
-        <v>128.13</v>
+        <v>213.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:20:30</t>
+          <t>08:16:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.32</v>
+        <v>4.17</v>
       </c>
       <c r="F54" t="n">
-        <v>11.65</v>
+        <v>11.03</v>
       </c>
       <c r="G54" t="n">
-        <v>220.3</v>
+        <v>217.8</v>
       </c>
       <c r="H54" t="n">
-        <v>89.7</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-276.85</v>
+        <v>-357.44</v>
       </c>
       <c r="K54" t="n">
-        <v>164.22</v>
+        <v>117.67</v>
       </c>
       <c r="L54" t="n">
-        <v>321.89</v>
+        <v>376.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:21:15</t>
+          <t>08:19:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="F55" t="n">
-        <v>11.49</v>
+        <v>12.07</v>
       </c>
       <c r="G55" t="n">
-        <v>220.6</v>
+        <v>225.7</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>125.35</v>
+        <v>88.36</v>
       </c>
       <c r="K55" t="n">
-        <v>345.15</v>
+        <v>-637.48</v>
       </c>
       <c r="L55" t="n">
-        <v>367.2</v>
+        <v>643.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:26:29</t>
+          <t>08:24:22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="F56" t="n">
-        <v>11.69</v>
+        <v>11.4</v>
       </c>
       <c r="G56" t="n">
-        <v>227.3</v>
+        <v>217.2</v>
       </c>
       <c r="H56" t="n">
-        <v>93.5</v>
+        <v>92</v>
       </c>
       <c r="I56" t="n">
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-407.33</v>
+        <v>347.37</v>
       </c>
       <c r="K56" t="n">
-        <v>-463.28</v>
+        <v>-239.92</v>
       </c>
       <c r="L56" t="n">
-        <v>616.88</v>
+        <v>422.17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:27:20</t>
+          <t>08:25:44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="F57" t="n">
-        <v>11.5</v>
+        <v>12.64</v>
       </c>
       <c r="G57" t="n">
-        <v>212.2</v>
+        <v>217.8</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>406.35</v>
+        <v>409.22</v>
       </c>
       <c r="K57" t="n">
-        <v>368.38</v>
+        <v>-493.79</v>
       </c>
       <c r="L57" t="n">
-        <v>548.47</v>
+        <v>641.3200000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:29:17</t>
+          <t>08:27:09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="F58" t="n">
-        <v>11.65</v>
+        <v>12.25</v>
       </c>
       <c r="G58" t="n">
-        <v>216.8</v>
+        <v>219.3</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-72.68000000000001</v>
+        <v>183.85</v>
       </c>
       <c r="K58" t="n">
-        <v>-437.29</v>
+        <v>124.18</v>
       </c>
       <c r="L58" t="n">
-        <v>443.29</v>
+        <v>221.86</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:40:45</t>
+          <t>08:35:13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.06</v>
+        <v>3.48</v>
       </c>
       <c r="F59" t="n">
-        <v>11.57</v>
+        <v>11.59</v>
       </c>
       <c r="G59" t="n">
-        <v>222.9</v>
+        <v>229.1</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.52</v>
+        <v>49.87</v>
       </c>
       <c r="K59" t="n">
-        <v>-87.92</v>
+        <v>-141.85</v>
       </c>
       <c r="L59" t="n">
-        <v>97.67</v>
+        <v>150.36</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:43:15</t>
+          <t>08:36:43</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="F60" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="G60" t="n">
-        <v>218.3</v>
+        <v>230.6</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-175.32</v>
+        <v>64.5</v>
       </c>
       <c r="K60" t="n">
-        <v>-47.82</v>
+        <v>100.22</v>
       </c>
       <c r="L60" t="n">
-        <v>181.73</v>
+        <v>119.18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:44:49</t>
+          <t>08:38:14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="F61" t="n">
-        <v>11.73</v>
+        <v>11.75</v>
       </c>
       <c r="G61" t="n">
-        <v>212.6</v>
+        <v>226.7</v>
       </c>
       <c r="H61" t="n">
-        <v>96.7</v>
+        <v>99.3</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>69.67</v>
+        <v>-20.99</v>
       </c>
       <c r="K61" t="n">
-        <v>145.07</v>
+        <v>-178.02</v>
       </c>
       <c r="L61" t="n">
-        <v>160.93</v>
+        <v>179.26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:49:50</t>
+          <t>08:43:19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>12.17</v>
+        <v>11.66</v>
       </c>
       <c r="G62" t="n">
-        <v>225.6</v>
+        <v>210.6</v>
       </c>
       <c r="H62" t="n">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>51.43</v>
+        <v>617.4299999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>164.08</v>
+        <v>255.98</v>
       </c>
       <c r="L62" t="n">
-        <v>171.95</v>
+        <v>668.39</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:51:27</t>
+          <t>08:45:21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.63</v>
+        <v>3.94</v>
       </c>
       <c r="F63" t="n">
-        <v>11.11</v>
+        <v>11.63</v>
       </c>
       <c r="G63" t="n">
-        <v>213.2</v>
+        <v>218.6</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>111.94</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-124.88</v>
+        <v>54.94</v>
       </c>
       <c r="L63" t="n">
-        <v>167.71</v>
+        <v>55.53</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:54:01</t>
+          <t>08:47:21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="F64" t="n">
-        <v>11.35</v>
+        <v>12.21</v>
       </c>
       <c r="G64" t="n">
-        <v>223.7</v>
+        <v>208</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-170.41</v>
+        <v>-336.88</v>
       </c>
       <c r="K64" t="n">
-        <v>13.36</v>
+        <v>-39.52</v>
       </c>
       <c r="L64" t="n">
-        <v>170.93</v>
+        <v>339.19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:57:33</t>
+          <t>08:52:49</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.62</v>
+        <v>3.88</v>
       </c>
       <c r="F65" t="n">
-        <v>11.37</v>
+        <v>11.32</v>
       </c>
       <c r="G65" t="n">
-        <v>212.1</v>
+        <v>218</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-75.53</v>
+        <v>-32.77</v>
       </c>
       <c r="K65" t="n">
-        <v>-93.04000000000001</v>
+        <v>-365.29</v>
       </c>
       <c r="L65" t="n">
-        <v>119.84</v>
+        <v>366.76</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:59:08</t>
+          <t>08:53:34</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="F66" t="n">
-        <v>11.54</v>
+        <v>11.33</v>
       </c>
       <c r="G66" t="n">
-        <v>206.6</v>
+        <v>214.6</v>
       </c>
       <c r="H66" t="n">
-        <v>97.5</v>
+        <v>94.3</v>
       </c>
       <c r="I66" t="n">
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-66.56</v>
+        <v>62.55</v>
       </c>
       <c r="K66" t="n">
-        <v>118</v>
+        <v>118.72</v>
       </c>
       <c r="L66" t="n">
-        <v>135.48</v>
+        <v>134.19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:00:13</t>
+          <t>08:55:54</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="F67" t="n">
-        <v>11.27</v>
+        <v>12.15</v>
       </c>
       <c r="G67" t="n">
-        <v>224.6</v>
+        <v>207.4</v>
       </c>
       <c r="H67" t="n">
-        <v>98</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-18.38</v>
+        <v>47.92</v>
       </c>
       <c r="K67" t="n">
-        <v>85.15000000000001</v>
+        <v>107.24</v>
       </c>
       <c r="L67" t="n">
-        <v>87.12</v>
+        <v>117.46</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:05:36</t>
+          <t>09:00:57</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.15</v>
+        <v>3.63</v>
       </c>
       <c r="F68" t="n">
-        <v>11.23</v>
+        <v>11.29</v>
       </c>
       <c r="G68" t="n">
-        <v>211.7</v>
+        <v>228.7</v>
       </c>
       <c r="H68" t="n">
-        <v>93.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-29.78</v>
+        <v>-546.74</v>
       </c>
       <c r="K68" t="n">
-        <v>297.69</v>
+        <v>-99.55</v>
       </c>
       <c r="L68" t="n">
-        <v>299.18</v>
+        <v>555.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:06:34</t>
+          <t>09:01:55</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.31</v>
+        <v>4.04</v>
       </c>
       <c r="F69" t="n">
-        <v>11.61</v>
+        <v>12.12</v>
       </c>
       <c r="G69" t="n">
-        <v>219.5</v>
+        <v>215.1</v>
       </c>
       <c r="H69" t="n">
-        <v>97.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I69" t="n">
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-264.31</v>
+        <v>-453.69</v>
       </c>
       <c r="K69" t="n">
-        <v>145.68</v>
+        <v>-98.97</v>
       </c>
       <c r="L69" t="n">
-        <v>301.8</v>
+        <v>464.36</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:08:23</t>
+          <t>09:03:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="F70" t="n">
-        <v>11.11</v>
+        <v>11.47</v>
       </c>
       <c r="G70" t="n">
-        <v>218.6</v>
+        <v>226.8</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.99</v>
+        <v>-664.78</v>
       </c>
       <c r="K70" t="n">
-        <v>-119.76</v>
+        <v>-217.02</v>
       </c>
       <c r="L70" t="n">
-        <v>120.26</v>
+        <v>699.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:12:54</t>
+          <t>09:07:59</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="F71" t="n">
-        <v>10.78</v>
+        <v>11.34</v>
       </c>
       <c r="G71" t="n">
-        <v>233.2</v>
+        <v>221.8</v>
       </c>
       <c r="H71" t="n">
-        <v>95.8</v>
+        <v>96</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-160.04</v>
+        <v>158.86</v>
       </c>
       <c r="K71" t="n">
-        <v>78.79000000000001</v>
+        <v>-371.22</v>
       </c>
       <c r="L71" t="n">
-        <v>178.38</v>
+        <v>403.78</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:14:31</t>
+          <t>09:09:09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.7</v>
+        <v>3.29</v>
       </c>
       <c r="F72" t="n">
-        <v>11.57</v>
+        <v>11.94</v>
       </c>
       <c r="G72" t="n">
-        <v>220.7</v>
+        <v>220.3</v>
       </c>
       <c r="H72" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>340.36</v>
+        <v>426.23</v>
       </c>
       <c r="K72" t="n">
-        <v>22.67</v>
+        <v>-292.62</v>
       </c>
       <c r="L72" t="n">
-        <v>341.11</v>
+        <v>517.01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:15:37</t>
+          <t>09:10:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="F73" t="n">
-        <v>11.68</v>
+        <v>11.62</v>
       </c>
       <c r="G73" t="n">
-        <v>217.9</v>
+        <v>226.2</v>
       </c>
       <c r="H73" t="n">
-        <v>94.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>592.23</v>
+        <v>-435.82</v>
       </c>
       <c r="K73" t="n">
-        <v>237.31</v>
+        <v>335.55</v>
       </c>
       <c r="L73" t="n">
-        <v>638</v>
+        <v>550.03</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:24:15</t>
+          <t>09:23:47</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="F74" t="n">
-        <v>11.56</v>
+        <v>11.46</v>
       </c>
       <c r="G74" t="n">
-        <v>231.3</v>
+        <v>225.8</v>
       </c>
       <c r="H74" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-146.4</v>
+        <v>153.76</v>
       </c>
       <c r="K74" t="n">
-        <v>-21.62</v>
+        <v>82.83</v>
       </c>
       <c r="L74" t="n">
-        <v>147.99</v>
+        <v>174.65</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:25:34</t>
+          <t>09:24:44</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.43</v>
+        <v>3.71</v>
       </c>
       <c r="F75" t="n">
-        <v>12.18</v>
+        <v>11.51</v>
       </c>
       <c r="G75" t="n">
-        <v>225</v>
+        <v>206.8</v>
       </c>
       <c r="H75" t="n">
         <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>24.65</v>
+        <v>-99.81999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-34.81</v>
+        <v>42.9</v>
       </c>
       <c r="L75" t="n">
-        <v>42.66</v>
+        <v>108.64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:27:08</t>
+          <t>09:26:50</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.54</v>
+        <v>3.23</v>
       </c>
       <c r="F76" t="n">
-        <v>11.6</v>
+        <v>11.08</v>
       </c>
       <c r="G76" t="n">
-        <v>229.6</v>
+        <v>212.7</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>62.15</v>
+        <v>122.85</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.91</v>
+        <v>62.05</v>
       </c>
       <c r="L76" t="n">
-        <v>63.48</v>
+        <v>137.63</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:31:13</t>
+          <t>09:32:55</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="F77" t="n">
-        <v>11.88</v>
+        <v>11.94</v>
       </c>
       <c r="G77" t="n">
-        <v>222.8</v>
+        <v>222.1</v>
       </c>
       <c r="H77" t="n">
-        <v>97.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-26.95</v>
+        <v>356.24</v>
       </c>
       <c r="K77" t="n">
-        <v>144.91</v>
+        <v>-33.43</v>
       </c>
       <c r="L77" t="n">
-        <v>147.39</v>
+        <v>357.81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:32:37</t>
+          <t>09:34:24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.58</v>
+        <v>3.07</v>
       </c>
       <c r="F78" t="n">
-        <v>11.15</v>
+        <v>10.68</v>
       </c>
       <c r="G78" t="n">
-        <v>217</v>
+        <v>214.8</v>
       </c>
       <c r="H78" t="n">
-        <v>97</v>
+        <v>98.7</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-17.51</v>
+        <v>-115.7</v>
       </c>
       <c r="K78" t="n">
-        <v>2.2</v>
+        <v>96.52</v>
       </c>
       <c r="L78" t="n">
-        <v>17.65</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:34:06</t>
+          <t>09:35:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.59</v>
+        <v>3.27</v>
       </c>
       <c r="F79" t="n">
-        <v>10.87</v>
+        <v>10.77</v>
       </c>
       <c r="G79" t="n">
-        <v>222.5</v>
+        <v>225.3</v>
       </c>
       <c r="H79" t="n">
-        <v>94.09999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-166.77</v>
+        <v>236.68</v>
       </c>
       <c r="K79" t="n">
-        <v>95.81</v>
+        <v>-47.01</v>
       </c>
       <c r="L79" t="n">
-        <v>192.34</v>
+        <v>241.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:38:35</t>
+          <t>09:41:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.06</v>
+        <v>3.65</v>
       </c>
       <c r="F80" t="n">
-        <v>11.23</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>218.7</v>
+        <v>218.3</v>
       </c>
       <c r="H80" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-54.77</v>
+        <v>-332.62</v>
       </c>
       <c r="K80" t="n">
-        <v>76.72</v>
+        <v>-39.03</v>
       </c>
       <c r="L80" t="n">
-        <v>94.26000000000001</v>
+        <v>334.91</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:40:22</t>
+          <t>09:41:45</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.59</v>
+        <v>3.37</v>
       </c>
       <c r="F81" t="n">
-        <v>11.88</v>
+        <v>10.74</v>
       </c>
       <c r="G81" t="n">
-        <v>212.7</v>
+        <v>228.2</v>
       </c>
       <c r="H81" t="n">
         <v>96.09999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-81.95999999999999</v>
+        <v>238.64</v>
       </c>
       <c r="K81" t="n">
-        <v>79.67</v>
+        <v>105.48</v>
       </c>
       <c r="L81" t="n">
-        <v>114.3</v>
+        <v>260.91</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:41:24</t>
+          <t>09:43:52</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.18</v>
+        <v>3.73</v>
       </c>
       <c r="F82" t="n">
-        <v>10.83</v>
+        <v>11.79</v>
       </c>
       <c r="G82" t="n">
-        <v>233.3</v>
+        <v>206.3</v>
       </c>
       <c r="H82" t="n">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>202.7</v>
+        <v>210.89</v>
       </c>
       <c r="K82" t="n">
-        <v>-364.36</v>
+        <v>-186.94</v>
       </c>
       <c r="L82" t="n">
-        <v>416.95</v>
+        <v>281.82</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:46:03</t>
+          <t>09:49:41</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.53</v>
+        <v>3.96</v>
       </c>
       <c r="F83" t="n">
-        <v>11.61</v>
+        <v>11.45</v>
       </c>
       <c r="G83" t="n">
-        <v>228.1</v>
+        <v>206.8</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>609.84</v>
+        <v>180.74</v>
       </c>
       <c r="K83" t="n">
-        <v>-300.72</v>
+        <v>153.17</v>
       </c>
       <c r="L83" t="n">
-        <v>679.96</v>
+        <v>236.91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:47:21</t>
+          <t>09:51:47</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,13 +3565,13 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.28</v>
+        <v>4.02</v>
       </c>
       <c r="F84" t="n">
-        <v>12.06</v>
+        <v>11.37</v>
       </c>
       <c r="G84" t="n">
-        <v>221.8</v>
+        <v>215.7</v>
       </c>
       <c r="H84" t="n">
         <v>100</v>
@@ -3580,19 +3580,19 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>348.32</v>
+        <v>-242.55</v>
       </c>
       <c r="K84" t="n">
-        <v>6.29</v>
+        <v>-71.59</v>
       </c>
       <c r="L84" t="n">
-        <v>348.38</v>
+        <v>252.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:49:06</t>
+          <t>09:53:42</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.93</v>
+        <v>3.61</v>
       </c>
       <c r="F85" t="n">
-        <v>12.03</v>
+        <v>11.67</v>
       </c>
       <c r="G85" t="n">
-        <v>216.3</v>
+        <v>211.5</v>
       </c>
       <c r="H85" t="n">
-        <v>98.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>579.77</v>
+        <v>40.55</v>
       </c>
       <c r="K85" t="n">
-        <v>-3.21</v>
+        <v>-245.72</v>
       </c>
       <c r="L85" t="n">
-        <v>579.78</v>
+        <v>249.04</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:53:47</t>
+          <t>09:58:17</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.87</v>
+        <v>4.1</v>
       </c>
       <c r="F86" t="n">
-        <v>11.06</v>
+        <v>12.08</v>
       </c>
       <c r="G86" t="n">
-        <v>234.4</v>
+        <v>224.5</v>
       </c>
       <c r="H86" t="n">
-        <v>98.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-96.64</v>
+        <v>-461.62</v>
       </c>
       <c r="K86" t="n">
-        <v>-23.32</v>
+        <v>270.04</v>
       </c>
       <c r="L86" t="n">
-        <v>99.41</v>
+        <v>534.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:56:25</t>
+          <t>09:59:52</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.05</v>
+        <v>3.24</v>
       </c>
       <c r="F87" t="n">
-        <v>11.69</v>
+        <v>11.39</v>
       </c>
       <c r="G87" t="n">
-        <v>219.9</v>
+        <v>214.8</v>
       </c>
       <c r="H87" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>183.48</v>
+        <v>409.5</v>
       </c>
       <c r="K87" t="n">
-        <v>546.4</v>
+        <v>-383.51</v>
       </c>
       <c r="L87" t="n">
-        <v>576.38</v>
+        <v>561.04</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:57:47</t>
+          <t>10:01:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="F88" t="n">
-        <v>10.88</v>
+        <v>12</v>
       </c>
       <c r="G88" t="n">
-        <v>217.1</v>
+        <v>226.4</v>
       </c>
       <c r="H88" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-269.37</v>
+        <v>-130.36</v>
       </c>
       <c r="K88" t="n">
-        <v>463.34</v>
+        <v>875.33</v>
       </c>
       <c r="L88" t="n">
-        <v>535.95</v>
+        <v>884.98</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>1.54</v>
       </c>
       <c r="K14" t="n">
-        <v>-44.73</v>
+        <v>-63.3</v>
       </c>
       <c r="L14" t="n">
-        <v>44.74</v>
+        <v>63.32</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.41</v>
+        <v>-3.82</v>
       </c>
       <c r="K15" t="n">
-        <v>-163.37</v>
+        <v>-183.05</v>
       </c>
       <c r="L15" t="n">
-        <v>163.41</v>
+        <v>183.08</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-68.34</v>
+        <v>-76.01000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-59.63</v>
+        <v>-66.33</v>
       </c>
       <c r="L16" t="n">
-        <v>90.7</v>
+        <v>100.88</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>57.99</v>
+        <v>49.31</v>
       </c>
       <c r="K17" t="n">
-        <v>255.85</v>
+        <v>217.56</v>
       </c>
       <c r="L17" t="n">
-        <v>262.34</v>
+        <v>223.07</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>220.48</v>
+        <v>225.37</v>
       </c>
       <c r="K18" t="n">
-        <v>-141.57</v>
+        <v>-144.71</v>
       </c>
       <c r="L18" t="n">
-        <v>262.02</v>
+        <v>267.83</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>179.12</v>
+        <v>194.68</v>
       </c>
       <c r="K19" t="n">
-        <v>-20.27</v>
+        <v>-22.03</v>
       </c>
       <c r="L19" t="n">
-        <v>180.27</v>
+        <v>195.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-36.89</v>
+        <v>-41.95</v>
       </c>
       <c r="K20" t="n">
-        <v>-245.11</v>
+        <v>-278.7</v>
       </c>
       <c r="L20" t="n">
-        <v>247.87</v>
+        <v>281.84</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-328.46</v>
+        <v>-358.14</v>
       </c>
       <c r="K21" t="n">
-        <v>433.79</v>
+        <v>472.97</v>
       </c>
       <c r="L21" t="n">
-        <v>544.11</v>
+        <v>593.27</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-283.37</v>
+        <v>-317.05</v>
       </c>
       <c r="K22" t="n">
-        <v>280.21</v>
+        <v>313.51</v>
       </c>
       <c r="L22" t="n">
-        <v>398.52</v>
+        <v>445.88</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-136.79</v>
+        <v>-219.3</v>
       </c>
       <c r="K23" t="n">
-        <v>66.22</v>
+        <v>106.16</v>
       </c>
       <c r="L23" t="n">
-        <v>151.98</v>
+        <v>243.64</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>26.97</v>
+        <v>41.61</v>
       </c>
       <c r="K24" t="n">
-        <v>-173.82</v>
+        <v>-268.17</v>
       </c>
       <c r="L24" t="n">
-        <v>175.9</v>
+        <v>271.38</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-568.66</v>
+        <v>-677.5599999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>219.25</v>
+        <v>261.24</v>
       </c>
       <c r="L25" t="n">
-        <v>609.46</v>
+        <v>726.1799999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>291.53</v>
+        <v>347.61</v>
       </c>
       <c r="K26" t="n">
-        <v>-649.36</v>
+        <v>-774.29</v>
       </c>
       <c r="L26" t="n">
-        <v>711.8</v>
+        <v>848.74</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-15.4</v>
+        <v>-34.6</v>
       </c>
       <c r="K27" t="n">
-        <v>-156.74</v>
+        <v>-352.28</v>
       </c>
       <c r="L27" t="n">
-        <v>157.5</v>
+        <v>353.97</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-231.98</v>
+        <v>-444.23</v>
       </c>
       <c r="K28" t="n">
-        <v>-31.54</v>
+        <v>-60.39</v>
       </c>
       <c r="L28" t="n">
-        <v>234.12</v>
+        <v>448.32</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>135.51</v>
+        <v>124.29</v>
       </c>
       <c r="K29" t="n">
-        <v>-116.01</v>
+        <v>-106.4</v>
       </c>
       <c r="L29" t="n">
-        <v>178.38</v>
+        <v>163.61</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>111.52</v>
+        <v>118.35</v>
       </c>
       <c r="K30" t="n">
-        <v>129.84</v>
+        <v>137.79</v>
       </c>
       <c r="L30" t="n">
-        <v>171.16</v>
+        <v>181.64</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>26.65</v>
+        <v>24.71</v>
       </c>
       <c r="K31" t="n">
-        <v>143.66</v>
+        <v>133.16</v>
       </c>
       <c r="L31" t="n">
-        <v>146.11</v>
+        <v>135.43</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>68.94</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-170.5</v>
+        <v>-192.33</v>
       </c>
       <c r="L32" t="n">
-        <v>183.91</v>
+        <v>207.45</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>127.44</v>
+        <v>164.75</v>
       </c>
       <c r="K33" t="n">
-        <v>102.58</v>
+        <v>132.61</v>
       </c>
       <c r="L33" t="n">
-        <v>163.59</v>
+        <v>211.49</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-88.76000000000001</v>
+        <v>-129.08</v>
       </c>
       <c r="K34" t="n">
-        <v>-32.39</v>
+        <v>-47.11</v>
       </c>
       <c r="L34" t="n">
-        <v>94.48</v>
+        <v>137.41</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-354.58</v>
+        <v>-398.52</v>
       </c>
       <c r="K35" t="n">
-        <v>312.02</v>
+        <v>350.68</v>
       </c>
       <c r="L35" t="n">
-        <v>472.32</v>
+        <v>530.84</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-413.64</v>
+        <v>-419.79</v>
       </c>
       <c r="K36" t="n">
-        <v>-395.68</v>
+        <v>-401.56</v>
       </c>
       <c r="L36" t="n">
-        <v>572.41</v>
+        <v>580.9299999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>49.66</v>
+        <v>139.47</v>
       </c>
       <c r="K37" t="n">
-        <v>-36.74</v>
+        <v>-103.17</v>
       </c>
       <c r="L37" t="n">
-        <v>61.77</v>
+        <v>173.48</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-24.11</v>
+        <v>-39.58</v>
       </c>
       <c r="K38" t="n">
-        <v>-254.49</v>
+        <v>-417.89</v>
       </c>
       <c r="L38" t="n">
-        <v>255.63</v>
+        <v>419.76</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-559.12</v>
+        <v>-650.98</v>
       </c>
       <c r="K39" t="n">
-        <v>-230.2</v>
+        <v>-268.02</v>
       </c>
       <c r="L39" t="n">
-        <v>604.65</v>
+        <v>704</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-243.72</v>
+        <v>-383.13</v>
       </c>
       <c r="K40" t="n">
-        <v>-238.45</v>
+        <v>-374.84</v>
       </c>
       <c r="L40" t="n">
-        <v>340.96</v>
+        <v>536</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>767.25</v>
+        <v>867.85</v>
       </c>
       <c r="K41" t="n">
-        <v>353.43</v>
+        <v>399.78</v>
       </c>
       <c r="L41" t="n">
-        <v>844.74</v>
+        <v>955.5</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>252.75</v>
+        <v>409.37</v>
       </c>
       <c r="K42" t="n">
-        <v>-298.38</v>
+        <v>-483.28</v>
       </c>
       <c r="L42" t="n">
-        <v>391.05</v>
+        <v>633.36</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>22.97</v>
+        <v>27.06</v>
       </c>
       <c r="K43" t="n">
-        <v>-818.1900000000001</v>
+        <v>-963.6900000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>818.52</v>
+        <v>964.0700000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-100.44</v>
+        <v>-113.39</v>
       </c>
       <c r="K44" t="n">
-        <v>-106.69</v>
+        <v>-120.45</v>
       </c>
       <c r="L44" t="n">
-        <v>146.53</v>
+        <v>165.43</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>37.8</v>
+        <v>99.27</v>
       </c>
       <c r="K45" t="n">
-        <v>30.2</v>
+        <v>79.33</v>
       </c>
       <c r="L45" t="n">
-        <v>48.38</v>
+        <v>127.08</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>15.76</v>
+        <v>21.76</v>
       </c>
       <c r="K46" t="n">
-        <v>-130.87</v>
+        <v>-180.68</v>
       </c>
       <c r="L46" t="n">
-        <v>131.82</v>
+        <v>181.98</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-140.48</v>
+        <v>-150.49</v>
       </c>
       <c r="K47" t="n">
-        <v>-165.73</v>
+        <v>-177.53</v>
       </c>
       <c r="L47" t="n">
-        <v>217.26</v>
+        <v>232.73</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-241.34</v>
+        <v>-261.39</v>
       </c>
       <c r="K48" t="n">
-        <v>62.58</v>
+        <v>67.78</v>
       </c>
       <c r="L48" t="n">
-        <v>249.32</v>
+        <v>270.04</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-191.39</v>
+        <v>-200.62</v>
       </c>
       <c r="K49" t="n">
-        <v>156.75</v>
+        <v>164.32</v>
       </c>
       <c r="L49" t="n">
-        <v>247.39</v>
+        <v>259.33</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-32.48</v>
+        <v>-37.29</v>
       </c>
       <c r="K50" t="n">
-        <v>-502.81</v>
+        <v>-577.26</v>
       </c>
       <c r="L50" t="n">
-        <v>503.86</v>
+        <v>578.46</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-64.40000000000001</v>
+        <v>-99.39</v>
       </c>
       <c r="K51" t="n">
-        <v>-146.78</v>
+        <v>-226.53</v>
       </c>
       <c r="L51" t="n">
-        <v>160.29</v>
+        <v>247.37</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>572.89</v>
+        <v>519.84</v>
       </c>
       <c r="K52" t="n">
-        <v>308.38</v>
+        <v>279.83</v>
       </c>
       <c r="L52" t="n">
-        <v>650.61</v>
+        <v>590.37</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>87.40000000000001</v>
+        <v>153.02</v>
       </c>
       <c r="K53" t="n">
-        <v>195.24</v>
+        <v>341.82</v>
       </c>
       <c r="L53" t="n">
-        <v>213.91</v>
+        <v>374.51</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-357.44</v>
+        <v>-554.63</v>
       </c>
       <c r="K54" t="n">
-        <v>117.67</v>
+        <v>182.59</v>
       </c>
       <c r="L54" t="n">
-        <v>376.32</v>
+        <v>583.91</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>88.36</v>
+        <v>95.38</v>
       </c>
       <c r="K55" t="n">
-        <v>-637.48</v>
+        <v>-688.15</v>
       </c>
       <c r="L55" t="n">
-        <v>643.58</v>
+        <v>694.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>347.37</v>
+        <v>644.59</v>
       </c>
       <c r="K56" t="n">
-        <v>-239.92</v>
+        <v>-445.2</v>
       </c>
       <c r="L56" t="n">
-        <v>422.17</v>
+        <v>783.39</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>409.22</v>
+        <v>559.46</v>
       </c>
       <c r="K57" t="n">
-        <v>-493.79</v>
+        <v>-675.0700000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>641.3200000000001</v>
+        <v>876.77</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>183.85</v>
+        <v>438.1</v>
       </c>
       <c r="K58" t="n">
-        <v>124.18</v>
+        <v>295.9</v>
       </c>
       <c r="L58" t="n">
-        <v>221.86</v>
+        <v>528.67</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>49.87</v>
+        <v>57.9</v>
       </c>
       <c r="K59" t="n">
-        <v>-141.85</v>
+        <v>-164.68</v>
       </c>
       <c r="L59" t="n">
-        <v>150.36</v>
+        <v>174.56</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>64.5</v>
+        <v>87.73</v>
       </c>
       <c r="K60" t="n">
-        <v>100.22</v>
+        <v>136.33</v>
       </c>
       <c r="L60" t="n">
-        <v>119.18</v>
+        <v>162.12</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-20.99</v>
+        <v>-24.07</v>
       </c>
       <c r="K61" t="n">
-        <v>-178.02</v>
+        <v>-204.11</v>
       </c>
       <c r="L61" t="n">
-        <v>179.26</v>
+        <v>205.53</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>617.4299999999999</v>
+        <v>610.21</v>
       </c>
       <c r="K62" t="n">
-        <v>255.98</v>
+        <v>252.98</v>
       </c>
       <c r="L62" t="n">
-        <v>668.39</v>
+        <v>660.5700000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-8.119999999999999</v>
+        <v>-19.4</v>
       </c>
       <c r="K63" t="n">
-        <v>54.94</v>
+        <v>131.22</v>
       </c>
       <c r="L63" t="n">
-        <v>55.53</v>
+        <v>132.65</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-336.88</v>
+        <v>-351.56</v>
       </c>
       <c r="K64" t="n">
-        <v>-39.52</v>
+        <v>-41.24</v>
       </c>
       <c r="L64" t="n">
-        <v>339.19</v>
+        <v>353.97</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-32.77</v>
+        <v>-41.77</v>
       </c>
       <c r="K65" t="n">
-        <v>-365.29</v>
+        <v>-465.58</v>
       </c>
       <c r="L65" t="n">
-        <v>366.76</v>
+        <v>467.45</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>62.55</v>
+        <v>117.78</v>
       </c>
       <c r="K66" t="n">
-        <v>118.72</v>
+        <v>223.55</v>
       </c>
       <c r="L66" t="n">
-        <v>134.19</v>
+        <v>252.68</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>47.92</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>107.24</v>
+        <v>196.29</v>
       </c>
       <c r="L67" t="n">
-        <v>117.46</v>
+        <v>215</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-546.74</v>
+        <v>-658.11</v>
       </c>
       <c r="K68" t="n">
-        <v>-99.55</v>
+        <v>-119.82</v>
       </c>
       <c r="L68" t="n">
-        <v>555.73</v>
+        <v>668.9299999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-453.69</v>
+        <v>-597.85</v>
       </c>
       <c r="K69" t="n">
-        <v>-98.97</v>
+        <v>-130.41</v>
       </c>
       <c r="L69" t="n">
-        <v>464.36</v>
+        <v>611.91</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-664.78</v>
+        <v>-750.5599999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-217.02</v>
+        <v>-245.02</v>
       </c>
       <c r="L70" t="n">
-        <v>699.3</v>
+        <v>789.54</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>158.86</v>
+        <v>274.46</v>
       </c>
       <c r="K71" t="n">
-        <v>-371.22</v>
+        <v>-641.34</v>
       </c>
       <c r="L71" t="n">
-        <v>403.78</v>
+        <v>697.6</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>426.23</v>
+        <v>604.88</v>
       </c>
       <c r="K72" t="n">
-        <v>-292.62</v>
+        <v>-415.27</v>
       </c>
       <c r="L72" t="n">
-        <v>517.01</v>
+        <v>733.71</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-435.82</v>
+        <v>-556.75</v>
       </c>
       <c r="K73" t="n">
-        <v>335.55</v>
+        <v>428.66</v>
       </c>
       <c r="L73" t="n">
-        <v>550.03</v>
+        <v>702.65</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>153.76</v>
+        <v>169.36</v>
       </c>
       <c r="K74" t="n">
-        <v>82.83</v>
+        <v>91.23</v>
       </c>
       <c r="L74" t="n">
-        <v>174.65</v>
+        <v>192.37</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-99.81999999999999</v>
+        <v>-131.53</v>
       </c>
       <c r="K75" t="n">
-        <v>42.9</v>
+        <v>56.53</v>
       </c>
       <c r="L75" t="n">
-        <v>108.64</v>
+        <v>143.16</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>122.85</v>
+        <v>126.51</v>
       </c>
       <c r="K76" t="n">
-        <v>62.05</v>
+        <v>63.9</v>
       </c>
       <c r="L76" t="n">
-        <v>137.63</v>
+        <v>141.73</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>356.24</v>
+        <v>386.04</v>
       </c>
       <c r="K77" t="n">
-        <v>-33.43</v>
+        <v>-36.23</v>
       </c>
       <c r="L77" t="n">
-        <v>357.81</v>
+        <v>387.73</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-115.7</v>
+        <v>-140.37</v>
       </c>
       <c r="K78" t="n">
-        <v>96.52</v>
+        <v>117.1</v>
       </c>
       <c r="L78" t="n">
-        <v>150.67</v>
+        <v>182.8</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>236.68</v>
+        <v>220.29</v>
       </c>
       <c r="K79" t="n">
-        <v>-47.01</v>
+        <v>-43.75</v>
       </c>
       <c r="L79" t="n">
-        <v>241.3</v>
+        <v>224.59</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-332.62</v>
+        <v>-389.53</v>
       </c>
       <c r="K80" t="n">
-        <v>-39.03</v>
+        <v>-45.71</v>
       </c>
       <c r="L80" t="n">
-        <v>334.91</v>
+        <v>392.21</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>238.64</v>
+        <v>299.92</v>
       </c>
       <c r="K81" t="n">
-        <v>105.48</v>
+        <v>132.57</v>
       </c>
       <c r="L81" t="n">
-        <v>260.91</v>
+        <v>327.91</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>210.89</v>
+        <v>296.35</v>
       </c>
       <c r="K82" t="n">
-        <v>-186.94</v>
+        <v>-262.7</v>
       </c>
       <c r="L82" t="n">
-        <v>281.82</v>
+        <v>396.03</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>180.74</v>
+        <v>319.98</v>
       </c>
       <c r="K83" t="n">
-        <v>153.17</v>
+        <v>271.17</v>
       </c>
       <c r="L83" t="n">
-        <v>236.91</v>
+        <v>419.43</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-242.55</v>
+        <v>-420.58</v>
       </c>
       <c r="K84" t="n">
-        <v>-71.59</v>
+        <v>-124.14</v>
       </c>
       <c r="L84" t="n">
-        <v>252.9</v>
+        <v>438.52</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>40.55</v>
+        <v>59.19</v>
       </c>
       <c r="K85" t="n">
-        <v>-245.72</v>
+        <v>-358.65</v>
       </c>
       <c r="L85" t="n">
-        <v>249.04</v>
+        <v>363.5</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-461.62</v>
+        <v>-661.3099999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>270.04</v>
+        <v>386.86</v>
       </c>
       <c r="L86" t="n">
-        <v>534.8</v>
+        <v>766.15</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>409.5</v>
+        <v>517</v>
       </c>
       <c r="K87" t="n">
-        <v>-383.51</v>
+        <v>-484.19</v>
       </c>
       <c r="L87" t="n">
-        <v>561.04</v>
+        <v>708.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-130.36</v>
+        <v>-148.13</v>
       </c>
       <c r="K88" t="n">
-        <v>875.33</v>
+        <v>994.6799999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>884.98</v>
+        <v>1005.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="K14" t="n">
-        <v>-63.3</v>
+        <v>-51.7</v>
       </c>
       <c r="L14" t="n">
-        <v>63.32</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.82</v>
+        <v>-2.69</v>
       </c>
       <c r="K15" t="n">
-        <v>-183.05</v>
+        <v>-128.65</v>
       </c>
       <c r="L15" t="n">
-        <v>183.08</v>
+        <v>128.68</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-76.01000000000001</v>
+        <v>-58.19</v>
       </c>
       <c r="K16" t="n">
-        <v>-66.33</v>
+        <v>-50.78</v>
       </c>
       <c r="L16" t="n">
-        <v>100.88</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>49.31</v>
+        <v>35.11</v>
       </c>
       <c r="K17" t="n">
-        <v>217.56</v>
+        <v>154.89</v>
       </c>
       <c r="L17" t="n">
-        <v>223.07</v>
+        <v>158.82</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>225.37</v>
+        <v>149</v>
       </c>
       <c r="K18" t="n">
-        <v>-144.71</v>
+        <v>-95.67</v>
       </c>
       <c r="L18" t="n">
-        <v>267.83</v>
+        <v>177.07</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>194.68</v>
+        <v>142.17</v>
       </c>
       <c r="K19" t="n">
-        <v>-22.03</v>
+        <v>-16.09</v>
       </c>
       <c r="L19" t="n">
-        <v>195.92</v>
+        <v>143.08</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-41.95</v>
+        <v>-27.12</v>
       </c>
       <c r="K20" t="n">
-        <v>-278.7</v>
+        <v>-180.18</v>
       </c>
       <c r="L20" t="n">
-        <v>281.84</v>
+        <v>182.21</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-358.14</v>
+        <v>-207.62</v>
       </c>
       <c r="K21" t="n">
-        <v>472.97</v>
+        <v>274.19</v>
       </c>
       <c r="L21" t="n">
-        <v>593.27</v>
+        <v>343.93</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-317.05</v>
+        <v>-177.65</v>
       </c>
       <c r="K22" t="n">
-        <v>313.51</v>
+        <v>175.66</v>
       </c>
       <c r="L22" t="n">
-        <v>445.88</v>
+        <v>249.83</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-219.3</v>
+        <v>-120.6</v>
       </c>
       <c r="K23" t="n">
-        <v>106.16</v>
+        <v>58.38</v>
       </c>
       <c r="L23" t="n">
-        <v>243.64</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>41.61</v>
+        <v>24.02</v>
       </c>
       <c r="K24" t="n">
-        <v>-268.17</v>
+        <v>-154.77</v>
       </c>
       <c r="L24" t="n">
-        <v>271.38</v>
+        <v>156.62</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-677.5599999999999</v>
+        <v>-375.43</v>
       </c>
       <c r="K25" t="n">
-        <v>261.24</v>
+        <v>144.75</v>
       </c>
       <c r="L25" t="n">
-        <v>726.1799999999999</v>
+        <v>402.36</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>347.61</v>
+        <v>169.46</v>
       </c>
       <c r="K26" t="n">
-        <v>-774.29</v>
+        <v>-377.46</v>
       </c>
       <c r="L26" t="n">
-        <v>848.74</v>
+        <v>413.75</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-34.6</v>
+        <v>-17.44</v>
       </c>
       <c r="K27" t="n">
-        <v>-352.28</v>
+        <v>-177.55</v>
       </c>
       <c r="L27" t="n">
-        <v>353.97</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-444.23</v>
+        <v>-210.98</v>
       </c>
       <c r="K28" t="n">
-        <v>-60.39</v>
+        <v>-28.68</v>
       </c>
       <c r="L28" t="n">
-        <v>448.32</v>
+        <v>212.92</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>124.29</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>-106.4</v>
+        <v>-79.65000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>163.61</v>
+        <v>122.48</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>118.35</v>
+        <v>87.78</v>
       </c>
       <c r="K30" t="n">
-        <v>137.79</v>
+        <v>102.2</v>
       </c>
       <c r="L30" t="n">
-        <v>181.64</v>
+        <v>134.72</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>24.71</v>
+        <v>20.44</v>
       </c>
       <c r="K31" t="n">
-        <v>133.16</v>
+        <v>110.18</v>
       </c>
       <c r="L31" t="n">
-        <v>135.43</v>
+        <v>112.06</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>77.76000000000001</v>
+        <v>50.96</v>
       </c>
       <c r="K32" t="n">
-        <v>-192.33</v>
+        <v>-126.04</v>
       </c>
       <c r="L32" t="n">
-        <v>207.45</v>
+        <v>135.96</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>164.75</v>
+        <v>113.3</v>
       </c>
       <c r="K33" t="n">
-        <v>132.61</v>
+        <v>91.2</v>
       </c>
       <c r="L33" t="n">
-        <v>211.49</v>
+        <v>145.45</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-129.08</v>
+        <v>-85.76000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-47.11</v>
+        <v>-31.3</v>
       </c>
       <c r="L34" t="n">
-        <v>137.41</v>
+        <v>91.29000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-398.52</v>
+        <v>-231.73</v>
       </c>
       <c r="K35" t="n">
-        <v>350.68</v>
+        <v>203.91</v>
       </c>
       <c r="L35" t="n">
-        <v>530.84</v>
+        <v>308.67</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-419.79</v>
+        <v>-244.13</v>
       </c>
       <c r="K36" t="n">
-        <v>-401.56</v>
+        <v>-233.53</v>
       </c>
       <c r="L36" t="n">
-        <v>580.9299999999999</v>
+        <v>337.84</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>139.47</v>
+        <v>78.91</v>
       </c>
       <c r="K37" t="n">
-        <v>-103.17</v>
+        <v>-58.37</v>
       </c>
       <c r="L37" t="n">
-        <v>173.48</v>
+        <v>98.16</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-39.58</v>
+        <v>-19.72</v>
       </c>
       <c r="K38" t="n">
-        <v>-417.89</v>
+        <v>-208.16</v>
       </c>
       <c r="L38" t="n">
-        <v>419.76</v>
+        <v>209.09</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-650.98</v>
+        <v>-321.76</v>
       </c>
       <c r="K39" t="n">
-        <v>-268.02</v>
+        <v>-132.47</v>
       </c>
       <c r="L39" t="n">
-        <v>704</v>
+        <v>347.97</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-383.13</v>
+        <v>-198.7</v>
       </c>
       <c r="K40" t="n">
-        <v>-374.84</v>
+        <v>-194.41</v>
       </c>
       <c r="L40" t="n">
-        <v>536</v>
+        <v>277.99</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>867.85</v>
+        <v>409.43</v>
       </c>
       <c r="K41" t="n">
-        <v>399.78</v>
+        <v>188.6</v>
       </c>
       <c r="L41" t="n">
-        <v>955.5</v>
+        <v>450.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>409.37</v>
+        <v>194.46</v>
       </c>
       <c r="K42" t="n">
-        <v>-483.28</v>
+        <v>-229.57</v>
       </c>
       <c r="L42" t="n">
-        <v>633.36</v>
+        <v>300.86</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>27.06</v>
+        <v>13.36</v>
       </c>
       <c r="K43" t="n">
-        <v>-963.6900000000001</v>
+        <v>-475.74</v>
       </c>
       <c r="L43" t="n">
-        <v>964.0700000000001</v>
+        <v>475.93</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-113.39</v>
+        <v>-79.23999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-120.45</v>
+        <v>-84.17</v>
       </c>
       <c r="L44" t="n">
-        <v>165.43</v>
+        <v>115.61</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>99.27</v>
+        <v>66.62</v>
       </c>
       <c r="K45" t="n">
-        <v>79.33</v>
+        <v>53.24</v>
       </c>
       <c r="L45" t="n">
-        <v>127.08</v>
+        <v>85.28</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>21.76</v>
+        <v>14.25</v>
       </c>
       <c r="K46" t="n">
-        <v>-180.68</v>
+        <v>-118.3</v>
       </c>
       <c r="L46" t="n">
-        <v>181.98</v>
+        <v>119.16</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-150.49</v>
+        <v>-105.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-177.53</v>
+        <v>-124.92</v>
       </c>
       <c r="L47" t="n">
-        <v>232.73</v>
+        <v>163.76</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-261.39</v>
+        <v>-170.36</v>
       </c>
       <c r="K48" t="n">
-        <v>67.78</v>
+        <v>44.18</v>
       </c>
       <c r="L48" t="n">
-        <v>270.04</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-200.62</v>
+        <v>-130.16</v>
       </c>
       <c r="K49" t="n">
-        <v>164.32</v>
+        <v>106.61</v>
       </c>
       <c r="L49" t="n">
-        <v>259.33</v>
+        <v>168.24</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-37.29</v>
+        <v>-20.98</v>
       </c>
       <c r="K50" t="n">
-        <v>-577.26</v>
+        <v>-324.76</v>
       </c>
       <c r="L50" t="n">
-        <v>578.46</v>
+        <v>325.44</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-99.39</v>
+        <v>-59.49</v>
       </c>
       <c r="K51" t="n">
-        <v>-226.53</v>
+        <v>-135.6</v>
       </c>
       <c r="L51" t="n">
-        <v>247.37</v>
+        <v>148.08</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>519.84</v>
+        <v>331.86</v>
       </c>
       <c r="K52" t="n">
-        <v>279.83</v>
+        <v>178.64</v>
       </c>
       <c r="L52" t="n">
-        <v>590.37</v>
+        <v>376.88</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>153.02</v>
+        <v>75.27</v>
       </c>
       <c r="K53" t="n">
-        <v>341.82</v>
+        <v>168.14</v>
       </c>
       <c r="L53" t="n">
-        <v>374.51</v>
+        <v>184.22</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-554.63</v>
+        <v>-273.24</v>
       </c>
       <c r="K54" t="n">
-        <v>182.59</v>
+        <v>89.95</v>
       </c>
       <c r="L54" t="n">
-        <v>583.91</v>
+        <v>287.67</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>95.38</v>
+        <v>48.22</v>
       </c>
       <c r="K55" t="n">
-        <v>-688.15</v>
+        <v>-347.9</v>
       </c>
       <c r="L55" t="n">
-        <v>694.73</v>
+        <v>351.22</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>644.59</v>
+        <v>284.19</v>
       </c>
       <c r="K56" t="n">
-        <v>-445.2</v>
+        <v>-196.28</v>
       </c>
       <c r="L56" t="n">
-        <v>783.39</v>
+        <v>345.38</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>559.46</v>
+        <v>253.77</v>
       </c>
       <c r="K57" t="n">
-        <v>-675.0700000000001</v>
+        <v>-306.21</v>
       </c>
       <c r="L57" t="n">
-        <v>876.77</v>
+        <v>397.7</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>438.1</v>
+        <v>191.88</v>
       </c>
       <c r="K58" t="n">
-        <v>295.9</v>
+        <v>129.6</v>
       </c>
       <c r="L58" t="n">
-        <v>528.67</v>
+        <v>231.55</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>57.9</v>
+        <v>41.38</v>
       </c>
       <c r="K59" t="n">
-        <v>-164.68</v>
+        <v>-117.7</v>
       </c>
       <c r="L59" t="n">
-        <v>174.56</v>
+        <v>124.76</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>87.73</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>136.33</v>
+        <v>100.22</v>
       </c>
       <c r="L60" t="n">
-        <v>162.12</v>
+        <v>119.18</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-24.07</v>
+        <v>-16.29</v>
       </c>
       <c r="K61" t="n">
-        <v>-204.11</v>
+        <v>-138.16</v>
       </c>
       <c r="L61" t="n">
-        <v>205.53</v>
+        <v>139.12</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>610.21</v>
+        <v>371.73</v>
       </c>
       <c r="K62" t="n">
-        <v>252.98</v>
+        <v>154.11</v>
       </c>
       <c r="L62" t="n">
-        <v>660.5700000000001</v>
+        <v>402.41</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-19.4</v>
+        <v>-13.24</v>
       </c>
       <c r="K63" t="n">
-        <v>131.22</v>
+        <v>89.55</v>
       </c>
       <c r="L63" t="n">
-        <v>132.65</v>
+        <v>90.52</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-351.56</v>
+        <v>-221.02</v>
       </c>
       <c r="K64" t="n">
-        <v>-41.24</v>
+        <v>-25.93</v>
       </c>
       <c r="L64" t="n">
-        <v>353.97</v>
+        <v>222.53</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-41.77</v>
+        <v>-22.95</v>
       </c>
       <c r="K65" t="n">
-        <v>-465.58</v>
+        <v>-255.88</v>
       </c>
       <c r="L65" t="n">
-        <v>467.45</v>
+        <v>256.91</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>117.78</v>
+        <v>68.34</v>
       </c>
       <c r="K66" t="n">
-        <v>223.55</v>
+        <v>129.7</v>
       </c>
       <c r="L66" t="n">
-        <v>252.68</v>
+        <v>146.61</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>87.70999999999999</v>
+        <v>54.58</v>
       </c>
       <c r="K67" t="n">
-        <v>196.29</v>
+        <v>122.14</v>
       </c>
       <c r="L67" t="n">
-        <v>215</v>
+        <v>133.78</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-658.11</v>
+        <v>-341.92</v>
       </c>
       <c r="K68" t="n">
-        <v>-119.82</v>
+        <v>-62.25</v>
       </c>
       <c r="L68" t="n">
-        <v>668.9299999999999</v>
+        <v>347.54</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-597.85</v>
+        <v>-313.9</v>
       </c>
       <c r="K69" t="n">
-        <v>-130.41</v>
+        <v>-68.47</v>
       </c>
       <c r="L69" t="n">
-        <v>611.91</v>
+        <v>321.28</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-750.5599999999999</v>
+        <v>-376.19</v>
       </c>
       <c r="K70" t="n">
-        <v>-245.02</v>
+        <v>-122.81</v>
       </c>
       <c r="L70" t="n">
-        <v>789.54</v>
+        <v>395.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>274.46</v>
+        <v>120.03</v>
       </c>
       <c r="K71" t="n">
-        <v>-641.34</v>
+        <v>-280.48</v>
       </c>
       <c r="L71" t="n">
-        <v>697.6</v>
+        <v>305.09</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>604.88</v>
+        <v>276.94</v>
       </c>
       <c r="K72" t="n">
-        <v>-415.27</v>
+        <v>-190.13</v>
       </c>
       <c r="L72" t="n">
-        <v>733.71</v>
+        <v>335.93</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-556.75</v>
+        <v>-272.01</v>
       </c>
       <c r="K73" t="n">
-        <v>428.66</v>
+        <v>209.43</v>
       </c>
       <c r="L73" t="n">
-        <v>702.65</v>
+        <v>343.29</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>169.36</v>
+        <v>123.53</v>
       </c>
       <c r="K74" t="n">
-        <v>91.23</v>
+        <v>66.55</v>
       </c>
       <c r="L74" t="n">
-        <v>192.37</v>
+        <v>140.31</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-131.53</v>
+        <v>-98.56999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>56.53</v>
+        <v>42.36</v>
       </c>
       <c r="L75" t="n">
-        <v>143.16</v>
+        <v>107.29</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>126.51</v>
+        <v>101.38</v>
       </c>
       <c r="K76" t="n">
-        <v>63.9</v>
+        <v>51.21</v>
       </c>
       <c r="L76" t="n">
-        <v>141.73</v>
+        <v>113.58</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>386.04</v>
+        <v>252.43</v>
       </c>
       <c r="K77" t="n">
-        <v>-36.23</v>
+        <v>-23.69</v>
       </c>
       <c r="L77" t="n">
-        <v>387.73</v>
+        <v>253.54</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-140.37</v>
+        <v>-93.34</v>
       </c>
       <c r="K78" t="n">
-        <v>117.1</v>
+        <v>77.87</v>
       </c>
       <c r="L78" t="n">
-        <v>182.8</v>
+        <v>121.55</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>220.29</v>
+        <v>167.91</v>
       </c>
       <c r="K79" t="n">
-        <v>-43.75</v>
+        <v>-33.35</v>
       </c>
       <c r="L79" t="n">
-        <v>224.59</v>
+        <v>171.19</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-389.53</v>
+        <v>-235.57</v>
       </c>
       <c r="K80" t="n">
-        <v>-45.71</v>
+        <v>-27.64</v>
       </c>
       <c r="L80" t="n">
-        <v>392.21</v>
+        <v>237.18</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>299.92</v>
+        <v>178.61</v>
       </c>
       <c r="K81" t="n">
-        <v>132.57</v>
+        <v>78.95</v>
       </c>
       <c r="L81" t="n">
-        <v>327.91</v>
+        <v>195.28</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>296.35</v>
+        <v>159.87</v>
       </c>
       <c r="K82" t="n">
-        <v>-262.7</v>
+        <v>-141.71</v>
       </c>
       <c r="L82" t="n">
-        <v>396.03</v>
+        <v>213.64</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>319.98</v>
+        <v>163.61</v>
       </c>
       <c r="K83" t="n">
-        <v>271.17</v>
+        <v>138.65</v>
       </c>
       <c r="L83" t="n">
-        <v>419.43</v>
+        <v>214.46</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-420.58</v>
+        <v>-214.48</v>
       </c>
       <c r="K84" t="n">
-        <v>-124.14</v>
+        <v>-63.31</v>
       </c>
       <c r="L84" t="n">
-        <v>438.52</v>
+        <v>223.63</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>59.19</v>
+        <v>33.88</v>
       </c>
       <c r="K85" t="n">
-        <v>-358.65</v>
+        <v>-205.27</v>
       </c>
       <c r="L85" t="n">
-        <v>363.5</v>
+        <v>208.05</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-661.3099999999999</v>
+        <v>-319.68</v>
       </c>
       <c r="K86" t="n">
-        <v>386.86</v>
+        <v>187.01</v>
       </c>
       <c r="L86" t="n">
-        <v>766.15</v>
+        <v>370.36</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>517</v>
+        <v>258.32</v>
       </c>
       <c r="K87" t="n">
-        <v>-484.19</v>
+        <v>-241.93</v>
       </c>
       <c r="L87" t="n">
-        <v>708.33</v>
+        <v>353.92</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-148.13</v>
+        <v>-71.98</v>
       </c>
       <c r="K88" t="n">
-        <v>994.6799999999999</v>
+        <v>483.32</v>
       </c>
       <c r="L88" t="n">
-        <v>1005.65</v>
+        <v>488.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="K14" t="n">
-        <v>-51.7</v>
+        <v>-54.89</v>
       </c>
       <c r="L14" t="n">
-        <v>51.72</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.69</v>
+        <v>-2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>-128.65</v>
+        <v>-137.04</v>
       </c>
       <c r="L15" t="n">
-        <v>128.68</v>
+        <v>137.07</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-58.19</v>
+        <v>-62.13</v>
       </c>
       <c r="K16" t="n">
-        <v>-50.78</v>
+        <v>-54.21</v>
       </c>
       <c r="L16" t="n">
-        <v>77.23</v>
+        <v>82.45999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>35.11</v>
+        <v>38.95</v>
       </c>
       <c r="K17" t="n">
-        <v>154.89</v>
+        <v>171.84</v>
       </c>
       <c r="L17" t="n">
-        <v>158.82</v>
+        <v>176.2</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>149</v>
+        <v>167.81</v>
       </c>
       <c r="K18" t="n">
-        <v>-95.67</v>
+        <v>-107.75</v>
       </c>
       <c r="L18" t="n">
-        <v>177.07</v>
+        <v>199.43</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>142.17</v>
+        <v>156.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-16.09</v>
+        <v>-17.68</v>
       </c>
       <c r="L19" t="n">
-        <v>143.08</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-27.12</v>
+        <v>-30.84</v>
       </c>
       <c r="K20" t="n">
-        <v>-180.18</v>
+        <v>-204.91</v>
       </c>
       <c r="L20" t="n">
-        <v>182.21</v>
+        <v>207.21</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-207.62</v>
+        <v>-238.86</v>
       </c>
       <c r="K21" t="n">
-        <v>274.19</v>
+        <v>315.45</v>
       </c>
       <c r="L21" t="n">
-        <v>343.93</v>
+        <v>395.67</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-177.65</v>
+        <v>-205.71</v>
       </c>
       <c r="K22" t="n">
-        <v>175.66</v>
+        <v>203.41</v>
       </c>
       <c r="L22" t="n">
-        <v>249.83</v>
+        <v>289.3</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-120.6</v>
+        <v>-142.08</v>
       </c>
       <c r="K23" t="n">
-        <v>58.38</v>
+        <v>68.78</v>
       </c>
       <c r="L23" t="n">
-        <v>133.99</v>
+        <v>157.86</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>24.02</v>
+        <v>27.82</v>
       </c>
       <c r="K24" t="n">
-        <v>-154.77</v>
+        <v>-179.28</v>
       </c>
       <c r="L24" t="n">
-        <v>156.62</v>
+        <v>181.42</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-375.43</v>
+        <v>-438.07</v>
       </c>
       <c r="K25" t="n">
-        <v>144.75</v>
+        <v>168.9</v>
       </c>
       <c r="L25" t="n">
-        <v>402.36</v>
+        <v>469.5</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>169.46</v>
+        <v>200.04</v>
       </c>
       <c r="K26" t="n">
-        <v>-377.46</v>
+        <v>-445.58</v>
       </c>
       <c r="L26" t="n">
-        <v>413.75</v>
+        <v>488.42</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-17.44</v>
+        <v>-20.42</v>
       </c>
       <c r="K27" t="n">
-        <v>-177.55</v>
+        <v>-207.86</v>
       </c>
       <c r="L27" t="n">
-        <v>178.4</v>
+        <v>208.86</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-210.98</v>
+        <v>-251.91</v>
       </c>
       <c r="K28" t="n">
-        <v>-28.68</v>
+        <v>-34.24</v>
       </c>
       <c r="L28" t="n">
-        <v>212.92</v>
+        <v>254.22</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>93.04000000000001</v>
+        <v>99.34</v>
       </c>
       <c r="K29" t="n">
-        <v>-79.65000000000001</v>
+        <v>-85.04000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>122.48</v>
+        <v>130.77</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>87.78</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>102.2</v>
+        <v>109.14</v>
       </c>
       <c r="L30" t="n">
-        <v>134.72</v>
+        <v>143.87</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>20.44</v>
+        <v>21.5</v>
       </c>
       <c r="K31" t="n">
-        <v>110.18</v>
+        <v>115.9</v>
       </c>
       <c r="L31" t="n">
-        <v>112.06</v>
+        <v>117.88</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>50.96</v>
+        <v>57.22</v>
       </c>
       <c r="K32" t="n">
-        <v>-126.04</v>
+        <v>-141.52</v>
       </c>
       <c r="L32" t="n">
-        <v>135.96</v>
+        <v>152.64</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>113.3</v>
+        <v>124.8</v>
       </c>
       <c r="K33" t="n">
-        <v>91.2</v>
+        <v>100.45</v>
       </c>
       <c r="L33" t="n">
-        <v>145.45</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-85.76000000000001</v>
+        <v>-95.77</v>
       </c>
       <c r="K34" t="n">
-        <v>-31.3</v>
+        <v>-34.95</v>
       </c>
       <c r="L34" t="n">
-        <v>91.29000000000001</v>
+        <v>101.95</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-231.73</v>
+        <v>-264.45</v>
       </c>
       <c r="K35" t="n">
-        <v>203.91</v>
+        <v>232.7</v>
       </c>
       <c r="L35" t="n">
-        <v>308.67</v>
+        <v>352.25</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-244.13</v>
+        <v>-282.12</v>
       </c>
       <c r="K36" t="n">
-        <v>-233.53</v>
+        <v>-269.86</v>
       </c>
       <c r="L36" t="n">
-        <v>337.84</v>
+        <v>390.4</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>78.91</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-58.37</v>
+        <v>-68.03</v>
       </c>
       <c r="L37" t="n">
-        <v>98.16</v>
+        <v>114.39</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-19.72</v>
+        <v>-23.36</v>
       </c>
       <c r="K38" t="n">
-        <v>-208.16</v>
+        <v>-246.63</v>
       </c>
       <c r="L38" t="n">
-        <v>209.09</v>
+        <v>247.73</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-321.76</v>
+        <v>-380.48</v>
       </c>
       <c r="K39" t="n">
-        <v>-132.47</v>
+        <v>-156.65</v>
       </c>
       <c r="L39" t="n">
-        <v>347.97</v>
+        <v>411.47</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-198.7</v>
+        <v>-232.79</v>
       </c>
       <c r="K40" t="n">
-        <v>-194.41</v>
+        <v>-227.75</v>
       </c>
       <c r="L40" t="n">
-        <v>277.99</v>
+        <v>325.67</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>409.43</v>
+        <v>489.02</v>
       </c>
       <c r="K41" t="n">
-        <v>188.6</v>
+        <v>225.27</v>
       </c>
       <c r="L41" t="n">
-        <v>450.78</v>
+        <v>538.41</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>194.46</v>
+        <v>233.14</v>
       </c>
       <c r="K42" t="n">
-        <v>-229.57</v>
+        <v>-275.23</v>
       </c>
       <c r="L42" t="n">
-        <v>300.86</v>
+        <v>360.7</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>13.36</v>
+        <v>15.88</v>
       </c>
       <c r="K43" t="n">
-        <v>-475.74</v>
+        <v>-565.6900000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>475.93</v>
+        <v>565.91</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-79.23999999999999</v>
+        <v>-85.25</v>
       </c>
       <c r="K44" t="n">
-        <v>-84.17</v>
+        <v>-90.55</v>
       </c>
       <c r="L44" t="n">
-        <v>115.61</v>
+        <v>124.37</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>66.62</v>
+        <v>72</v>
       </c>
       <c r="K45" t="n">
-        <v>53.24</v>
+        <v>57.53</v>
       </c>
       <c r="L45" t="n">
-        <v>85.28</v>
+        <v>92.16</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>14.25</v>
+        <v>15.44</v>
       </c>
       <c r="K46" t="n">
-        <v>-118.3</v>
+        <v>-128.24</v>
       </c>
       <c r="L46" t="n">
-        <v>119.16</v>
+        <v>129.16</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-105.89</v>
+        <v>-117.54</v>
       </c>
       <c r="K47" t="n">
-        <v>-124.92</v>
+        <v>-138.67</v>
       </c>
       <c r="L47" t="n">
-        <v>163.76</v>
+        <v>181.78</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-170.36</v>
+        <v>-190.94</v>
       </c>
       <c r="K48" t="n">
-        <v>44.18</v>
+        <v>49.51</v>
       </c>
       <c r="L48" t="n">
-        <v>176</v>
+        <v>197.25</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-130.16</v>
+        <v>-147.05</v>
       </c>
       <c r="K49" t="n">
-        <v>106.61</v>
+        <v>120.44</v>
       </c>
       <c r="L49" t="n">
-        <v>168.24</v>
+        <v>190.07</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-20.98</v>
+        <v>-23.96</v>
       </c>
       <c r="K50" t="n">
-        <v>-324.76</v>
+        <v>-370.9</v>
       </c>
       <c r="L50" t="n">
-        <v>325.44</v>
+        <v>371.67</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-59.49</v>
+        <v>-67.61</v>
       </c>
       <c r="K51" t="n">
-        <v>-135.6</v>
+        <v>-154.1</v>
       </c>
       <c r="L51" t="n">
-        <v>148.08</v>
+        <v>168.28</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>331.86</v>
+        <v>378.24</v>
       </c>
       <c r="K52" t="n">
-        <v>178.64</v>
+        <v>203.6</v>
       </c>
       <c r="L52" t="n">
-        <v>376.88</v>
+        <v>429.56</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>75.27</v>
+        <v>89.25</v>
       </c>
       <c r="K53" t="n">
-        <v>168.14</v>
+        <v>199.38</v>
       </c>
       <c r="L53" t="n">
-        <v>184.22</v>
+        <v>218.45</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-273.24</v>
+        <v>-324.47</v>
       </c>
       <c r="K54" t="n">
-        <v>89.95</v>
+        <v>106.82</v>
       </c>
       <c r="L54" t="n">
-        <v>287.67</v>
+        <v>341.61</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>48.22</v>
+        <v>57.49</v>
       </c>
       <c r="K55" t="n">
-        <v>-347.9</v>
+        <v>-414.73</v>
       </c>
       <c r="L55" t="n">
-        <v>351.22</v>
+        <v>418.69</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>284.19</v>
+        <v>344.59</v>
       </c>
       <c r="K56" t="n">
-        <v>-196.28</v>
+        <v>-238</v>
       </c>
       <c r="L56" t="n">
-        <v>345.38</v>
+        <v>418.79</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>253.77</v>
+        <v>305.73</v>
       </c>
       <c r="K57" t="n">
-        <v>-306.21</v>
+        <v>-368.91</v>
       </c>
       <c r="L57" t="n">
-        <v>397.7</v>
+        <v>479.13</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>191.88</v>
+        <v>231.58</v>
       </c>
       <c r="K58" t="n">
-        <v>129.6</v>
+        <v>156.41</v>
       </c>
       <c r="L58" t="n">
-        <v>231.55</v>
+        <v>279.45</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>41.38</v>
+        <v>44.42</v>
       </c>
       <c r="K59" t="n">
-        <v>-117.7</v>
+        <v>-126.33</v>
       </c>
       <c r="L59" t="n">
-        <v>124.76</v>
+        <v>133.91</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>64.48999999999999</v>
+        <v>69.34</v>
       </c>
       <c r="K60" t="n">
-        <v>100.22</v>
+        <v>107.75</v>
       </c>
       <c r="L60" t="n">
-        <v>119.18</v>
+        <v>128.14</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.29</v>
+        <v>-17.66</v>
       </c>
       <c r="K61" t="n">
-        <v>-138.16</v>
+        <v>-149.75</v>
       </c>
       <c r="L61" t="n">
-        <v>139.12</v>
+        <v>150.79</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>371.73</v>
+        <v>417.83</v>
       </c>
       <c r="K62" t="n">
-        <v>154.11</v>
+        <v>173.23</v>
       </c>
       <c r="L62" t="n">
-        <v>402.41</v>
+        <v>452.31</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-13.24</v>
+        <v>-14.59</v>
       </c>
       <c r="K63" t="n">
-        <v>89.55</v>
+        <v>98.69</v>
       </c>
       <c r="L63" t="n">
-        <v>90.52</v>
+        <v>99.76000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-221.02</v>
+        <v>-248.85</v>
       </c>
       <c r="K64" t="n">
-        <v>-25.93</v>
+        <v>-29.19</v>
       </c>
       <c r="L64" t="n">
-        <v>222.53</v>
+        <v>250.55</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-22.95</v>
+        <v>-26.49</v>
       </c>
       <c r="K65" t="n">
-        <v>-255.88</v>
+        <v>-295.26</v>
       </c>
       <c r="L65" t="n">
-        <v>256.91</v>
+        <v>296.45</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>68.34</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>129.7</v>
+        <v>148.11</v>
       </c>
       <c r="L66" t="n">
-        <v>146.61</v>
+        <v>167.42</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>54.58</v>
+        <v>61.65</v>
       </c>
       <c r="K67" t="n">
-        <v>122.14</v>
+        <v>137.96</v>
       </c>
       <c r="L67" t="n">
-        <v>133.78</v>
+        <v>151.11</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-341.92</v>
+        <v>-400.8</v>
       </c>
       <c r="K68" t="n">
-        <v>-62.25</v>
+        <v>-72.97</v>
       </c>
       <c r="L68" t="n">
-        <v>347.54</v>
+        <v>407.39</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-313.9</v>
+        <v>-368.77</v>
       </c>
       <c r="K69" t="n">
-        <v>-68.47</v>
+        <v>-80.44</v>
       </c>
       <c r="L69" t="n">
-        <v>321.28</v>
+        <v>377.44</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-376.19</v>
+        <v>-444.14</v>
       </c>
       <c r="K70" t="n">
-        <v>-122.81</v>
+        <v>-144.99</v>
       </c>
       <c r="L70" t="n">
-        <v>395.73</v>
+        <v>467.21</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>120.03</v>
+        <v>145.3</v>
       </c>
       <c r="K71" t="n">
-        <v>-280.48</v>
+        <v>-339.53</v>
       </c>
       <c r="L71" t="n">
-        <v>305.09</v>
+        <v>369.31</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>276.94</v>
+        <v>332.04</v>
       </c>
       <c r="K72" t="n">
-        <v>-190.13</v>
+        <v>-227.95</v>
       </c>
       <c r="L72" t="n">
-        <v>335.93</v>
+        <v>402.76</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-272.01</v>
+        <v>-321.83</v>
       </c>
       <c r="K73" t="n">
-        <v>209.43</v>
+        <v>247.78</v>
       </c>
       <c r="L73" t="n">
-        <v>343.29</v>
+        <v>406.16</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>123.53</v>
+        <v>132.76</v>
       </c>
       <c r="K74" t="n">
-        <v>66.55</v>
+        <v>71.52</v>
       </c>
       <c r="L74" t="n">
-        <v>140.31</v>
+        <v>150.8</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-98.56999999999999</v>
+        <v>-105.63</v>
       </c>
       <c r="K75" t="n">
-        <v>42.36</v>
+        <v>45.4</v>
       </c>
       <c r="L75" t="n">
-        <v>107.29</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>101.38</v>
+        <v>105.83</v>
       </c>
       <c r="K76" t="n">
-        <v>51.21</v>
+        <v>53.46</v>
       </c>
       <c r="L76" t="n">
-        <v>113.58</v>
+        <v>118.57</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>252.43</v>
+        <v>278.64</v>
       </c>
       <c r="K77" t="n">
-        <v>-23.69</v>
+        <v>-26.15</v>
       </c>
       <c r="L77" t="n">
-        <v>253.54</v>
+        <v>279.86</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-93.34</v>
+        <v>-104.84</v>
       </c>
       <c r="K78" t="n">
-        <v>77.87</v>
+        <v>87.47</v>
       </c>
       <c r="L78" t="n">
-        <v>121.55</v>
+        <v>136.54</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>167.91</v>
+        <v>184.76</v>
       </c>
       <c r="K79" t="n">
-        <v>-33.35</v>
+        <v>-36.7</v>
       </c>
       <c r="L79" t="n">
-        <v>171.19</v>
+        <v>188.37</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-235.57</v>
+        <v>-269.77</v>
       </c>
       <c r="K80" t="n">
-        <v>-27.64</v>
+        <v>-31.66</v>
       </c>
       <c r="L80" t="n">
-        <v>237.18</v>
+        <v>271.62</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>178.61</v>
+        <v>204.44</v>
       </c>
       <c r="K81" t="n">
-        <v>78.95</v>
+        <v>90.37</v>
       </c>
       <c r="L81" t="n">
-        <v>195.28</v>
+        <v>223.52</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>159.87</v>
+        <v>186.31</v>
       </c>
       <c r="K82" t="n">
-        <v>-141.71</v>
+        <v>-165.15</v>
       </c>
       <c r="L82" t="n">
-        <v>213.64</v>
+        <v>248.97</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>163.61</v>
+        <v>191.14</v>
       </c>
       <c r="K83" t="n">
-        <v>138.65</v>
+        <v>161.98</v>
       </c>
       <c r="L83" t="n">
-        <v>214.46</v>
+        <v>250.55</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-214.48</v>
+        <v>-253.29</v>
       </c>
       <c r="K84" t="n">
-        <v>-63.31</v>
+        <v>-74.76000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>223.63</v>
+        <v>264.1</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>33.88</v>
+        <v>39.25</v>
       </c>
       <c r="K85" t="n">
-        <v>-205.27</v>
+        <v>-237.83</v>
       </c>
       <c r="L85" t="n">
-        <v>208.05</v>
+        <v>241.04</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-319.68</v>
+        <v>-381.37</v>
       </c>
       <c r="K86" t="n">
-        <v>187.01</v>
+        <v>223.1</v>
       </c>
       <c r="L86" t="n">
-        <v>370.36</v>
+        <v>441.84</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>258.32</v>
+        <v>305.35</v>
       </c>
       <c r="K87" t="n">
-        <v>-241.93</v>
+        <v>-285.97</v>
       </c>
       <c r="L87" t="n">
-        <v>353.92</v>
+        <v>418.35</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-71.98</v>
+        <v>-85.5</v>
       </c>
       <c r="K88" t="n">
-        <v>483.32</v>
+        <v>574.11</v>
       </c>
       <c r="L88" t="n">
-        <v>488.65</v>
+        <v>580.4400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>1.33</v>
+        <v>0.85</v>
       </c>
       <c r="K14" t="n">
-        <v>-54.89</v>
+        <v>-35.08</v>
       </c>
       <c r="L14" t="n">
-        <v>54.9</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.86</v>
+        <v>-1.53</v>
       </c>
       <c r="K15" t="n">
-        <v>-137.04</v>
+        <v>-73.31999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>137.07</v>
+        <v>73.34</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-62.13</v>
+        <v>-37.97</v>
       </c>
       <c r="K16" t="n">
-        <v>-54.21</v>
+        <v>-33.13</v>
       </c>
       <c r="L16" t="n">
-        <v>82.45999999999999</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>38.95</v>
+        <v>25.22</v>
       </c>
       <c r="K17" t="n">
-        <v>171.84</v>
+        <v>111.25</v>
       </c>
       <c r="L17" t="n">
-        <v>176.2</v>
+        <v>114.08</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>167.81</v>
+        <v>92.17</v>
       </c>
       <c r="K18" t="n">
-        <v>-107.75</v>
+        <v>-59.19</v>
       </c>
       <c r="L18" t="n">
-        <v>199.43</v>
+        <v>109.54</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>156.25</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-17.68</v>
+        <v>-9.27</v>
       </c>
       <c r="L19" t="n">
-        <v>157.25</v>
+        <v>82.43000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-30.84</v>
+        <v>-16.48</v>
       </c>
       <c r="K20" t="n">
-        <v>-204.91</v>
+        <v>-109.52</v>
       </c>
       <c r="L20" t="n">
-        <v>207.21</v>
+        <v>110.76</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-238.86</v>
+        <v>-118.34</v>
       </c>
       <c r="K21" t="n">
-        <v>315.45</v>
+        <v>156.29</v>
       </c>
       <c r="L21" t="n">
-        <v>395.67</v>
+        <v>196.04</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-205.71</v>
+        <v>-109.72</v>
       </c>
       <c r="K22" t="n">
-        <v>203.41</v>
+        <v>108.5</v>
       </c>
       <c r="L22" t="n">
-        <v>289.3</v>
+        <v>154.31</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-142.08</v>
+        <v>-92.28</v>
       </c>
       <c r="K23" t="n">
-        <v>68.78</v>
+        <v>44.67</v>
       </c>
       <c r="L23" t="n">
-        <v>157.86</v>
+        <v>102.52</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>27.82</v>
+        <v>16.77</v>
       </c>
       <c r="K24" t="n">
-        <v>-179.28</v>
+        <v>-108.06</v>
       </c>
       <c r="L24" t="n">
-        <v>181.42</v>
+        <v>109.35</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-438.07</v>
+        <v>-203.67</v>
       </c>
       <c r="K25" t="n">
-        <v>168.9</v>
+        <v>78.53</v>
       </c>
       <c r="L25" t="n">
-        <v>469.5</v>
+        <v>218.28</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>200.04</v>
+        <v>115.52</v>
       </c>
       <c r="K26" t="n">
-        <v>-445.58</v>
+        <v>-257.31</v>
       </c>
       <c r="L26" t="n">
-        <v>488.42</v>
+        <v>282.05</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-20.42</v>
+        <v>-11.91</v>
       </c>
       <c r="K27" t="n">
-        <v>-207.86</v>
+        <v>-121.26</v>
       </c>
       <c r="L27" t="n">
-        <v>208.86</v>
+        <v>121.84</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-251.91</v>
+        <v>-146.46</v>
       </c>
       <c r="K28" t="n">
-        <v>-34.24</v>
+        <v>-19.91</v>
       </c>
       <c r="L28" t="n">
-        <v>254.22</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>99.34</v>
+        <v>58.93</v>
       </c>
       <c r="K29" t="n">
-        <v>-85.04000000000001</v>
+        <v>-50.45</v>
       </c>
       <c r="L29" t="n">
-        <v>130.77</v>
+        <v>77.56999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>93.73999999999999</v>
+        <v>49.35</v>
       </c>
       <c r="K30" t="n">
-        <v>109.14</v>
+        <v>57.46</v>
       </c>
       <c r="L30" t="n">
-        <v>143.87</v>
+        <v>75.73999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>21.5</v>
+        <v>12.34</v>
       </c>
       <c r="K31" t="n">
-        <v>115.9</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>117.88</v>
+        <v>67.63</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>57.22</v>
+        <v>32.71</v>
       </c>
       <c r="K32" t="n">
-        <v>-141.52</v>
+        <v>-80.90000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>152.64</v>
+        <v>87.27</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>124.8</v>
+        <v>60.06</v>
       </c>
       <c r="K33" t="n">
-        <v>100.45</v>
+        <v>48.34</v>
       </c>
       <c r="L33" t="n">
-        <v>160.2</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-95.77</v>
+        <v>-56.51</v>
       </c>
       <c r="K34" t="n">
-        <v>-34.95</v>
+        <v>-20.62</v>
       </c>
       <c r="L34" t="n">
-        <v>101.95</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-264.45</v>
+        <v>-131.5</v>
       </c>
       <c r="K35" t="n">
-        <v>232.7</v>
+        <v>115.72</v>
       </c>
       <c r="L35" t="n">
-        <v>352.25</v>
+        <v>175.17</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-282.12</v>
+        <v>-145.07</v>
       </c>
       <c r="K36" t="n">
-        <v>-269.86</v>
+        <v>-138.77</v>
       </c>
       <c r="L36" t="n">
-        <v>390.4</v>
+        <v>200.76</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>91.95999999999999</v>
+        <v>20.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-68.03</v>
+        <v>-15.22</v>
       </c>
       <c r="L37" t="n">
-        <v>114.39</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-23.36</v>
+        <v>-13.06</v>
       </c>
       <c r="K38" t="n">
-        <v>-246.63</v>
+        <v>-137.84</v>
       </c>
       <c r="L38" t="n">
-        <v>247.73</v>
+        <v>138.46</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-380.48</v>
+        <v>-223.76</v>
       </c>
       <c r="K39" t="n">
-        <v>-156.65</v>
+        <v>-92.13</v>
       </c>
       <c r="L39" t="n">
-        <v>411.47</v>
+        <v>241.99</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-232.79</v>
+        <v>-108.04</v>
       </c>
       <c r="K40" t="n">
-        <v>-227.75</v>
+        <v>-105.71</v>
       </c>
       <c r="L40" t="n">
-        <v>325.67</v>
+        <v>151.15</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>489.02</v>
+        <v>301.42</v>
       </c>
       <c r="K41" t="n">
-        <v>225.27</v>
+        <v>138.85</v>
       </c>
       <c r="L41" t="n">
-        <v>538.41</v>
+        <v>331.86</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>233.14</v>
+        <v>128.64</v>
       </c>
       <c r="K42" t="n">
-        <v>-275.23</v>
+        <v>-151.86</v>
       </c>
       <c r="L42" t="n">
-        <v>360.7</v>
+        <v>199.02</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>15.88</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-565.6900000000001</v>
+        <v>-315.8</v>
       </c>
       <c r="L43" t="n">
-        <v>565.91</v>
+        <v>315.93</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-85.25</v>
+        <v>-47.63</v>
       </c>
       <c r="K44" t="n">
-        <v>-90.55</v>
+        <v>-50.59</v>
       </c>
       <c r="L44" t="n">
-        <v>124.37</v>
+        <v>69.48</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>72</v>
+        <v>16.52</v>
       </c>
       <c r="K45" t="n">
-        <v>57.53</v>
+        <v>13.2</v>
       </c>
       <c r="L45" t="n">
-        <v>92.16</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>15.44</v>
+        <v>7.71</v>
       </c>
       <c r="K46" t="n">
-        <v>-128.24</v>
+        <v>-64.02</v>
       </c>
       <c r="L46" t="n">
-        <v>129.16</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-117.54</v>
+        <v>-60.68</v>
       </c>
       <c r="K47" t="n">
-        <v>-138.67</v>
+        <v>-71.58</v>
       </c>
       <c r="L47" t="n">
-        <v>181.78</v>
+        <v>93.84</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-190.94</v>
+        <v>-100.99</v>
       </c>
       <c r="K48" t="n">
-        <v>49.51</v>
+        <v>26.19</v>
       </c>
       <c r="L48" t="n">
-        <v>197.25</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-147.05</v>
+        <v>-82.06</v>
       </c>
       <c r="K49" t="n">
-        <v>120.44</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>190.07</v>
+        <v>106.08</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-23.96</v>
+        <v>-11.85</v>
       </c>
       <c r="K50" t="n">
-        <v>-370.9</v>
+        <v>-183.38</v>
       </c>
       <c r="L50" t="n">
-        <v>371.67</v>
+        <v>183.76</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-67.61</v>
+        <v>-34.79</v>
       </c>
       <c r="K51" t="n">
-        <v>-154.1</v>
+        <v>-79.3</v>
       </c>
       <c r="L51" t="n">
-        <v>168.28</v>
+        <v>86.59</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>378.24</v>
+        <v>195.41</v>
       </c>
       <c r="K52" t="n">
-        <v>203.6</v>
+        <v>105.19</v>
       </c>
       <c r="L52" t="n">
-        <v>429.56</v>
+        <v>221.92</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>89.25</v>
+        <v>51.99</v>
       </c>
       <c r="K53" t="n">
-        <v>199.38</v>
+        <v>116.13</v>
       </c>
       <c r="L53" t="n">
-        <v>218.45</v>
+        <v>127.24</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-324.47</v>
+        <v>-155.41</v>
       </c>
       <c r="K54" t="n">
-        <v>106.82</v>
+        <v>51.16</v>
       </c>
       <c r="L54" t="n">
-        <v>341.61</v>
+        <v>163.61</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>57.49</v>
+        <v>35.29</v>
       </c>
       <c r="K55" t="n">
-        <v>-414.73</v>
+        <v>-254.64</v>
       </c>
       <c r="L55" t="n">
-        <v>418.69</v>
+        <v>257.07</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>344.59</v>
+        <v>181.87</v>
       </c>
       <c r="K56" t="n">
-        <v>-238</v>
+        <v>-125.61</v>
       </c>
       <c r="L56" t="n">
-        <v>418.79</v>
+        <v>221.03</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>305.73</v>
+        <v>170.77</v>
       </c>
       <c r="K57" t="n">
-        <v>-368.91</v>
+        <v>-206.06</v>
       </c>
       <c r="L57" t="n">
-        <v>479.13</v>
+        <v>267.63</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>231.58</v>
+        <v>127.64</v>
       </c>
       <c r="K58" t="n">
-        <v>156.41</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>279.45</v>
+        <v>154.03</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>44.42</v>
+        <v>22.79</v>
       </c>
       <c r="K59" t="n">
-        <v>-126.33</v>
+        <v>-64.81</v>
       </c>
       <c r="L59" t="n">
-        <v>133.91</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>69.34</v>
+        <v>31.06</v>
       </c>
       <c r="K60" t="n">
-        <v>107.75</v>
+        <v>48.27</v>
       </c>
       <c r="L60" t="n">
-        <v>128.14</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.66</v>
+        <v>-9.08</v>
       </c>
       <c r="K61" t="n">
-        <v>-149.75</v>
+        <v>-77.02</v>
       </c>
       <c r="L61" t="n">
-        <v>150.79</v>
+        <v>77.55</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>417.83</v>
+        <v>193.99</v>
       </c>
       <c r="K62" t="n">
-        <v>173.23</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>452.31</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.59</v>
+        <v>-4.82</v>
       </c>
       <c r="K63" t="n">
-        <v>98.69</v>
+        <v>32.6</v>
       </c>
       <c r="L63" t="n">
-        <v>99.76000000000001</v>
+        <v>32.95</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-248.85</v>
+        <v>-127.64</v>
       </c>
       <c r="K64" t="n">
-        <v>-29.19</v>
+        <v>-14.97</v>
       </c>
       <c r="L64" t="n">
-        <v>250.55</v>
+        <v>128.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-26.49</v>
+        <v>-13.15</v>
       </c>
       <c r="K65" t="n">
-        <v>-295.26</v>
+        <v>-146.59</v>
       </c>
       <c r="L65" t="n">
-        <v>296.45</v>
+        <v>147.18</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>78.04000000000001</v>
+        <v>38.7</v>
       </c>
       <c r="K66" t="n">
-        <v>148.11</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>167.42</v>
+        <v>83.03</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>61.65</v>
+        <v>30.88</v>
       </c>
       <c r="K67" t="n">
-        <v>137.96</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>151.11</v>
+        <v>75.68000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-400.8</v>
+        <v>-213.11</v>
       </c>
       <c r="K68" t="n">
-        <v>-72.97</v>
+        <v>-38.8</v>
       </c>
       <c r="L68" t="n">
-        <v>407.39</v>
+        <v>216.61</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-368.77</v>
+        <v>-180.86</v>
       </c>
       <c r="K69" t="n">
-        <v>-80.44</v>
+        <v>-39.45</v>
       </c>
       <c r="L69" t="n">
-        <v>377.44</v>
+        <v>185.11</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-444.14</v>
+        <v>-253.97</v>
       </c>
       <c r="K70" t="n">
-        <v>-144.99</v>
+        <v>-82.91</v>
       </c>
       <c r="L70" t="n">
-        <v>467.21</v>
+        <v>267.16</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>145.3</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-339.53</v>
+        <v>-186.76</v>
       </c>
       <c r="L71" t="n">
-        <v>369.31</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>332.04</v>
+        <v>187.84</v>
       </c>
       <c r="K72" t="n">
-        <v>-227.95</v>
+        <v>-128.95</v>
       </c>
       <c r="L72" t="n">
-        <v>402.76</v>
+        <v>227.84</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-321.83</v>
+        <v>-187.11</v>
       </c>
       <c r="K73" t="n">
-        <v>247.78</v>
+        <v>144.06</v>
       </c>
       <c r="L73" t="n">
-        <v>406.16</v>
+        <v>236.14</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>132.76</v>
+        <v>65.64</v>
       </c>
       <c r="K74" t="n">
-        <v>71.52</v>
+        <v>35.36</v>
       </c>
       <c r="L74" t="n">
-        <v>150.8</v>
+        <v>74.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-105.63</v>
+        <v>-51.25</v>
       </c>
       <c r="K75" t="n">
-        <v>45.4</v>
+        <v>22.03</v>
       </c>
       <c r="L75" t="n">
-        <v>114.97</v>
+        <v>55.79</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>105.83</v>
+        <v>57.88</v>
       </c>
       <c r="K76" t="n">
-        <v>53.46</v>
+        <v>29.24</v>
       </c>
       <c r="L76" t="n">
-        <v>118.57</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>278.64</v>
+        <v>125.14</v>
       </c>
       <c r="K77" t="n">
-        <v>-26.15</v>
+        <v>-11.74</v>
       </c>
       <c r="L77" t="n">
-        <v>279.86</v>
+        <v>125.69</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-104.84</v>
+        <v>-58.41</v>
       </c>
       <c r="K78" t="n">
-        <v>87.47</v>
+        <v>48.73</v>
       </c>
       <c r="L78" t="n">
-        <v>136.54</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>184.76</v>
+        <v>99.3</v>
       </c>
       <c r="K79" t="n">
-        <v>-36.7</v>
+        <v>-19.72</v>
       </c>
       <c r="L79" t="n">
-        <v>188.37</v>
+        <v>101.24</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-269.77</v>
+        <v>-135.65</v>
       </c>
       <c r="K80" t="n">
-        <v>-31.66</v>
+        <v>-15.92</v>
       </c>
       <c r="L80" t="n">
-        <v>271.62</v>
+        <v>136.58</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>204.44</v>
+        <v>104.58</v>
       </c>
       <c r="K81" t="n">
-        <v>90.37</v>
+        <v>46.23</v>
       </c>
       <c r="L81" t="n">
-        <v>223.52</v>
+        <v>114.34</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>186.31</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-165.15</v>
+        <v>-82.67</v>
       </c>
       <c r="L82" t="n">
-        <v>248.97</v>
+        <v>124.63</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>191.14</v>
+        <v>95.16</v>
       </c>
       <c r="K83" t="n">
-        <v>161.98</v>
+        <v>80.64</v>
       </c>
       <c r="L83" t="n">
-        <v>250.55</v>
+        <v>124.74</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-253.29</v>
+        <v>-124.69</v>
       </c>
       <c r="K84" t="n">
-        <v>-74.76000000000001</v>
+        <v>-36.8</v>
       </c>
       <c r="L84" t="n">
-        <v>264.1</v>
+        <v>130.01</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>39.25</v>
+        <v>20.96</v>
       </c>
       <c r="K85" t="n">
-        <v>-237.83</v>
+        <v>-126.99</v>
       </c>
       <c r="L85" t="n">
-        <v>241.04</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-381.37</v>
+        <v>-206.78</v>
       </c>
       <c r="K86" t="n">
-        <v>223.1</v>
+        <v>120.97</v>
       </c>
       <c r="L86" t="n">
-        <v>441.84</v>
+        <v>239.57</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>305.35</v>
+        <v>173.44</v>
       </c>
       <c r="K87" t="n">
-        <v>-285.97</v>
+        <v>-162.43</v>
       </c>
       <c r="L87" t="n">
-        <v>418.35</v>
+        <v>237.62</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-85.5</v>
+        <v>-48.88</v>
       </c>
       <c r="K88" t="n">
-        <v>574.11</v>
+        <v>328.24</v>
       </c>
       <c r="L88" t="n">
-        <v>580.4400000000001</v>
+        <v>331.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="K14" t="n">
-        <v>-35.08</v>
+        <v>-38.16</v>
       </c>
       <c r="L14" t="n">
-        <v>35.09</v>
+        <v>38.17</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.53</v>
+        <v>-1.54</v>
       </c>
       <c r="K15" t="n">
-        <v>-73.31999999999999</v>
+        <v>-73.53</v>
       </c>
       <c r="L15" t="n">
-        <v>73.34</v>
+        <v>73.55</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-37.97</v>
+        <v>-39.29</v>
       </c>
       <c r="K16" t="n">
-        <v>-33.13</v>
+        <v>-34.29</v>
       </c>
       <c r="L16" t="n">
-        <v>50.39</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>25.22</v>
+        <v>24.32</v>
       </c>
       <c r="K17" t="n">
-        <v>111.25</v>
+        <v>107.3</v>
       </c>
       <c r="L17" t="n">
-        <v>114.08</v>
+        <v>110.02</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>92.17</v>
+        <v>90.14</v>
       </c>
       <c r="K18" t="n">
-        <v>-59.19</v>
+        <v>-57.88</v>
       </c>
       <c r="L18" t="n">
-        <v>109.54</v>
+        <v>107.12</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>81.90000000000001</v>
+        <v>81.86</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.27</v>
+        <v>-9.26</v>
       </c>
       <c r="L19" t="n">
-        <v>82.43000000000001</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.48</v>
+        <v>-16.55</v>
       </c>
       <c r="K20" t="n">
-        <v>-109.52</v>
+        <v>-110</v>
       </c>
       <c r="L20" t="n">
-        <v>110.76</v>
+        <v>111.23</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-118.34</v>
+        <v>-113.04</v>
       </c>
       <c r="K21" t="n">
-        <v>156.29</v>
+        <v>149.29</v>
       </c>
       <c r="L21" t="n">
-        <v>196.04</v>
+        <v>187.26</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-109.72</v>
+        <v>-107.21</v>
       </c>
       <c r="K22" t="n">
-        <v>108.5</v>
+        <v>106.01</v>
       </c>
       <c r="L22" t="n">
-        <v>154.31</v>
+        <v>150.77</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-92.28</v>
+        <v>-97.97</v>
       </c>
       <c r="K23" t="n">
-        <v>44.67</v>
+        <v>47.43</v>
       </c>
       <c r="L23" t="n">
-        <v>102.52</v>
+        <v>108.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>16.77</v>
+        <v>17.66</v>
       </c>
       <c r="K24" t="n">
-        <v>-108.06</v>
+        <v>-113.83</v>
       </c>
       <c r="L24" t="n">
-        <v>109.35</v>
+        <v>115.19</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-203.67</v>
+        <v>-200.34</v>
       </c>
       <c r="K25" t="n">
-        <v>78.53</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>218.28</v>
+        <v>214.71</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>115.52</v>
+        <v>112.55</v>
       </c>
       <c r="K26" t="n">
-        <v>-257.31</v>
+        <v>-250.7</v>
       </c>
       <c r="L26" t="n">
-        <v>282.05</v>
+        <v>274.81</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-11.91</v>
+        <v>-13.05</v>
       </c>
       <c r="K27" t="n">
-        <v>-121.26</v>
+        <v>-132.89</v>
       </c>
       <c r="L27" t="n">
-        <v>121.84</v>
+        <v>133.53</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-146.46</v>
+        <v>-156.23</v>
       </c>
       <c r="K28" t="n">
-        <v>-19.91</v>
+        <v>-21.24</v>
       </c>
       <c r="L28" t="n">
-        <v>147.8</v>
+        <v>157.67</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>58.93</v>
+        <v>58.15</v>
       </c>
       <c r="K29" t="n">
-        <v>-50.45</v>
+        <v>-49.78</v>
       </c>
       <c r="L29" t="n">
-        <v>77.56999999999999</v>
+        <v>76.55</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>49.35</v>
+        <v>49.23</v>
       </c>
       <c r="K30" t="n">
-        <v>57.46</v>
+        <v>57.31</v>
       </c>
       <c r="L30" t="n">
-        <v>75.73999999999999</v>
+        <v>75.55</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="K31" t="n">
-        <v>66.48999999999999</v>
+        <v>66.47</v>
       </c>
       <c r="L31" t="n">
-        <v>67.63</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>32.71</v>
+        <v>32.89</v>
       </c>
       <c r="K32" t="n">
-        <v>-80.90000000000001</v>
+        <v>-81.34999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>87.27</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>60.06</v>
+        <v>60.53</v>
       </c>
       <c r="K33" t="n">
-        <v>48.34</v>
+        <v>48.73</v>
       </c>
       <c r="L33" t="n">
-        <v>77.09999999999999</v>
+        <v>77.70999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-56.51</v>
+        <v>-59.85</v>
       </c>
       <c r="K34" t="n">
-        <v>-20.62</v>
+        <v>-21.84</v>
       </c>
       <c r="L34" t="n">
-        <v>60.16</v>
+        <v>63.71</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-131.5</v>
+        <v>-127.15</v>
       </c>
       <c r="K35" t="n">
-        <v>115.72</v>
+        <v>111.88</v>
       </c>
       <c r="L35" t="n">
-        <v>175.17</v>
+        <v>169.36</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-145.07</v>
+        <v>-138.57</v>
       </c>
       <c r="K36" t="n">
-        <v>-138.77</v>
+        <v>-132.55</v>
       </c>
       <c r="L36" t="n">
-        <v>200.76</v>
+        <v>191.76</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>20.57</v>
+        <v>20.18</v>
       </c>
       <c r="K37" t="n">
-        <v>-15.22</v>
+        <v>-14.93</v>
       </c>
       <c r="L37" t="n">
-        <v>25.59</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-13.06</v>
+        <v>-13.61</v>
       </c>
       <c r="K38" t="n">
-        <v>-137.84</v>
+        <v>-143.72</v>
       </c>
       <c r="L38" t="n">
-        <v>138.46</v>
+        <v>144.36</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-223.76</v>
+        <v>-216.95</v>
       </c>
       <c r="K39" t="n">
-        <v>-92.13</v>
+        <v>-89.31999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>241.99</v>
+        <v>234.62</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-108.04</v>
+        <v>-112.03</v>
       </c>
       <c r="K40" t="n">
-        <v>-105.71</v>
+        <v>-109.61</v>
       </c>
       <c r="L40" t="n">
-        <v>151.15</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>301.42</v>
+        <v>290.29</v>
       </c>
       <c r="K41" t="n">
-        <v>138.85</v>
+        <v>133.72</v>
       </c>
       <c r="L41" t="n">
-        <v>331.86</v>
+        <v>319.61</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>128.64</v>
+        <v>136.52</v>
       </c>
       <c r="K42" t="n">
-        <v>-151.86</v>
+        <v>-161.16</v>
       </c>
       <c r="L42" t="n">
-        <v>199.02</v>
+        <v>211.21</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>8.869999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="K43" t="n">
-        <v>-315.8</v>
+        <v>-311.14</v>
       </c>
       <c r="L43" t="n">
-        <v>315.93</v>
+        <v>311.26</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-47.63</v>
+        <v>-48.2</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.59</v>
+        <v>-51.2</v>
       </c>
       <c r="L44" t="n">
-        <v>69.48</v>
+        <v>70.31999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>16.52</v>
+        <v>15.75</v>
       </c>
       <c r="K45" t="n">
-        <v>13.2</v>
+        <v>12.58</v>
       </c>
       <c r="L45" t="n">
-        <v>21.14</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>7.71</v>
+        <v>7.89</v>
       </c>
       <c r="K46" t="n">
-        <v>-64.02</v>
+        <v>-65.48999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>64.48</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-60.68</v>
+        <v>-59.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-71.58</v>
+        <v>-70.69</v>
       </c>
       <c r="L47" t="n">
-        <v>93.84</v>
+        <v>92.67</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-100.99</v>
+        <v>-99.34</v>
       </c>
       <c r="K48" t="n">
-        <v>26.19</v>
+        <v>25.76</v>
       </c>
       <c r="L48" t="n">
-        <v>104.33</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-82.06</v>
+        <v>-80.73</v>
       </c>
       <c r="K49" t="n">
-        <v>67.20999999999999</v>
+        <v>66.12</v>
       </c>
       <c r="L49" t="n">
-        <v>106.08</v>
+        <v>104.36</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.85</v>
+        <v>-11.41</v>
       </c>
       <c r="K50" t="n">
-        <v>-183.38</v>
+        <v>-176.65</v>
       </c>
       <c r="L50" t="n">
-        <v>183.76</v>
+        <v>177.02</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-34.79</v>
+        <v>-36.56</v>
       </c>
       <c r="K51" t="n">
-        <v>-79.3</v>
+        <v>-83.34</v>
       </c>
       <c r="L51" t="n">
-        <v>86.59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>195.41</v>
+        <v>184.26</v>
       </c>
       <c r="K52" t="n">
-        <v>105.19</v>
+        <v>99.19</v>
       </c>
       <c r="L52" t="n">
-        <v>221.92</v>
+        <v>209.26</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>51.99</v>
+        <v>54.77</v>
       </c>
       <c r="K53" t="n">
-        <v>116.13</v>
+        <v>122.34</v>
       </c>
       <c r="L53" t="n">
-        <v>127.24</v>
+        <v>134.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-155.41</v>
+        <v>-159.58</v>
       </c>
       <c r="K54" t="n">
-        <v>51.16</v>
+        <v>52.53</v>
       </c>
       <c r="L54" t="n">
-        <v>163.61</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>35.29</v>
+        <v>33.87</v>
       </c>
       <c r="K55" t="n">
-        <v>-254.64</v>
+        <v>-244.39</v>
       </c>
       <c r="L55" t="n">
-        <v>257.07</v>
+        <v>246.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>181.87</v>
+        <v>213.39</v>
       </c>
       <c r="K56" t="n">
-        <v>-125.61</v>
+        <v>-147.39</v>
       </c>
       <c r="L56" t="n">
-        <v>221.03</v>
+        <v>259.34</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>170.77</v>
+        <v>171.91</v>
       </c>
       <c r="K57" t="n">
-        <v>-206.06</v>
+        <v>-207.43</v>
       </c>
       <c r="L57" t="n">
-        <v>267.63</v>
+        <v>269.41</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>127.64</v>
+        <v>142.66</v>
       </c>
       <c r="K58" t="n">
-        <v>86.20999999999999</v>
+        <v>96.36</v>
       </c>
       <c r="L58" t="n">
-        <v>154.03</v>
+        <v>172.16</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>22.79</v>
+        <v>22.87</v>
       </c>
       <c r="K59" t="n">
-        <v>-64.81</v>
+        <v>-65.06</v>
       </c>
       <c r="L59" t="n">
-        <v>68.7</v>
+        <v>68.97</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>31.06</v>
+        <v>31.45</v>
       </c>
       <c r="K60" t="n">
-        <v>48.27</v>
+        <v>48.86</v>
       </c>
       <c r="L60" t="n">
-        <v>57.4</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.08</v>
+        <v>-9.02</v>
       </c>
       <c r="K61" t="n">
-        <v>-77.02</v>
+        <v>-76.52</v>
       </c>
       <c r="L61" t="n">
-        <v>77.55</v>
+        <v>77.05</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>193.99</v>
+        <v>167.29</v>
       </c>
       <c r="K62" t="n">
-        <v>80.43000000000001</v>
+        <v>69.36</v>
       </c>
       <c r="L62" t="n">
-        <v>210</v>
+        <v>181.1</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.82</v>
+        <v>-4.61</v>
       </c>
       <c r="K63" t="n">
-        <v>32.6</v>
+        <v>31.16</v>
       </c>
       <c r="L63" t="n">
-        <v>32.95</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-127.64</v>
+        <v>-122.35</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.97</v>
+        <v>-14.35</v>
       </c>
       <c r="L64" t="n">
-        <v>128.51</v>
+        <v>123.19</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-13.15</v>
+        <v>-12.95</v>
       </c>
       <c r="K65" t="n">
-        <v>-146.59</v>
+        <v>-144.31</v>
       </c>
       <c r="L65" t="n">
-        <v>147.18</v>
+        <v>144.89</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>38.7</v>
+        <v>41.22</v>
       </c>
       <c r="K66" t="n">
-        <v>73.45999999999999</v>
+        <v>78.23</v>
       </c>
       <c r="L66" t="n">
-        <v>83.03</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>30.88</v>
+        <v>33.08</v>
       </c>
       <c r="K67" t="n">
-        <v>69.09999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>75.68000000000001</v>
+        <v>81.09</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-213.11</v>
+        <v>-208.37</v>
       </c>
       <c r="K68" t="n">
-        <v>-38.8</v>
+        <v>-37.94</v>
       </c>
       <c r="L68" t="n">
-        <v>216.61</v>
+        <v>211.79</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-180.86</v>
+        <v>-180.68</v>
       </c>
       <c r="K69" t="n">
-        <v>-39.45</v>
+        <v>-39.41</v>
       </c>
       <c r="L69" t="n">
-        <v>185.11</v>
+        <v>184.93</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-253.97</v>
+        <v>-243.3</v>
       </c>
       <c r="K70" t="n">
-        <v>-82.91</v>
+        <v>-79.42</v>
       </c>
       <c r="L70" t="n">
-        <v>267.16</v>
+        <v>255.93</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>79.93000000000001</v>
+        <v>84.98</v>
       </c>
       <c r="K71" t="n">
-        <v>-186.76</v>
+        <v>-198.58</v>
       </c>
       <c r="L71" t="n">
-        <v>203.15</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>187.84</v>
+        <v>188.7</v>
       </c>
       <c r="K72" t="n">
-        <v>-128.95</v>
+        <v>-129.54</v>
       </c>
       <c r="L72" t="n">
-        <v>227.84</v>
+        <v>228.88</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-187.11</v>
+        <v>-185.4</v>
       </c>
       <c r="K73" t="n">
-        <v>144.06</v>
+        <v>142.75</v>
       </c>
       <c r="L73" t="n">
-        <v>236.14</v>
+        <v>233.99</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>65.64</v>
+        <v>64.88</v>
       </c>
       <c r="K74" t="n">
-        <v>35.36</v>
+        <v>34.95</v>
       </c>
       <c r="L74" t="n">
-        <v>74.56</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-51.25</v>
+        <v>-52.53</v>
       </c>
       <c r="K75" t="n">
-        <v>22.03</v>
+        <v>22.57</v>
       </c>
       <c r="L75" t="n">
-        <v>55.79</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>57.88</v>
+        <v>58.33</v>
       </c>
       <c r="K76" t="n">
-        <v>29.24</v>
+        <v>29.46</v>
       </c>
       <c r="L76" t="n">
-        <v>64.84999999999999</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>125.14</v>
+        <v>117.83</v>
       </c>
       <c r="K77" t="n">
-        <v>-11.74</v>
+        <v>-11.06</v>
       </c>
       <c r="L77" t="n">
-        <v>125.69</v>
+        <v>118.35</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-58.41</v>
+        <v>-59.48</v>
       </c>
       <c r="K78" t="n">
-        <v>48.73</v>
+        <v>49.62</v>
       </c>
       <c r="L78" t="n">
-        <v>76.06</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>99.3</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-19.72</v>
+        <v>-19.24</v>
       </c>
       <c r="L79" t="n">
-        <v>101.24</v>
+        <v>98.73999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-135.65</v>
+        <v>-133.7</v>
       </c>
       <c r="K80" t="n">
-        <v>-15.92</v>
+        <v>-15.69</v>
       </c>
       <c r="L80" t="n">
-        <v>136.58</v>
+        <v>134.62</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>104.58</v>
+        <v>105.23</v>
       </c>
       <c r="K81" t="n">
-        <v>46.23</v>
+        <v>46.51</v>
       </c>
       <c r="L81" t="n">
-        <v>114.34</v>
+        <v>115.05</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>93.26000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-82.67</v>
+        <v>-83.23</v>
       </c>
       <c r="L82" t="n">
-        <v>124.63</v>
+        <v>125.48</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>95.16</v>
+        <v>100.48</v>
       </c>
       <c r="K83" t="n">
-        <v>80.64</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>124.74</v>
+        <v>131.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-124.69</v>
+        <v>-131.15</v>
       </c>
       <c r="K84" t="n">
-        <v>-36.8</v>
+        <v>-38.71</v>
       </c>
       <c r="L84" t="n">
-        <v>130.01</v>
+        <v>136.74</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>20.96</v>
+        <v>21.71</v>
       </c>
       <c r="K85" t="n">
-        <v>-126.99</v>
+        <v>-131.53</v>
       </c>
       <c r="L85" t="n">
-        <v>128.7</v>
+        <v>133.31</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-206.78</v>
+        <v>-217.21</v>
       </c>
       <c r="K86" t="n">
-        <v>120.97</v>
+        <v>127.06</v>
       </c>
       <c r="L86" t="n">
-        <v>239.57</v>
+        <v>251.64</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>173.44</v>
+        <v>171.7</v>
       </c>
       <c r="K87" t="n">
-        <v>-162.43</v>
+        <v>-160.8</v>
       </c>
       <c r="L87" t="n">
-        <v>237.62</v>
+        <v>235.24</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-48.88</v>
+        <v>-46.89</v>
       </c>
       <c r="K88" t="n">
-        <v>328.24</v>
+        <v>314.88</v>
       </c>
       <c r="L88" t="n">
-        <v>331.86</v>
+        <v>318.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>-38.16</v>
+        <v>-41.67</v>
       </c>
       <c r="L14" t="n">
-        <v>38.17</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="15">
@@ -685,10 +685,10 @@
         <v>-1.54</v>
       </c>
       <c r="K15" t="n">
-        <v>-73.53</v>
+        <v>-73.95</v>
       </c>
       <c r="L15" t="n">
-        <v>73.55</v>
+        <v>73.95999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-39.29</v>
+        <v>-40.81</v>
       </c>
       <c r="K16" t="n">
-        <v>-34.29</v>
+        <v>-35.61</v>
       </c>
       <c r="L16" t="n">
-        <v>52.15</v>
+        <v>54.16</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>24.32</v>
+        <v>23.29</v>
       </c>
       <c r="K17" t="n">
-        <v>107.3</v>
+        <v>102.78</v>
       </c>
       <c r="L17" t="n">
-        <v>110.02</v>
+        <v>105.38</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>90.14</v>
+        <v>87.81</v>
       </c>
       <c r="K18" t="n">
-        <v>-57.88</v>
+        <v>-56.39</v>
       </c>
       <c r="L18" t="n">
-        <v>107.12</v>
+        <v>104.36</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>81.86</v>
+        <v>82.19</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.26</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>82.38</v>
+        <v>82.70999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.55</v>
+        <v>-16.64</v>
       </c>
       <c r="K20" t="n">
-        <v>-110</v>
+        <v>-110.54</v>
       </c>
       <c r="L20" t="n">
-        <v>111.23</v>
+        <v>111.78</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-113.04</v>
+        <v>-107.94</v>
       </c>
       <c r="K21" t="n">
-        <v>149.29</v>
+        <v>142.55</v>
       </c>
       <c r="L21" t="n">
-        <v>187.26</v>
+        <v>178.81</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-107.21</v>
+        <v>-104.33</v>
       </c>
       <c r="K22" t="n">
-        <v>106.01</v>
+        <v>103.17</v>
       </c>
       <c r="L22" t="n">
-        <v>150.77</v>
+        <v>146.73</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-97.97</v>
+        <v>-104.49</v>
       </c>
       <c r="K23" t="n">
-        <v>47.43</v>
+        <v>50.58</v>
       </c>
       <c r="L23" t="n">
-        <v>108.85</v>
+        <v>116.09</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>17.66</v>
+        <v>18.69</v>
       </c>
       <c r="K24" t="n">
-        <v>-113.83</v>
+        <v>-120.43</v>
       </c>
       <c r="L24" t="n">
-        <v>115.19</v>
+        <v>121.87</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-200.34</v>
+        <v>-194.73</v>
       </c>
       <c r="K25" t="n">
-        <v>77.23999999999999</v>
+        <v>75.08</v>
       </c>
       <c r="L25" t="n">
-        <v>214.71</v>
+        <v>208.7</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>112.55</v>
+        <v>109.16</v>
       </c>
       <c r="K26" t="n">
-        <v>-250.7</v>
+        <v>-243.14</v>
       </c>
       <c r="L26" t="n">
-        <v>274.81</v>
+        <v>266.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-13.05</v>
+        <v>-14.36</v>
       </c>
       <c r="K27" t="n">
-        <v>-132.89</v>
+        <v>-146.18</v>
       </c>
       <c r="L27" t="n">
-        <v>133.53</v>
+        <v>146.88</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-156.23</v>
+        <v>-167.4</v>
       </c>
       <c r="K28" t="n">
-        <v>-21.24</v>
+        <v>-22.76</v>
       </c>
       <c r="L28" t="n">
-        <v>157.67</v>
+        <v>168.94</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>58.15</v>
+        <v>57.26</v>
       </c>
       <c r="K29" t="n">
-        <v>-49.78</v>
+        <v>-49.02</v>
       </c>
       <c r="L29" t="n">
-        <v>76.55</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>49.23</v>
+        <v>49.31</v>
       </c>
       <c r="K30" t="n">
-        <v>57.31</v>
+        <v>57.41</v>
       </c>
       <c r="L30" t="n">
-        <v>75.55</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="31">
@@ -1357,10 +1357,10 @@
         <v>12.33</v>
       </c>
       <c r="K31" t="n">
-        <v>66.47</v>
+        <v>66.44</v>
       </c>
       <c r="L31" t="n">
-        <v>67.59999999999999</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>32.89</v>
+        <v>33.1</v>
       </c>
       <c r="K32" t="n">
-        <v>-81.34999999999999</v>
+        <v>-81.86</v>
       </c>
       <c r="L32" t="n">
-        <v>87.75</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>60.53</v>
+        <v>62.18</v>
       </c>
       <c r="K33" t="n">
-        <v>48.73</v>
+        <v>50.05</v>
       </c>
       <c r="L33" t="n">
-        <v>77.70999999999999</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-59.85</v>
+        <v>-63.67</v>
       </c>
       <c r="K34" t="n">
-        <v>-21.84</v>
+        <v>-23.24</v>
       </c>
       <c r="L34" t="n">
-        <v>63.71</v>
+        <v>67.78</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-127.15</v>
+        <v>-123.12</v>
       </c>
       <c r="K35" t="n">
-        <v>111.88</v>
+        <v>108.34</v>
       </c>
       <c r="L35" t="n">
-        <v>169.36</v>
+        <v>164.01</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-138.57</v>
+        <v>-131.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-132.55</v>
+        <v>-125.52</v>
       </c>
       <c r="L36" t="n">
-        <v>191.76</v>
+        <v>181.59</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>20.18</v>
+        <v>21.74</v>
       </c>
       <c r="K37" t="n">
-        <v>-14.93</v>
+        <v>-16.08</v>
       </c>
       <c r="L37" t="n">
-        <v>25.1</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-13.61</v>
+        <v>-14.23</v>
       </c>
       <c r="K38" t="n">
-        <v>-143.72</v>
+        <v>-150.26</v>
       </c>
       <c r="L38" t="n">
-        <v>144.36</v>
+        <v>150.93</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-216.95</v>
+        <v>-209.17</v>
       </c>
       <c r="K39" t="n">
-        <v>-89.31999999999999</v>
+        <v>-86.12</v>
       </c>
       <c r="L39" t="n">
-        <v>234.62</v>
+        <v>226.21</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-112.03</v>
+        <v>-115.64</v>
       </c>
       <c r="K40" t="n">
-        <v>-109.61</v>
+        <v>-113.14</v>
       </c>
       <c r="L40" t="n">
-        <v>156.73</v>
+        <v>161.78</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>290.29</v>
+        <v>277.58</v>
       </c>
       <c r="K41" t="n">
-        <v>133.72</v>
+        <v>127.87</v>
       </c>
       <c r="L41" t="n">
-        <v>319.61</v>
+        <v>305.61</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>136.52</v>
+        <v>141.86</v>
       </c>
       <c r="K42" t="n">
-        <v>-161.16</v>
+        <v>-167.47</v>
       </c>
       <c r="L42" t="n">
-        <v>211.21</v>
+        <v>219.48</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>8.74</v>
+        <v>8.44</v>
       </c>
       <c r="K43" t="n">
-        <v>-311.14</v>
+        <v>-300.64</v>
       </c>
       <c r="L43" t="n">
-        <v>311.26</v>
+        <v>300.76</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.2</v>
+        <v>-48.86</v>
       </c>
       <c r="K44" t="n">
-        <v>-51.2</v>
+        <v>-51.9</v>
       </c>
       <c r="L44" t="n">
-        <v>70.31999999999999</v>
+        <v>71.28</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>15.75</v>
+        <v>17.02</v>
       </c>
       <c r="K45" t="n">
-        <v>12.58</v>
+        <v>13.6</v>
       </c>
       <c r="L45" t="n">
-        <v>20.16</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>7.89</v>
+        <v>8.18</v>
       </c>
       <c r="K46" t="n">
-        <v>-65.48999999999999</v>
+        <v>-67.92</v>
       </c>
       <c r="L46" t="n">
-        <v>65.97</v>
+        <v>68.41</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-59.92</v>
+        <v>-59.48</v>
       </c>
       <c r="K47" t="n">
-        <v>-70.69</v>
+        <v>-70.17</v>
       </c>
       <c r="L47" t="n">
-        <v>92.67</v>
+        <v>91.98999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-99.34</v>
+        <v>-97.77</v>
       </c>
       <c r="K48" t="n">
-        <v>25.76</v>
+        <v>25.35</v>
       </c>
       <c r="L48" t="n">
-        <v>102.62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-80.73</v>
+        <v>-79.20999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>66.12</v>
+        <v>64.88</v>
       </c>
       <c r="L49" t="n">
-        <v>104.36</v>
+        <v>102.39</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.41</v>
+        <v>-11.02</v>
       </c>
       <c r="K50" t="n">
-        <v>-176.65</v>
+        <v>-170.51</v>
       </c>
       <c r="L50" t="n">
-        <v>177.02</v>
+        <v>170.87</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-36.56</v>
+        <v>-38.6</v>
       </c>
       <c r="K51" t="n">
-        <v>-83.34</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>91</v>
+        <v>96.08</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>184.26</v>
+        <v>171.53</v>
       </c>
       <c r="K52" t="n">
-        <v>99.19</v>
+        <v>92.33</v>
       </c>
       <c r="L52" t="n">
-        <v>209.26</v>
+        <v>194.8</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>54.77</v>
+        <v>57.94</v>
       </c>
       <c r="K53" t="n">
-        <v>122.34</v>
+        <v>129.43</v>
       </c>
       <c r="L53" t="n">
-        <v>134.04</v>
+        <v>141.81</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-159.58</v>
+        <v>-163.19</v>
       </c>
       <c r="K54" t="n">
-        <v>52.53</v>
+        <v>53.72</v>
       </c>
       <c r="L54" t="n">
-        <v>168</v>
+        <v>171.8</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>33.87</v>
+        <v>32.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-244.39</v>
+        <v>-232.68</v>
       </c>
       <c r="L55" t="n">
-        <v>246.73</v>
+        <v>234.91</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>213.39</v>
+        <v>225.38</v>
       </c>
       <c r="K56" t="n">
-        <v>-147.39</v>
+        <v>-155.67</v>
       </c>
       <c r="L56" t="n">
-        <v>259.34</v>
+        <v>273.92</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>171.91</v>
+        <v>170.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-207.43</v>
+        <v>-205.76</v>
       </c>
       <c r="L57" t="n">
-        <v>269.41</v>
+        <v>267.23</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>142.66</v>
+        <v>156.1</v>
       </c>
       <c r="K58" t="n">
-        <v>96.36</v>
+        <v>105.43</v>
       </c>
       <c r="L58" t="n">
-        <v>172.16</v>
+        <v>188.37</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>22.87</v>
+        <v>23.16</v>
       </c>
       <c r="K59" t="n">
-        <v>-65.06</v>
+        <v>-65.86</v>
       </c>
       <c r="L59" t="n">
-        <v>68.97</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>31.45</v>
+        <v>32.71</v>
       </c>
       <c r="K60" t="n">
-        <v>48.86</v>
+        <v>50.83</v>
       </c>
       <c r="L60" t="n">
-        <v>58.11</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="61">
@@ -2617,10 +2617,10 @@
         <v>-9.02</v>
       </c>
       <c r="K61" t="n">
-        <v>-76.52</v>
+        <v>-76.53</v>
       </c>
       <c r="L61" t="n">
-        <v>77.05</v>
+        <v>77.06</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>167.29</v>
+        <v>156.06</v>
       </c>
       <c r="K62" t="n">
-        <v>69.36</v>
+        <v>64.7</v>
       </c>
       <c r="L62" t="n">
-        <v>181.1</v>
+        <v>168.94</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.61</v>
+        <v>-5.02</v>
       </c>
       <c r="K63" t="n">
-        <v>31.16</v>
+        <v>33.94</v>
       </c>
       <c r="L63" t="n">
-        <v>31.5</v>
+        <v>34.31</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-122.35</v>
+        <v>-117.33</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.35</v>
+        <v>-13.76</v>
       </c>
       <c r="L64" t="n">
-        <v>123.19</v>
+        <v>118.13</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.95</v>
+        <v>-12.81</v>
       </c>
       <c r="K65" t="n">
-        <v>-144.31</v>
+        <v>-142.81</v>
       </c>
       <c r="L65" t="n">
-        <v>144.89</v>
+        <v>143.38</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>41.22</v>
+        <v>44.39</v>
       </c>
       <c r="K66" t="n">
-        <v>78.23</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>88.42</v>
+        <v>95.22</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>33.08</v>
+        <v>35.78</v>
       </c>
       <c r="K67" t="n">
-        <v>74.04000000000001</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>81.09</v>
+        <v>87.70999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-208.37</v>
+        <v>-202.27</v>
       </c>
       <c r="K68" t="n">
-        <v>-37.94</v>
+        <v>-36.83</v>
       </c>
       <c r="L68" t="n">
-        <v>211.79</v>
+        <v>205.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-180.68</v>
+        <v>-179.31</v>
       </c>
       <c r="K69" t="n">
-        <v>-39.41</v>
+        <v>-39.11</v>
       </c>
       <c r="L69" t="n">
-        <v>184.93</v>
+        <v>183.53</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-243.3</v>
+        <v>-230.98</v>
       </c>
       <c r="K70" t="n">
-        <v>-79.42</v>
+        <v>-75.40000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>255.93</v>
+        <v>242.98</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>84.98</v>
+        <v>88.23</v>
       </c>
       <c r="K71" t="n">
-        <v>-198.58</v>
+        <v>-206.16</v>
       </c>
       <c r="L71" t="n">
-        <v>216</v>
+        <v>224.25</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>188.7</v>
+        <v>189.21</v>
       </c>
       <c r="K72" t="n">
-        <v>-129.54</v>
+        <v>-129.9</v>
       </c>
       <c r="L72" t="n">
-        <v>228.88</v>
+        <v>229.51</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-185.4</v>
+        <v>-183.46</v>
       </c>
       <c r="K73" t="n">
-        <v>142.75</v>
+        <v>141.25</v>
       </c>
       <c r="L73" t="n">
-        <v>233.99</v>
+        <v>231.53</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>64.88</v>
+        <v>64.86</v>
       </c>
       <c r="K74" t="n">
-        <v>34.95</v>
+        <v>34.94</v>
       </c>
       <c r="L74" t="n">
-        <v>73.7</v>
+        <v>73.67</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-52.53</v>
+        <v>-54.76</v>
       </c>
       <c r="K75" t="n">
-        <v>22.57</v>
+        <v>23.54</v>
       </c>
       <c r="L75" t="n">
-        <v>57.17</v>
+        <v>59.61</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>58.33</v>
+        <v>58.85</v>
       </c>
       <c r="K76" t="n">
-        <v>29.46</v>
+        <v>29.72</v>
       </c>
       <c r="L76" t="n">
-        <v>65.34999999999999</v>
+        <v>65.93000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>117.83</v>
+        <v>113.32</v>
       </c>
       <c r="K77" t="n">
-        <v>-11.06</v>
+        <v>-10.64</v>
       </c>
       <c r="L77" t="n">
-        <v>118.35</v>
+        <v>113.82</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-59.48</v>
+        <v>-60.7</v>
       </c>
       <c r="K78" t="n">
-        <v>49.62</v>
+        <v>50.64</v>
       </c>
       <c r="L78" t="n">
-        <v>77.45</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>96.84999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="K79" t="n">
-        <v>-19.24</v>
+        <v>-18.69</v>
       </c>
       <c r="L79" t="n">
-        <v>98.73999999999999</v>
+        <v>95.95999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-133.7</v>
+        <v>-132.15</v>
       </c>
       <c r="K80" t="n">
-        <v>-15.69</v>
+        <v>-15.51</v>
       </c>
       <c r="L80" t="n">
-        <v>134.62</v>
+        <v>133.06</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>105.23</v>
+        <v>106.14</v>
       </c>
       <c r="K81" t="n">
-        <v>46.51</v>
+        <v>46.92</v>
       </c>
       <c r="L81" t="n">
-        <v>115.05</v>
+        <v>116.05</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>93.90000000000001</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-83.23</v>
+        <v>-84.37</v>
       </c>
       <c r="L82" t="n">
-        <v>125.48</v>
+        <v>127.19</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>100.48</v>
+        <v>106.02</v>
       </c>
       <c r="K83" t="n">
-        <v>85.15000000000001</v>
+        <v>89.84</v>
       </c>
       <c r="L83" t="n">
-        <v>131.71</v>
+        <v>138.97</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-131.15</v>
+        <v>-137.75</v>
       </c>
       <c r="K84" t="n">
-        <v>-38.71</v>
+        <v>-40.66</v>
       </c>
       <c r="L84" t="n">
-        <v>136.74</v>
+        <v>143.62</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>21.71</v>
+        <v>22.5</v>
       </c>
       <c r="K85" t="n">
-        <v>-131.53</v>
+        <v>-136.35</v>
       </c>
       <c r="L85" t="n">
-        <v>133.31</v>
+        <v>138.19</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-217.21</v>
+        <v>-219.34</v>
       </c>
       <c r="K86" t="n">
-        <v>127.06</v>
+        <v>128.31</v>
       </c>
       <c r="L86" t="n">
-        <v>251.64</v>
+        <v>254.11</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>171.7</v>
+        <v>169.71</v>
       </c>
       <c r="K87" t="n">
-        <v>-160.8</v>
+        <v>-158.94</v>
       </c>
       <c r="L87" t="n">
-        <v>235.24</v>
+        <v>232.52</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-46.89</v>
+        <v>-44.62</v>
       </c>
       <c r="K88" t="n">
-        <v>314.88</v>
+        <v>299.6</v>
       </c>
       <c r="L88" t="n">
-        <v>318.35</v>
+        <v>302.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -628,25 +628,25 @@
         <v>2.37</v>
       </c>
       <c r="F14" t="n">
-        <v>11.29</v>
+        <v>5.74</v>
       </c>
       <c r="G14" t="n">
-        <v>229.7</v>
+        <v>216</v>
       </c>
       <c r="H14" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>-41.67</v>
+        <v>-48.5</v>
       </c>
       <c r="L14" t="n">
-        <v>41.68</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>3.32</v>
       </c>
       <c r="F15" t="n">
-        <v>10.59</v>
+        <v>9.31</v>
       </c>
       <c r="G15" t="n">
-        <v>210.7</v>
+        <v>202</v>
       </c>
       <c r="H15" t="n">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.54</v>
+        <v>-1.91</v>
       </c>
       <c r="K15" t="n">
-        <v>-73.95</v>
+        <v>-81.34999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>73.95999999999999</v>
+        <v>81.37</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>2.57</v>
       </c>
       <c r="F16" t="n">
-        <v>11.35</v>
+        <v>6.86</v>
       </c>
       <c r="G16" t="n">
-        <v>218.6</v>
+        <v>217.4</v>
       </c>
       <c r="H16" t="n">
-        <v>95.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.81</v>
+        <v>-48.53</v>
       </c>
       <c r="K16" t="n">
-        <v>-35.61</v>
+        <v>-42.7</v>
       </c>
       <c r="L16" t="n">
-        <v>54.16</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>2.36</v>
       </c>
       <c r="F17" t="n">
-        <v>11.57</v>
+        <v>7.69</v>
       </c>
       <c r="G17" t="n">
-        <v>235.6</v>
+        <v>221.6</v>
       </c>
       <c r="H17" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>23.29</v>
+        <v>26.53</v>
       </c>
       <c r="K17" t="n">
-        <v>102.78</v>
+        <v>119.3</v>
       </c>
       <c r="L17" t="n">
-        <v>105.38</v>
+        <v>122.21</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>3.15</v>
       </c>
       <c r="F18" t="n">
-        <v>10.73</v>
+        <v>10.92</v>
       </c>
       <c r="G18" t="n">
-        <v>213.3</v>
+        <v>204.9</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>94.8</v>
       </c>
       <c r="I18" t="n">
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>87.81</v>
+        <v>101.44</v>
       </c>
       <c r="K18" t="n">
-        <v>-56.39</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>104.36</v>
+        <v>122.34</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.38</v>
       </c>
       <c r="F19" t="n">
-        <v>10.94</v>
+        <v>10.51</v>
       </c>
       <c r="G19" t="n">
-        <v>217.1</v>
+        <v>209.1</v>
       </c>
       <c r="H19" t="n">
-        <v>95.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="I19" t="n">
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>82.19</v>
+        <v>95.08</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.300000000000001</v>
+        <v>-14.23</v>
       </c>
       <c r="L19" t="n">
-        <v>82.70999999999999</v>
+        <v>96.14</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>3.07</v>
       </c>
       <c r="F20" t="n">
-        <v>10.97</v>
+        <v>9.84</v>
       </c>
       <c r="G20" t="n">
-        <v>234.1</v>
+        <v>209.8</v>
       </c>
       <c r="H20" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.64</v>
+        <v>-22.66</v>
       </c>
       <c r="K20" t="n">
-        <v>-110.54</v>
+        <v>-139.95</v>
       </c>
       <c r="L20" t="n">
-        <v>111.78</v>
+        <v>141.78</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>3.92</v>
       </c>
       <c r="F21" t="n">
-        <v>11.38</v>
+        <v>12.15</v>
       </c>
       <c r="G21" t="n">
-        <v>216.5</v>
+        <v>217.8</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-107.94</v>
+        <v>-137.44</v>
       </c>
       <c r="K21" t="n">
-        <v>142.55</v>
+        <v>159.14</v>
       </c>
       <c r="L21" t="n">
-        <v>178.81</v>
+        <v>210.28</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>3.08</v>
       </c>
       <c r="F22" t="n">
-        <v>10.9</v>
+        <v>8.24</v>
       </c>
       <c r="G22" t="n">
-        <v>221.8</v>
+        <v>208.3</v>
       </c>
       <c r="H22" t="n">
-        <v>95.09999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-104.33</v>
+        <v>-107.65</v>
       </c>
       <c r="K22" t="n">
-        <v>103.17</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>146.73</v>
+        <v>142.91</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>2.51</v>
       </c>
       <c r="F23" t="n">
-        <v>11.89</v>
+        <v>3.92</v>
       </c>
       <c r="G23" t="n">
-        <v>216.6</v>
+        <v>228.1</v>
       </c>
       <c r="H23" t="n">
-        <v>94.7</v>
+        <v>96.5</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-104.49</v>
+        <v>-128.22</v>
       </c>
       <c r="K23" t="n">
-        <v>50.58</v>
+        <v>26.51</v>
       </c>
       <c r="L23" t="n">
-        <v>116.09</v>
+        <v>130.93</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>2.96</v>
       </c>
       <c r="F24" t="n">
-        <v>11.83</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>223.6</v>
+        <v>226.9</v>
       </c>
       <c r="H24" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>18.69</v>
+        <v>-12.61</v>
       </c>
       <c r="K24" t="n">
-        <v>-120.43</v>
+        <v>-149.68</v>
       </c>
       <c r="L24" t="n">
-        <v>121.87</v>
+        <v>150.21</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>4.34</v>
       </c>
       <c r="F25" t="n">
-        <v>10.86</v>
+        <v>11.69</v>
       </c>
       <c r="G25" t="n">
-        <v>225</v>
+        <v>207.6</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-194.73</v>
+        <v>-227.69</v>
       </c>
       <c r="K25" t="n">
-        <v>75.08</v>
+        <v>52.89</v>
       </c>
       <c r="L25" t="n">
-        <v>208.7</v>
+        <v>233.75</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>3.14</v>
       </c>
       <c r="F26" t="n">
-        <v>11.81</v>
+        <v>8.48</v>
       </c>
       <c r="G26" t="n">
-        <v>217.8</v>
+        <v>226.6</v>
       </c>
       <c r="H26" t="n">
-        <v>94.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>109.16</v>
+        <v>90.31</v>
       </c>
       <c r="K26" t="n">
-        <v>-243.14</v>
+        <v>-296.88</v>
       </c>
       <c r="L26" t="n">
-        <v>266.52</v>
+        <v>310.31</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>3.08</v>
       </c>
       <c r="F27" t="n">
-        <v>12.1</v>
+        <v>8.51</v>
       </c>
       <c r="G27" t="n">
-        <v>210</v>
+        <v>232.3</v>
       </c>
       <c r="H27" t="n">
-        <v>91.7</v>
+        <v>93.2</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-14.36</v>
+        <v>-111.47</v>
       </c>
       <c r="K27" t="n">
-        <v>-146.18</v>
+        <v>-166.18</v>
       </c>
       <c r="L27" t="n">
-        <v>146.88</v>
+        <v>200.1</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>3.1</v>
       </c>
       <c r="F28" t="n">
-        <v>11.25</v>
+        <v>11.7</v>
       </c>
       <c r="G28" t="n">
-        <v>220.6</v>
+        <v>215.3</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-167.4</v>
+        <v>-206.46</v>
       </c>
       <c r="K28" t="n">
-        <v>-22.76</v>
+        <v>-93.64</v>
       </c>
       <c r="L28" t="n">
-        <v>168.94</v>
+        <v>226.7</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>2.72</v>
       </c>
       <c r="F29" t="n">
-        <v>11.34</v>
+        <v>7.52</v>
       </c>
       <c r="G29" t="n">
-        <v>224.4</v>
+        <v>217</v>
       </c>
       <c r="H29" t="n">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>57.26</v>
+        <v>61.39</v>
       </c>
       <c r="K29" t="n">
-        <v>-49.02</v>
+        <v>-53.6</v>
       </c>
       <c r="L29" t="n">
-        <v>75.37</v>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>3.38</v>
       </c>
       <c r="F30" t="n">
-        <v>11.24</v>
+        <v>13.22</v>
       </c>
       <c r="G30" t="n">
-        <v>237.7</v>
+        <v>215.2</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>49.31</v>
+        <v>62.78</v>
       </c>
       <c r="K30" t="n">
-        <v>57.41</v>
+        <v>71.7</v>
       </c>
       <c r="L30" t="n">
-        <v>75.67</v>
+        <v>95.29000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>2.91</v>
       </c>
       <c r="F31" t="n">
-        <v>12.13</v>
+        <v>13.22</v>
       </c>
       <c r="G31" t="n">
-        <v>227.7</v>
+        <v>232.9</v>
       </c>
       <c r="H31" t="n">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>12.33</v>
+        <v>16.42</v>
       </c>
       <c r="K31" t="n">
-        <v>66.44</v>
+        <v>93.61</v>
       </c>
       <c r="L31" t="n">
-        <v>67.58</v>
+        <v>95.04000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>2.93</v>
       </c>
       <c r="F32" t="n">
-        <v>10.86</v>
+        <v>8.75</v>
       </c>
       <c r="G32" t="n">
-        <v>205.2</v>
+        <v>207.5</v>
       </c>
       <c r="H32" t="n">
-        <v>96.5</v>
+        <v>90.8</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>33.1</v>
+        <v>31.97</v>
       </c>
       <c r="K32" t="n">
-        <v>-81.86</v>
+        <v>-85.06</v>
       </c>
       <c r="L32" t="n">
-        <v>88.3</v>
+        <v>90.87</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>3.8</v>
       </c>
       <c r="F33" t="n">
-        <v>11.86</v>
+        <v>13.07</v>
       </c>
       <c r="G33" t="n">
-        <v>221.2</v>
+        <v>227.5</v>
       </c>
       <c r="H33" t="n">
-        <v>96.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>62.18</v>
+        <v>72.94</v>
       </c>
       <c r="K33" t="n">
-        <v>50.05</v>
+        <v>59.01</v>
       </c>
       <c r="L33" t="n">
-        <v>79.81999999999999</v>
+        <v>93.81999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>2.77</v>
       </c>
       <c r="F34" t="n">
-        <v>11.36</v>
+        <v>6.99</v>
       </c>
       <c r="G34" t="n">
-        <v>219.5</v>
+        <v>217.5</v>
       </c>
       <c r="H34" t="n">
-        <v>94.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-63.67</v>
+        <v>-65.17</v>
       </c>
       <c r="K34" t="n">
-        <v>-23.24</v>
+        <v>-26.4</v>
       </c>
       <c r="L34" t="n">
-        <v>67.78</v>
+        <v>70.31999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>3.85</v>
       </c>
       <c r="F35" t="n">
-        <v>11.21</v>
+        <v>12.77</v>
       </c>
       <c r="G35" t="n">
-        <v>225.7</v>
+        <v>214.5</v>
       </c>
       <c r="H35" t="n">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-123.12</v>
+        <v>-154.79</v>
       </c>
       <c r="K35" t="n">
-        <v>108.34</v>
+        <v>116.32</v>
       </c>
       <c r="L35" t="n">
-        <v>164.01</v>
+        <v>193.63</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>3.29</v>
       </c>
       <c r="F36" t="n">
-        <v>11.25</v>
+        <v>12.62</v>
       </c>
       <c r="G36" t="n">
-        <v>210.3</v>
+        <v>215.4</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-131.22</v>
+        <v>-163.82</v>
       </c>
       <c r="K36" t="n">
-        <v>-125.52</v>
+        <v>-158.62</v>
       </c>
       <c r="L36" t="n">
-        <v>181.59</v>
+        <v>228.03</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>2.96</v>
       </c>
       <c r="F37" t="n">
-        <v>12.22</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>226.3</v>
+        <v>234.8</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>21.74</v>
+        <v>1.37</v>
       </c>
       <c r="K37" t="n">
-        <v>-16.08</v>
+        <v>-32.24</v>
       </c>
       <c r="L37" t="n">
-        <v>27.04</v>
+        <v>32.27</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>3.4</v>
       </c>
       <c r="F38" t="n">
-        <v>11.71</v>
+        <v>13.22</v>
       </c>
       <c r="G38" t="n">
-        <v>227.6</v>
+        <v>224.5</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-14.23</v>
+        <v>-48.18</v>
       </c>
       <c r="K38" t="n">
-        <v>-150.26</v>
+        <v>-187.86</v>
       </c>
       <c r="L38" t="n">
-        <v>150.93</v>
+        <v>193.94</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>3.13</v>
       </c>
       <c r="F39" t="n">
-        <v>11.64</v>
+        <v>8.25</v>
       </c>
       <c r="G39" t="n">
-        <v>211.2</v>
+        <v>223.1</v>
       </c>
       <c r="H39" t="n">
-        <v>95.8</v>
+        <v>93.7</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-209.17</v>
+        <v>-214.09</v>
       </c>
       <c r="K39" t="n">
-        <v>-86.12</v>
+        <v>-95.91</v>
       </c>
       <c r="L39" t="n">
-        <v>226.21</v>
+        <v>234.59</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>4.35</v>
       </c>
       <c r="F40" t="n">
-        <v>11.49</v>
+        <v>13.2</v>
       </c>
       <c r="G40" t="n">
-        <v>222.6</v>
+        <v>220.2</v>
       </c>
       <c r="H40" t="n">
-        <v>95.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-115.64</v>
+        <v>-146.31</v>
       </c>
       <c r="K40" t="n">
-        <v>-113.14</v>
+        <v>-151.13</v>
       </c>
       <c r="L40" t="n">
-        <v>161.78</v>
+        <v>210.35</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>2.77</v>
       </c>
       <c r="F41" t="n">
-        <v>10.86</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>217.9</v>
+        <v>207.5</v>
       </c>
       <c r="H41" t="n">
-        <v>94.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>277.58</v>
+        <v>308.66</v>
       </c>
       <c r="K41" t="n">
-        <v>127.87</v>
+        <v>109.51</v>
       </c>
       <c r="L41" t="n">
-        <v>305.61</v>
+        <v>327.51</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>3.74</v>
       </c>
       <c r="F42" t="n">
-        <v>11.13</v>
+        <v>13.12</v>
       </c>
       <c r="G42" t="n">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="H42" t="n">
-        <v>99.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>141.86</v>
+        <v>135.48</v>
       </c>
       <c r="K42" t="n">
-        <v>-167.47</v>
+        <v>-262.03</v>
       </c>
       <c r="L42" t="n">
-        <v>219.48</v>
+        <v>294.98</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>3.52</v>
       </c>
       <c r="F43" t="n">
-        <v>11.41</v>
+        <v>10.57</v>
       </c>
       <c r="G43" t="n">
-        <v>223.7</v>
+        <v>218.4</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>8.44</v>
+        <v>-13.05</v>
       </c>
       <c r="K43" t="n">
-        <v>-300.64</v>
+        <v>-380.61</v>
       </c>
       <c r="L43" t="n">
-        <v>300.76</v>
+        <v>380.83</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>3.08</v>
       </c>
       <c r="F44" t="n">
-        <v>11.69</v>
+        <v>10.46</v>
       </c>
       <c r="G44" t="n">
-        <v>229</v>
+        <v>224.1</v>
       </c>
       <c r="H44" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.86</v>
+        <v>-55.75</v>
       </c>
       <c r="K44" t="n">
-        <v>-51.9</v>
+        <v>-59.4</v>
       </c>
       <c r="L44" t="n">
-        <v>71.28</v>
+        <v>81.45999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>4.1</v>
       </c>
       <c r="F45" t="n">
-        <v>11.48</v>
+        <v>13.22</v>
       </c>
       <c r="G45" t="n">
-        <v>210.9</v>
+        <v>219.9</v>
       </c>
       <c r="H45" t="n">
-        <v>89.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" t="n">
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>17.02</v>
+        <v>16.33</v>
       </c>
       <c r="K45" t="n">
-        <v>13.6</v>
+        <v>13.07</v>
       </c>
       <c r="L45" t="n">
-        <v>21.78</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>3.59</v>
       </c>
       <c r="F46" t="n">
-        <v>11.24</v>
+        <v>9.93</v>
       </c>
       <c r="G46" t="n">
-        <v>219.5</v>
+        <v>215.1</v>
       </c>
       <c r="H46" t="n">
-        <v>93.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>8.18</v>
+        <v>7.46</v>
       </c>
       <c r="K46" t="n">
-        <v>-67.92</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>68.41</v>
+        <v>71.15000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>3.45</v>
       </c>
       <c r="F47" t="n">
-        <v>11.27</v>
+        <v>11.88</v>
       </c>
       <c r="G47" t="n">
-        <v>202.9</v>
+        <v>215.6</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-59.48</v>
+        <v>-76.48999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-70.17</v>
+        <v>-89.51000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>91.98999999999999</v>
+        <v>117.74</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>3.34</v>
       </c>
       <c r="F48" t="n">
-        <v>11.61</v>
+        <v>10.29</v>
       </c>
       <c r="G48" t="n">
-        <v>235</v>
+        <v>222.6</v>
       </c>
       <c r="H48" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-97.77</v>
+        <v>-107.63</v>
       </c>
       <c r="K48" t="n">
-        <v>25.35</v>
+        <v>24.76</v>
       </c>
       <c r="L48" t="n">
-        <v>101</v>
+        <v>110.44</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>3.06</v>
       </c>
       <c r="F49" t="n">
-        <v>11.95</v>
+        <v>11.32</v>
       </c>
       <c r="G49" t="n">
-        <v>222.3</v>
+        <v>229.3</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="I49" t="n">
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-79.20999999999999</v>
+        <v>-97.51000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>64.88</v>
+        <v>76.09</v>
       </c>
       <c r="L49" t="n">
-        <v>102.39</v>
+        <v>123.68</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>3.96</v>
       </c>
       <c r="F50" t="n">
-        <v>11.69</v>
+        <v>9.85</v>
       </c>
       <c r="G50" t="n">
-        <v>221.6</v>
+        <v>224.2</v>
       </c>
       <c r="H50" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.02</v>
+        <v>-21.05</v>
       </c>
       <c r="K50" t="n">
-        <v>-170.51</v>
+        <v>-185.89</v>
       </c>
       <c r="L50" t="n">
-        <v>170.87</v>
+        <v>187.08</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>3.28</v>
       </c>
       <c r="F51" t="n">
-        <v>11.85</v>
+        <v>10.13</v>
       </c>
       <c r="G51" t="n">
-        <v>225</v>
+        <v>227.2</v>
       </c>
       <c r="H51" t="n">
-        <v>90.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-38.6</v>
+        <v>-57.56</v>
       </c>
       <c r="K51" t="n">
-        <v>-87.98999999999999</v>
+        <v>-109.25</v>
       </c>
       <c r="L51" t="n">
-        <v>96.08</v>
+        <v>123.49</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>3.24</v>
       </c>
       <c r="F52" t="n">
-        <v>11.92</v>
+        <v>12.17</v>
       </c>
       <c r="G52" t="n">
-        <v>228.9</v>
+        <v>228.7</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>171.53</v>
+        <v>216.31</v>
       </c>
       <c r="K52" t="n">
-        <v>92.33</v>
+        <v>113.96</v>
       </c>
       <c r="L52" t="n">
-        <v>194.8</v>
+        <v>244.5</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>3.2</v>
       </c>
       <c r="F53" t="n">
-        <v>12.61</v>
+        <v>6.96</v>
       </c>
       <c r="G53" t="n">
-        <v>233.7</v>
+        <v>242.6</v>
       </c>
       <c r="H53" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>57.94</v>
+        <v>12.29</v>
       </c>
       <c r="K53" t="n">
-        <v>129.43</v>
+        <v>143.37</v>
       </c>
       <c r="L53" t="n">
-        <v>141.81</v>
+        <v>143.89</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>4.17</v>
       </c>
       <c r="F54" t="n">
-        <v>11.03</v>
+        <v>13.22</v>
       </c>
       <c r="G54" t="n">
-        <v>217.8</v>
+        <v>210.9</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I54" t="n">
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-163.19</v>
+        <v>-206.15</v>
       </c>
       <c r="K54" t="n">
-        <v>53.72</v>
+        <v>15.44</v>
       </c>
       <c r="L54" t="n">
-        <v>171.8</v>
+        <v>206.73</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>2.84</v>
       </c>
       <c r="F55" t="n">
-        <v>12.07</v>
+        <v>11.15</v>
       </c>
       <c r="G55" t="n">
-        <v>225.7</v>
+        <v>231.7</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>32.25</v>
+        <v>18.98</v>
       </c>
       <c r="K55" t="n">
-        <v>-232.68</v>
+        <v>-282.87</v>
       </c>
       <c r="L55" t="n">
-        <v>234.91</v>
+        <v>283.51</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>4.75</v>
       </c>
       <c r="F56" t="n">
-        <v>11.4</v>
+        <v>13.22</v>
       </c>
       <c r="G56" t="n">
-        <v>217.2</v>
+        <v>218.3</v>
       </c>
       <c r="H56" t="n">
-        <v>92</v>
+        <v>96.7</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>225.38</v>
+        <v>197.91</v>
       </c>
       <c r="K56" t="n">
-        <v>-155.67</v>
+        <v>-220.16</v>
       </c>
       <c r="L56" t="n">
-        <v>273.92</v>
+        <v>296.04</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>3.51</v>
       </c>
       <c r="F57" t="n">
-        <v>12.64</v>
+        <v>13.22</v>
       </c>
       <c r="G57" t="n">
-        <v>217.8</v>
+        <v>243.1</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>170.52</v>
+        <v>145.44</v>
       </c>
       <c r="K57" t="n">
-        <v>-205.76</v>
+        <v>-253.1</v>
       </c>
       <c r="L57" t="n">
-        <v>267.23</v>
+        <v>291.91</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>3.76</v>
       </c>
       <c r="F58" t="n">
-        <v>12.25</v>
+        <v>10.97</v>
       </c>
       <c r="G58" t="n">
-        <v>219.3</v>
+        <v>235.2</v>
       </c>
       <c r="H58" t="n">
-        <v>94.3</v>
+        <v>97.8</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>156.1</v>
+        <v>39.51</v>
       </c>
       <c r="K58" t="n">
-        <v>105.43</v>
+        <v>57.69</v>
       </c>
       <c r="L58" t="n">
-        <v>188.37</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>3.48</v>
       </c>
       <c r="F59" t="n">
-        <v>11.59</v>
+        <v>13.22</v>
       </c>
       <c r="G59" t="n">
-        <v>229.1</v>
+        <v>222.2</v>
       </c>
       <c r="H59" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>23.16</v>
+        <v>29.26</v>
       </c>
       <c r="K59" t="n">
-        <v>-65.86</v>
+        <v>-87.22</v>
       </c>
       <c r="L59" t="n">
-        <v>69.81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>4.08</v>
       </c>
       <c r="F60" t="n">
-        <v>11.6</v>
+        <v>13.22</v>
       </c>
       <c r="G60" t="n">
-        <v>230.6</v>
+        <v>222.3</v>
       </c>
       <c r="H60" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>32.71</v>
+        <v>40.06</v>
       </c>
       <c r="K60" t="n">
-        <v>50.83</v>
+        <v>62.14</v>
       </c>
       <c r="L60" t="n">
-        <v>60.45</v>
+        <v>73.94</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>3.47</v>
       </c>
       <c r="F61" t="n">
-        <v>11.75</v>
+        <v>9.51</v>
       </c>
       <c r="G61" t="n">
-        <v>226.7</v>
+        <v>225.3</v>
       </c>
       <c r="H61" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.02</v>
+        <v>-11.19</v>
       </c>
       <c r="K61" t="n">
-        <v>-76.53</v>
+        <v>-88.01000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>77.06</v>
+        <v>88.72</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>11.66</v>
+        <v>13.22</v>
       </c>
       <c r="G62" t="n">
-        <v>210.6</v>
+        <v>223.4</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>156.06</v>
+        <v>167.02</v>
       </c>
       <c r="K62" t="n">
-        <v>64.7</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>168.94</v>
+        <v>180.52</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>3.94</v>
       </c>
       <c r="F63" t="n">
-        <v>11.63</v>
+        <v>13.22</v>
       </c>
       <c r="G63" t="n">
-        <v>218.6</v>
+        <v>222.9</v>
       </c>
       <c r="H63" t="n">
-        <v>97.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I63" t="n">
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.02</v>
+        <v>-13.56</v>
       </c>
       <c r="K63" t="n">
-        <v>33.94</v>
+        <v>32.41</v>
       </c>
       <c r="L63" t="n">
-        <v>34.31</v>
+        <v>35.13</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>3.48</v>
       </c>
       <c r="F64" t="n">
-        <v>12.21</v>
+        <v>11.9</v>
       </c>
       <c r="G64" t="n">
-        <v>208</v>
+        <v>234.5</v>
       </c>
       <c r="H64" t="n">
-        <v>97.7</v>
+        <v>92.2</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-117.33</v>
+        <v>-122.15</v>
       </c>
       <c r="K64" t="n">
-        <v>-13.76</v>
+        <v>-14.71</v>
       </c>
       <c r="L64" t="n">
-        <v>118.13</v>
+        <v>123.03</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>3.88</v>
       </c>
       <c r="F65" t="n">
-        <v>11.32</v>
+        <v>11.78</v>
       </c>
       <c r="G65" t="n">
-        <v>218</v>
+        <v>216.8</v>
       </c>
       <c r="H65" t="n">
-        <v>95.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.81</v>
+        <v>-21.21</v>
       </c>
       <c r="K65" t="n">
-        <v>-142.81</v>
+        <v>-153.57</v>
       </c>
       <c r="L65" t="n">
-        <v>143.38</v>
+        <v>155.03</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>3.9</v>
       </c>
       <c r="F66" t="n">
-        <v>11.33</v>
+        <v>11.68</v>
       </c>
       <c r="G66" t="n">
-        <v>214.6</v>
+        <v>216.9</v>
       </c>
       <c r="H66" t="n">
-        <v>94.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>44.39</v>
+        <v>40.01</v>
       </c>
       <c r="K66" t="n">
-        <v>84.23999999999999</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>95.22</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>3.72</v>
       </c>
       <c r="F67" t="n">
-        <v>12.15</v>
+        <v>13.22</v>
       </c>
       <c r="G67" t="n">
-        <v>207.4</v>
+        <v>233.4</v>
       </c>
       <c r="H67" t="n">
-        <v>93.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>35.78</v>
+        <v>7.57</v>
       </c>
       <c r="K67" t="n">
-        <v>80.06999999999999</v>
+        <v>104.3</v>
       </c>
       <c r="L67" t="n">
-        <v>87.70999999999999</v>
+        <v>104.57</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>3.63</v>
       </c>
       <c r="F68" t="n">
-        <v>11.29</v>
+        <v>12.06</v>
       </c>
       <c r="G68" t="n">
-        <v>228.7</v>
+        <v>216.1</v>
       </c>
       <c r="H68" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-202.27</v>
+        <v>-226.55</v>
       </c>
       <c r="K68" t="n">
-        <v>-36.83</v>
+        <v>-64.34</v>
       </c>
       <c r="L68" t="n">
-        <v>205.6</v>
+        <v>235.51</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>4.04</v>
       </c>
       <c r="F69" t="n">
-        <v>12.12</v>
+        <v>11.47</v>
       </c>
       <c r="G69" t="n">
-        <v>215.1</v>
+        <v>232.7</v>
       </c>
       <c r="H69" t="n">
-        <v>99.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-179.31</v>
+        <v>-205.47</v>
       </c>
       <c r="K69" t="n">
-        <v>-39.11</v>
+        <v>-53.83</v>
       </c>
       <c r="L69" t="n">
-        <v>183.53</v>
+        <v>212.4</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>3.3</v>
       </c>
       <c r="F70" t="n">
-        <v>11.47</v>
+        <v>11.56</v>
       </c>
       <c r="G70" t="n">
-        <v>226.8</v>
+        <v>219.6</v>
       </c>
       <c r="H70" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-230.98</v>
+        <v>-249.56</v>
       </c>
       <c r="K70" t="n">
-        <v>-75.40000000000001</v>
+        <v>-95.78</v>
       </c>
       <c r="L70" t="n">
-        <v>242.98</v>
+        <v>267.31</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>3.8</v>
       </c>
       <c r="F71" t="n">
-        <v>11.34</v>
+        <v>13.22</v>
       </c>
       <c r="G71" t="n">
-        <v>221.8</v>
+        <v>217.1</v>
       </c>
       <c r="H71" t="n">
-        <v>96</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I71" t="n">
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>88.23</v>
+        <v>61.12</v>
       </c>
       <c r="K71" t="n">
-        <v>-206.16</v>
+        <v>-281.66</v>
       </c>
       <c r="L71" t="n">
-        <v>224.25</v>
+        <v>288.21</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>3.29</v>
       </c>
       <c r="F72" t="n">
-        <v>11.94</v>
+        <v>13.22</v>
       </c>
       <c r="G72" t="n">
-        <v>220.3</v>
+        <v>229.2</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>189.21</v>
+        <v>189.36</v>
       </c>
       <c r="K72" t="n">
-        <v>-129.9</v>
+        <v>-194.52</v>
       </c>
       <c r="L72" t="n">
-        <v>229.51</v>
+        <v>271.47</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>3.1</v>
       </c>
       <c r="F73" t="n">
-        <v>11.62</v>
+        <v>11.27</v>
       </c>
       <c r="G73" t="n">
-        <v>226.2</v>
+        <v>222.8</v>
       </c>
       <c r="H73" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I73" t="n">
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-183.46</v>
+        <v>-250.32</v>
       </c>
       <c r="K73" t="n">
-        <v>141.25</v>
+        <v>132.33</v>
       </c>
       <c r="L73" t="n">
-        <v>231.53</v>
+        <v>283.15</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>3.63</v>
       </c>
       <c r="F74" t="n">
-        <v>11.46</v>
+        <v>13.22</v>
       </c>
       <c r="G74" t="n">
-        <v>225.8</v>
+        <v>219.4</v>
       </c>
       <c r="H74" t="n">
         <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>64.86</v>
+        <v>81.77</v>
       </c>
       <c r="K74" t="n">
-        <v>34.94</v>
+        <v>43.16</v>
       </c>
       <c r="L74" t="n">
-        <v>73.67</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>3.71</v>
       </c>
       <c r="F75" t="n">
-        <v>11.51</v>
+        <v>12.19</v>
       </c>
       <c r="G75" t="n">
-        <v>206.8</v>
+        <v>220.6</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-54.76</v>
+        <v>-71.73</v>
       </c>
       <c r="K75" t="n">
-        <v>23.54</v>
+        <v>28.71</v>
       </c>
       <c r="L75" t="n">
-        <v>59.61</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>3.23</v>
       </c>
       <c r="F76" t="n">
-        <v>11.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>212.7</v>
+        <v>211.9</v>
       </c>
       <c r="H76" t="n">
-        <v>92.90000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>58.85</v>
+        <v>74.52</v>
       </c>
       <c r="K76" t="n">
-        <v>29.72</v>
+        <v>36.84</v>
       </c>
       <c r="L76" t="n">
-        <v>65.93000000000001</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>4.2</v>
       </c>
       <c r="F77" t="n">
-        <v>11.94</v>
+        <v>13.22</v>
       </c>
       <c r="G77" t="n">
-        <v>222.1</v>
+        <v>229.2</v>
       </c>
       <c r="H77" t="n">
-        <v>97.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>113.32</v>
+        <v>120.55</v>
       </c>
       <c r="K77" t="n">
-        <v>-10.64</v>
+        <v>-13.48</v>
       </c>
       <c r="L77" t="n">
-        <v>113.82</v>
+        <v>121.3</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>3.07</v>
       </c>
       <c r="F78" t="n">
-        <v>10.68</v>
+        <v>11.23</v>
       </c>
       <c r="G78" t="n">
-        <v>214.8</v>
+        <v>203.9</v>
       </c>
       <c r="H78" t="n">
-        <v>98.7</v>
+        <v>95.5</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-60.7</v>
+        <v>-70.75</v>
       </c>
       <c r="K78" t="n">
-        <v>50.64</v>
+        <v>54.6</v>
       </c>
       <c r="L78" t="n">
-        <v>79.05</v>
+        <v>89.36</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>3.27</v>
       </c>
       <c r="F79" t="n">
-        <v>10.77</v>
+        <v>12.8</v>
       </c>
       <c r="G79" t="n">
-        <v>225.3</v>
+        <v>205.7</v>
       </c>
       <c r="H79" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>94.12</v>
+        <v>128.04</v>
       </c>
       <c r="K79" t="n">
-        <v>-18.69</v>
+        <v>-28.85</v>
       </c>
       <c r="L79" t="n">
-        <v>95.95999999999999</v>
+        <v>131.25</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>3.65</v>
       </c>
       <c r="F80" t="n">
-        <v>11</v>
+        <v>13.22</v>
       </c>
       <c r="G80" t="n">
-        <v>218.3</v>
+        <v>210.3</v>
       </c>
       <c r="H80" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-132.15</v>
+        <v>-169.18</v>
       </c>
       <c r="K80" t="n">
-        <v>-15.51</v>
+        <v>-33.11</v>
       </c>
       <c r="L80" t="n">
-        <v>133.06</v>
+        <v>172.39</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>3.37</v>
       </c>
       <c r="F81" t="n">
-        <v>10.74</v>
+        <v>9.98</v>
       </c>
       <c r="G81" t="n">
-        <v>228.2</v>
+        <v>205.1</v>
       </c>
       <c r="H81" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>106.14</v>
+        <v>120.44</v>
       </c>
       <c r="K81" t="n">
-        <v>46.92</v>
+        <v>38.68</v>
       </c>
       <c r="L81" t="n">
-        <v>116.05</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>3.73</v>
       </c>
       <c r="F82" t="n">
-        <v>11.79</v>
+        <v>13.22</v>
       </c>
       <c r="G82" t="n">
-        <v>206.3</v>
+        <v>226.1</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>91.3</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>95.18000000000001</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-84.37</v>
+        <v>-102.64</v>
       </c>
       <c r="L82" t="n">
-        <v>127.19</v>
+        <v>135.01</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>3.96</v>
       </c>
       <c r="F83" t="n">
-        <v>11.45</v>
+        <v>13.22</v>
       </c>
       <c r="G83" t="n">
-        <v>206.8</v>
+        <v>219.4</v>
       </c>
       <c r="H83" t="n">
-        <v>92.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>106.02</v>
+        <v>116.7</v>
       </c>
       <c r="K83" t="n">
-        <v>89.84</v>
+        <v>90.92</v>
       </c>
       <c r="L83" t="n">
-        <v>138.97</v>
+        <v>147.94</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>4.02</v>
       </c>
       <c r="F84" t="n">
-        <v>11.37</v>
+        <v>13.22</v>
       </c>
       <c r="G84" t="n">
-        <v>215.7</v>
+        <v>217.8</v>
       </c>
       <c r="H84" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I84" t="n">
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-137.75</v>
+        <v>-168.38</v>
       </c>
       <c r="K84" t="n">
-        <v>-40.66</v>
+        <v>-81.37</v>
       </c>
       <c r="L84" t="n">
-        <v>143.62</v>
+        <v>187.02</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>3.61</v>
       </c>
       <c r="F85" t="n">
-        <v>11.67</v>
+        <v>12.78</v>
       </c>
       <c r="G85" t="n">
-        <v>211.5</v>
+        <v>223.6</v>
       </c>
       <c r="H85" t="n">
-        <v>98.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>22.5</v>
+        <v>-12.52</v>
       </c>
       <c r="K85" t="n">
-        <v>-136.35</v>
+        <v>-191.41</v>
       </c>
       <c r="L85" t="n">
-        <v>138.19</v>
+        <v>191.82</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>4.1</v>
       </c>
       <c r="F86" t="n">
-        <v>12.08</v>
+        <v>12.73</v>
       </c>
       <c r="G86" t="n">
-        <v>224.5</v>
+        <v>231.9</v>
       </c>
       <c r="H86" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-219.34</v>
+        <v>-306.73</v>
       </c>
       <c r="K86" t="n">
-        <v>128.31</v>
+        <v>126.52</v>
       </c>
       <c r="L86" t="n">
-        <v>254.11</v>
+        <v>331.8</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>3.24</v>
       </c>
       <c r="F87" t="n">
-        <v>11.39</v>
+        <v>9.69</v>
       </c>
       <c r="G87" t="n">
-        <v>214.8</v>
+        <v>218</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>169.71</v>
+        <v>158.95</v>
       </c>
       <c r="K87" t="n">
-        <v>-158.94</v>
+        <v>-206.93</v>
       </c>
       <c r="L87" t="n">
-        <v>232.52</v>
+        <v>260.93</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>3.2</v>
       </c>
       <c r="F88" t="n">
-        <v>12</v>
+        <v>13.03</v>
       </c>
       <c r="G88" t="n">
-        <v>226.4</v>
+        <v>230.3</v>
       </c>
       <c r="H88" t="n">
         <v>100</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-44.62</v>
+        <v>-83.41</v>
       </c>
       <c r="K88" t="n">
-        <v>299.6</v>
+        <v>336.12</v>
       </c>
       <c r="L88" t="n">
-        <v>302.9</v>
+        <v>346.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="K14" t="n">
-        <v>-48.5</v>
+        <v>-51.25</v>
       </c>
       <c r="L14" t="n">
-        <v>48.5</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.91</v>
+        <v>-1.99</v>
       </c>
       <c r="K15" t="n">
-        <v>-81.34999999999999</v>
+        <v>-84.45</v>
       </c>
       <c r="L15" t="n">
-        <v>81.37</v>
+        <v>84.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-48.53</v>
+        <v>-53.73</v>
       </c>
       <c r="K16" t="n">
-        <v>-42.7</v>
+        <v>-47.27</v>
       </c>
       <c r="L16" t="n">
-        <v>64.64</v>
+        <v>71.56</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>26.53</v>
+        <v>29.37</v>
       </c>
       <c r="K17" t="n">
-        <v>119.3</v>
+        <v>132.08</v>
       </c>
       <c r="L17" t="n">
-        <v>122.21</v>
+        <v>135.3</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>101.44</v>
+        <v>110.66</v>
       </c>
       <c r="K18" t="n">
-        <v>-68.40000000000001</v>
+        <v>-74.62</v>
       </c>
       <c r="L18" t="n">
-        <v>122.34</v>
+        <v>133.47</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>95.08</v>
+        <v>96.89</v>
       </c>
       <c r="K19" t="n">
-        <v>-14.23</v>
+        <v>-14.5</v>
       </c>
       <c r="L19" t="n">
-        <v>96.14</v>
+        <v>97.95999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-22.66</v>
+        <v>-23.94</v>
       </c>
       <c r="K20" t="n">
-        <v>-139.95</v>
+        <v>-147.88</v>
       </c>
       <c r="L20" t="n">
-        <v>141.78</v>
+        <v>149.8</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-137.44</v>
+        <v>-151.99</v>
       </c>
       <c r="K21" t="n">
-        <v>159.14</v>
+        <v>175.99</v>
       </c>
       <c r="L21" t="n">
-        <v>210.28</v>
+        <v>232.54</v>
       </c>
     </row>
     <row r="22">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-128.22</v>
+        <v>-141.96</v>
       </c>
       <c r="K23" t="n">
-        <v>26.51</v>
+        <v>29.35</v>
       </c>
       <c r="L23" t="n">
-        <v>130.93</v>
+        <v>144.96</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-12.61</v>
+        <v>-12.85</v>
       </c>
       <c r="K24" t="n">
-        <v>-149.68</v>
+        <v>-152.61</v>
       </c>
       <c r="L24" t="n">
-        <v>150.21</v>
+        <v>153.15</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-227.69</v>
+        <v>-232.44</v>
       </c>
       <c r="K25" t="n">
-        <v>52.89</v>
+        <v>53.99</v>
       </c>
       <c r="L25" t="n">
-        <v>233.75</v>
+        <v>238.63</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>90.31</v>
+        <v>98.52</v>
       </c>
       <c r="K26" t="n">
-        <v>-296.88</v>
+        <v>-323.87</v>
       </c>
       <c r="L26" t="n">
-        <v>310.31</v>
+        <v>338.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-111.47</v>
+        <v>-121.6</v>
       </c>
       <c r="K27" t="n">
-        <v>-166.18</v>
+        <v>-181.29</v>
       </c>
       <c r="L27" t="n">
-        <v>200.1</v>
+        <v>218.3</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-206.46</v>
+        <v>-218.14</v>
       </c>
       <c r="K28" t="n">
-        <v>-93.64</v>
+        <v>-98.94</v>
       </c>
       <c r="L28" t="n">
-        <v>226.7</v>
+        <v>239.54</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>61.39</v>
+        <v>63.75</v>
       </c>
       <c r="K29" t="n">
-        <v>-53.6</v>
+        <v>-55.66</v>
       </c>
       <c r="L29" t="n">
-        <v>81.48999999999999</v>
+        <v>84.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>62.78</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>71.7</v>
+        <v>75.7</v>
       </c>
       <c r="L30" t="n">
-        <v>95.29000000000001</v>
+        <v>100.62</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>16.42</v>
+        <v>17.64</v>
       </c>
       <c r="K31" t="n">
-        <v>93.61</v>
+        <v>100.54</v>
       </c>
       <c r="L31" t="n">
-        <v>95.04000000000001</v>
+        <v>102.07</v>
       </c>
     </row>
     <row r="32">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>72.94</v>
+        <v>74.17</v>
       </c>
       <c r="K33" t="n">
-        <v>59.01</v>
+        <v>60</v>
       </c>
       <c r="L33" t="n">
-        <v>93.81999999999999</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-154.79</v>
+        <v>-166.08</v>
       </c>
       <c r="K35" t="n">
-        <v>116.32</v>
+        <v>124.81</v>
       </c>
       <c r="L35" t="n">
-        <v>193.63</v>
+        <v>207.75</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-163.82</v>
+        <v>-181.36</v>
       </c>
       <c r="K36" t="n">
-        <v>-158.62</v>
+        <v>-175.6</v>
       </c>
       <c r="L36" t="n">
-        <v>228.03</v>
+        <v>252.44</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="K37" t="n">
-        <v>-32.24</v>
+        <v>-34.07</v>
       </c>
       <c r="L37" t="n">
-        <v>32.27</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-48.18</v>
+        <v>-50.04</v>
       </c>
       <c r="K38" t="n">
-        <v>-187.86</v>
+        <v>-195.12</v>
       </c>
       <c r="L38" t="n">
-        <v>193.94</v>
+        <v>201.44</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-214.09</v>
+        <v>-218.29</v>
       </c>
       <c r="K39" t="n">
-        <v>-95.91</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>234.59</v>
+        <v>239.19</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-146.31</v>
+        <v>-154.79</v>
       </c>
       <c r="K40" t="n">
-        <v>-151.13</v>
+        <v>-159.89</v>
       </c>
       <c r="L40" t="n">
-        <v>210.35</v>
+        <v>222.54</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>308.66</v>
+        <v>331.53</v>
       </c>
       <c r="K41" t="n">
-        <v>109.51</v>
+        <v>117.62</v>
       </c>
       <c r="L41" t="n">
-        <v>327.51</v>
+        <v>351.77</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>135.48</v>
+        <v>150.6</v>
       </c>
       <c r="K42" t="n">
-        <v>-262.03</v>
+        <v>-291.27</v>
       </c>
       <c r="L42" t="n">
-        <v>294.98</v>
+        <v>327.9</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-13.05</v>
+        <v>-14.48</v>
       </c>
       <c r="K43" t="n">
-        <v>-380.61</v>
+        <v>-422.36</v>
       </c>
       <c r="L43" t="n">
-        <v>380.83</v>
+        <v>422.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-55.75</v>
+        <v>-57.89</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.4</v>
+        <v>-61.69</v>
       </c>
       <c r="L44" t="n">
-        <v>81.45999999999999</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>16.33</v>
+        <v>17.47</v>
       </c>
       <c r="K45" t="n">
-        <v>13.07</v>
+        <v>13.98</v>
       </c>
       <c r="L45" t="n">
-        <v>20.92</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>7.46</v>
+        <v>7.44</v>
       </c>
       <c r="K46" t="n">
-        <v>-70.76000000000001</v>
+        <v>-70.64</v>
       </c>
       <c r="L46" t="n">
-        <v>71.15000000000001</v>
+        <v>71.03</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-76.48999999999999</v>
+        <v>-84.59999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-89.51000000000001</v>
+        <v>-99</v>
       </c>
       <c r="L47" t="n">
-        <v>117.74</v>
+        <v>130.22</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-107.63</v>
+        <v>-111.72</v>
       </c>
       <c r="K48" t="n">
-        <v>24.76</v>
+        <v>25.7</v>
       </c>
       <c r="L48" t="n">
-        <v>110.44</v>
+        <v>114.64</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-97.51000000000001</v>
+        <v>-107.95</v>
       </c>
       <c r="K49" t="n">
-        <v>76.09</v>
+        <v>84.25</v>
       </c>
       <c r="L49" t="n">
-        <v>123.68</v>
+        <v>136.93</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-21.05</v>
+        <v>-22.22</v>
       </c>
       <c r="K50" t="n">
-        <v>-185.89</v>
+        <v>-196.18</v>
       </c>
       <c r="L50" t="n">
-        <v>187.08</v>
+        <v>197.43</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-57.56</v>
+        <v>-61.82</v>
       </c>
       <c r="K51" t="n">
-        <v>-109.25</v>
+        <v>-117.33</v>
       </c>
       <c r="L51" t="n">
-        <v>123.49</v>
+        <v>132.62</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>216.31</v>
+        <v>239.49</v>
       </c>
       <c r="K52" t="n">
-        <v>113.96</v>
+        <v>126.17</v>
       </c>
       <c r="L52" t="n">
-        <v>244.5</v>
+        <v>270.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>12.29</v>
+        <v>13.2</v>
       </c>
       <c r="K53" t="n">
-        <v>143.37</v>
+        <v>153.99</v>
       </c>
       <c r="L53" t="n">
-        <v>143.89</v>
+        <v>154.55</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-206.15</v>
+        <v>-221.65</v>
       </c>
       <c r="K54" t="n">
-        <v>15.44</v>
+        <v>16.6</v>
       </c>
       <c r="L54" t="n">
-        <v>206.73</v>
+        <v>222.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>18.98</v>
+        <v>20.7</v>
       </c>
       <c r="K55" t="n">
-        <v>-282.87</v>
+        <v>-308.58</v>
       </c>
       <c r="L55" t="n">
-        <v>283.51</v>
+        <v>309.28</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>197.91</v>
+        <v>201.24</v>
       </c>
       <c r="K56" t="n">
-        <v>-220.16</v>
+        <v>-223.86</v>
       </c>
       <c r="L56" t="n">
-        <v>296.04</v>
+        <v>301.01</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>145.44</v>
+        <v>148.62</v>
       </c>
       <c r="K57" t="n">
-        <v>-253.1</v>
+        <v>-258.63</v>
       </c>
       <c r="L57" t="n">
-        <v>291.91</v>
+        <v>298.29</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>39.51</v>
+        <v>43.28</v>
       </c>
       <c r="K58" t="n">
-        <v>57.69</v>
+        <v>63.2</v>
       </c>
       <c r="L58" t="n">
-        <v>69.92</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>29.26</v>
+        <v>32.36</v>
       </c>
       <c r="K59" t="n">
-        <v>-87.22</v>
+        <v>-96.45</v>
       </c>
       <c r="L59" t="n">
-        <v>92</v>
+        <v>101.74</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>40.06</v>
+        <v>41.43</v>
       </c>
       <c r="K60" t="n">
-        <v>62.14</v>
+        <v>64.28</v>
       </c>
       <c r="L60" t="n">
-        <v>73.94</v>
+        <v>76.47</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.19</v>
+        <v>-12.37</v>
       </c>
       <c r="K61" t="n">
-        <v>-88.01000000000001</v>
+        <v>-97.34</v>
       </c>
       <c r="L61" t="n">
-        <v>88.72</v>
+        <v>98.12</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>167.02</v>
+        <v>178.75</v>
       </c>
       <c r="K62" t="n">
-        <v>68.48999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="L62" t="n">
-        <v>180.52</v>
+        <v>193.19</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-13.56</v>
+        <v>-14.03</v>
       </c>
       <c r="K63" t="n">
-        <v>32.41</v>
+        <v>33.55</v>
       </c>
       <c r="L63" t="n">
-        <v>35.13</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-122.15</v>
+        <v>-122.01</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.71</v>
+        <v>-14.7</v>
       </c>
       <c r="L64" t="n">
-        <v>123.03</v>
+        <v>122.89</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-21.21</v>
+        <v>-21.19</v>
       </c>
       <c r="K65" t="n">
-        <v>-153.57</v>
+        <v>-153.4</v>
       </c>
       <c r="L65" t="n">
-        <v>155.03</v>
+        <v>154.86</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>40.01</v>
+        <v>40.75</v>
       </c>
       <c r="K66" t="n">
-        <v>96.20999999999999</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>104.2</v>
+        <v>106.12</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>7.57</v>
+        <v>7.56</v>
       </c>
       <c r="K67" t="n">
-        <v>104.3</v>
+        <v>104.21</v>
       </c>
       <c r="L67" t="n">
-        <v>104.57</v>
+        <v>104.48</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-226.55</v>
+        <v>-226.65</v>
       </c>
       <c r="K68" t="n">
-        <v>-64.34</v>
+        <v>-64.36</v>
       </c>
       <c r="L68" t="n">
-        <v>235.51</v>
+        <v>235.61</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-205.47</v>
+        <v>-205.66</v>
       </c>
       <c r="K69" t="n">
-        <v>-53.83</v>
+        <v>-53.88</v>
       </c>
       <c r="L69" t="n">
-        <v>212.4</v>
+        <v>212.6</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-249.56</v>
+        <v>-249.58</v>
       </c>
       <c r="K70" t="n">
-        <v>-95.78</v>
+        <v>-95.79000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>267.31</v>
+        <v>267.33</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>61.12</v>
+        <v>67.97</v>
       </c>
       <c r="K71" t="n">
-        <v>-281.66</v>
+        <v>-313.22</v>
       </c>
       <c r="L71" t="n">
-        <v>288.21</v>
+        <v>320.51</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>189.36</v>
+        <v>200.15</v>
       </c>
       <c r="K72" t="n">
-        <v>-194.52</v>
+        <v>-205.6</v>
       </c>
       <c r="L72" t="n">
-        <v>271.47</v>
+        <v>286.94</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-250.32</v>
+        <v>-264.49</v>
       </c>
       <c r="K73" t="n">
-        <v>132.33</v>
+        <v>139.82</v>
       </c>
       <c r="L73" t="n">
-        <v>283.15</v>
+        <v>299.17</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>81.77</v>
+        <v>87.66</v>
       </c>
       <c r="K74" t="n">
-        <v>43.16</v>
+        <v>46.27</v>
       </c>
       <c r="L74" t="n">
-        <v>92.45999999999999</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-71.73</v>
+        <v>-78.06999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>28.71</v>
+        <v>31.25</v>
       </c>
       <c r="L75" t="n">
-        <v>77.26000000000001</v>
+        <v>84.09</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>74.52</v>
+        <v>82.5</v>
       </c>
       <c r="K76" t="n">
-        <v>36.84</v>
+        <v>40.79</v>
       </c>
       <c r="L76" t="n">
-        <v>83.13</v>
+        <v>92.04000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>120.55</v>
+        <v>120</v>
       </c>
       <c r="K77" t="n">
-        <v>-13.48</v>
+        <v>-13.42</v>
       </c>
       <c r="L77" t="n">
-        <v>121.3</v>
+        <v>120.75</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-70.75</v>
+        <v>-72.13</v>
       </c>
       <c r="K78" t="n">
-        <v>54.6</v>
+        <v>55.67</v>
       </c>
       <c r="L78" t="n">
-        <v>89.36</v>
+        <v>91.12</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>128.04</v>
+        <v>141.74</v>
       </c>
       <c r="K79" t="n">
-        <v>-28.85</v>
+        <v>-31.94</v>
       </c>
       <c r="L79" t="n">
-        <v>131.25</v>
+        <v>145.29</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-169.18</v>
+        <v>-184.43</v>
       </c>
       <c r="K80" t="n">
-        <v>-33.11</v>
+        <v>-36.1</v>
       </c>
       <c r="L80" t="n">
-        <v>172.39</v>
+        <v>187.93</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>120.44</v>
+        <v>122.78</v>
       </c>
       <c r="K81" t="n">
-        <v>38.68</v>
+        <v>39.43</v>
       </c>
       <c r="L81" t="n">
-        <v>126.5</v>
+        <v>128.95</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>87.70999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="K82" t="n">
-        <v>-102.64</v>
+        <v>-102.55</v>
       </c>
       <c r="L82" t="n">
-        <v>135.01</v>
+        <v>134.89</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>116.7</v>
+        <v>119.09</v>
       </c>
       <c r="K83" t="n">
-        <v>90.92</v>
+        <v>92.78</v>
       </c>
       <c r="L83" t="n">
-        <v>147.94</v>
+        <v>150.97</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-168.38</v>
+        <v>-178.08</v>
       </c>
       <c r="K84" t="n">
-        <v>-81.37</v>
+        <v>-86.06</v>
       </c>
       <c r="L84" t="n">
-        <v>187.02</v>
+        <v>197.78</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.52</v>
+        <v>-13.45</v>
       </c>
       <c r="K85" t="n">
-        <v>-191.41</v>
+        <v>-205.68</v>
       </c>
       <c r="L85" t="n">
-        <v>191.82</v>
+        <v>206.12</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-306.73</v>
+        <v>-341.8</v>
       </c>
       <c r="K86" t="n">
-        <v>126.52</v>
+        <v>140.98</v>
       </c>
       <c r="L86" t="n">
-        <v>331.8</v>
+        <v>369.73</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>158.95</v>
+        <v>162.06</v>
       </c>
       <c r="K87" t="n">
-        <v>-206.93</v>
+        <v>-210.98</v>
       </c>
       <c r="L87" t="n">
-        <v>260.93</v>
+        <v>266.04</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-83.41</v>
+        <v>-85.05</v>
       </c>
       <c r="K88" t="n">
-        <v>336.12</v>
+        <v>342.71</v>
       </c>
       <c r="L88" t="n">
-        <v>346.32</v>
+        <v>353.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.37</v>
+        <v>2.71</v>
       </c>
       <c r="F14" t="n">
-        <v>5.74</v>
+        <v>8.65</v>
       </c>
       <c r="G14" t="n">
-        <v>216</v>
+        <v>196.6</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>77.5</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.53</v>
+        <v>-27.66</v>
       </c>
       <c r="K14" t="n">
-        <v>-51.25</v>
+        <v>46.21</v>
       </c>
       <c r="L14" t="n">
-        <v>51.25</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:18:42</t>
+          <t>06:19:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="F15" t="n">
-        <v>9.31</v>
+        <v>13.22</v>
       </c>
       <c r="G15" t="n">
-        <v>202</v>
+        <v>217.9</v>
       </c>
       <c r="H15" t="n">
-        <v>93.5</v>
+        <v>41.4</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.99</v>
+        <v>-56.71</v>
       </c>
       <c r="K15" t="n">
-        <v>-84.45</v>
+        <v>-17.09</v>
       </c>
       <c r="L15" t="n">
-        <v>84.47</v>
+        <v>59.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:20:53</t>
+          <t>06:21:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="F16" t="n">
-        <v>6.86</v>
+        <v>10.31</v>
       </c>
       <c r="G16" t="n">
-        <v>217.4</v>
+        <v>218.6</v>
       </c>
       <c r="H16" t="n">
-        <v>97.40000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-53.73</v>
+        <v>53.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-47.27</v>
+        <v>19.34</v>
       </c>
       <c r="L16" t="n">
-        <v>71.56</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:24:44</t>
+          <t>06:25:48</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.36</v>
+        <v>3.22</v>
       </c>
       <c r="F17" t="n">
-        <v>7.69</v>
+        <v>13.09</v>
       </c>
       <c r="G17" t="n">
-        <v>221.6</v>
+        <v>209.7</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>52.7</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>29.37</v>
+        <v>-114.31</v>
       </c>
       <c r="K17" t="n">
-        <v>132.08</v>
+        <v>-3.21</v>
       </c>
       <c r="L17" t="n">
-        <v>135.3</v>
+        <v>114.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:27:07</t>
+          <t>06:27:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="F18" t="n">
-        <v>10.92</v>
+        <v>11.69</v>
       </c>
       <c r="G18" t="n">
-        <v>204.9</v>
+        <v>222</v>
       </c>
       <c r="H18" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>110.66</v>
+        <v>-34.85</v>
       </c>
       <c r="K18" t="n">
-        <v>-74.62</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>133.47</v>
+        <v>36.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:28:52</t>
+          <t>06:28:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>10.51</v>
+        <v>11.7</v>
       </c>
       <c r="G19" t="n">
-        <v>209.1</v>
+        <v>222.6</v>
       </c>
       <c r="H19" t="n">
-        <v>96.7</v>
+        <v>61.6</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>96.89</v>
+        <v>-48.21</v>
       </c>
       <c r="K19" t="n">
-        <v>-14.5</v>
+        <v>-84.90000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>97.95999999999999</v>
+        <v>97.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:33:20</t>
+          <t>06:33:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.07</v>
+        <v>3.58</v>
       </c>
       <c r="F20" t="n">
-        <v>9.84</v>
+        <v>13.18</v>
       </c>
       <c r="G20" t="n">
-        <v>209.8</v>
+        <v>214.3</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>50.2</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-23.94</v>
+        <v>-148.01</v>
       </c>
       <c r="K20" t="n">
-        <v>-147.88</v>
+        <v>53.43</v>
       </c>
       <c r="L20" t="n">
-        <v>149.8</v>
+        <v>157.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:35:37</t>
+          <t>06:34:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="F21" t="n">
-        <v>12.15</v>
+        <v>5.94</v>
       </c>
       <c r="G21" t="n">
-        <v>217.8</v>
+        <v>220</v>
       </c>
       <c r="H21" t="n">
-        <v>96.40000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-151.99</v>
+        <v>62.41</v>
       </c>
       <c r="K21" t="n">
-        <v>175.99</v>
+        <v>-80.90000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>232.54</v>
+        <v>102.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:37:28</t>
+          <t>06:36:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="F22" t="n">
-        <v>8.24</v>
+        <v>9.81</v>
       </c>
       <c r="G22" t="n">
-        <v>208.3</v>
+        <v>205.4</v>
       </c>
       <c r="H22" t="n">
-        <v>99.09999999999999</v>
+        <v>44.1</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-107.65</v>
+        <v>-112.88</v>
       </c>
       <c r="K22" t="n">
-        <v>93.98999999999999</v>
+        <v>73.08</v>
       </c>
       <c r="L22" t="n">
-        <v>142.91</v>
+        <v>134.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:42:21</t>
+          <t>06:41:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.51</v>
+        <v>3.15</v>
       </c>
       <c r="F23" t="n">
-        <v>3.92</v>
+        <v>13.22</v>
       </c>
       <c r="G23" t="n">
-        <v>228.1</v>
+        <v>217</v>
       </c>
       <c r="H23" t="n">
-        <v>96.5</v>
+        <v>82.8</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-141.96</v>
+        <v>-101.28</v>
       </c>
       <c r="K23" t="n">
-        <v>29.35</v>
+        <v>123.26</v>
       </c>
       <c r="L23" t="n">
-        <v>144.96</v>
+        <v>159.53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:44:30</t>
+          <t>06:43:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.96</v>
+        <v>2.57</v>
       </c>
       <c r="F24" t="n">
-        <v>8.359999999999999</v>
+        <v>11.27</v>
       </c>
       <c r="G24" t="n">
-        <v>226.9</v>
+        <v>214</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>48.8</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-12.85</v>
+        <v>-107.57</v>
       </c>
       <c r="K24" t="n">
-        <v>-152.61</v>
+        <v>-102.88</v>
       </c>
       <c r="L24" t="n">
-        <v>153.15</v>
+        <v>148.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:46:40</t>
+          <t>06:44:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.34</v>
+        <v>3.12</v>
       </c>
       <c r="F25" t="n">
-        <v>11.69</v>
+        <v>12.32</v>
       </c>
       <c r="G25" t="n">
-        <v>207.6</v>
+        <v>216.3</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>84.8</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-232.44</v>
+        <v>-54.41</v>
       </c>
       <c r="K25" t="n">
-        <v>53.99</v>
+        <v>-161.2</v>
       </c>
       <c r="L25" t="n">
-        <v>238.63</v>
+        <v>170.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:51:29</t>
+          <t>06:49:37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.14</v>
+        <v>3.95</v>
       </c>
       <c r="F26" t="n">
-        <v>8.48</v>
+        <v>13.22</v>
       </c>
       <c r="G26" t="n">
-        <v>226.6</v>
+        <v>220.6</v>
       </c>
       <c r="H26" t="n">
-        <v>97</v>
+        <v>55.4</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>98.52</v>
+        <v>295.24</v>
       </c>
       <c r="K26" t="n">
-        <v>-323.87</v>
+        <v>-69.06</v>
       </c>
       <c r="L26" t="n">
-        <v>338.52</v>
+        <v>303.21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:52:26</t>
+          <t>06:50:41</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.08</v>
+        <v>3.72</v>
       </c>
       <c r="F27" t="n">
-        <v>8.51</v>
+        <v>10.89</v>
       </c>
       <c r="G27" t="n">
-        <v>232.3</v>
+        <v>210.7</v>
       </c>
       <c r="H27" t="n">
-        <v>93.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-121.6</v>
+        <v>249.21</v>
       </c>
       <c r="K27" t="n">
-        <v>-181.29</v>
+        <v>46.52</v>
       </c>
       <c r="L27" t="n">
-        <v>218.3</v>
+        <v>253.51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:53:51</t>
+          <t>06:52:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.1</v>
+        <v>2.22</v>
       </c>
       <c r="F28" t="n">
-        <v>11.7</v>
+        <v>9.76</v>
       </c>
       <c r="G28" t="n">
-        <v>215.3</v>
+        <v>211.6</v>
       </c>
       <c r="H28" t="n">
-        <v>98.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-218.14</v>
+        <v>-216.37</v>
       </c>
       <c r="K28" t="n">
-        <v>-98.94</v>
+        <v>167.16</v>
       </c>
       <c r="L28" t="n">
-        <v>239.54</v>
+        <v>273.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:02:19</t>
+          <t>07:03:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="F29" t="n">
-        <v>7.52</v>
+        <v>10.07</v>
       </c>
       <c r="G29" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>63.75</v>
+        <v>18.37</v>
       </c>
       <c r="K29" t="n">
-        <v>-55.66</v>
+        <v>30.74</v>
       </c>
       <c r="L29" t="n">
-        <v>84.63</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:04:46</t>
+          <t>07:05:02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="F30" t="n">
-        <v>13.22</v>
+        <v>11.53</v>
       </c>
       <c r="G30" t="n">
-        <v>215.2</v>
+        <v>218.4</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>66.29000000000001</v>
+        <v>-78.04000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>75.7</v>
+        <v>-14.19</v>
       </c>
       <c r="L30" t="n">
-        <v>100.62</v>
+        <v>79.31999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:06:16</t>
+          <t>07:06:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="F31" t="n">
-        <v>13.22</v>
+        <v>8.44</v>
       </c>
       <c r="G31" t="n">
-        <v>232.9</v>
+        <v>220.1</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>17.64</v>
+        <v>-37.83</v>
       </c>
       <c r="K31" t="n">
-        <v>100.54</v>
+        <v>36.72</v>
       </c>
       <c r="L31" t="n">
-        <v>102.07</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:11:07</t>
+          <t>07:10:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="F32" t="n">
-        <v>8.75</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>207.5</v>
+        <v>226.8</v>
       </c>
       <c r="H32" t="n">
-        <v>90.8</v>
+        <v>90</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>31.97</v>
+        <v>-35.43</v>
       </c>
       <c r="K32" t="n">
-        <v>-85.06</v>
+        <v>-83.02</v>
       </c>
       <c r="L32" t="n">
-        <v>90.87</v>
+        <v>90.26000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:13:42</t>
+          <t>07:12:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="F33" t="n">
-        <v>13.07</v>
+        <v>12.41</v>
       </c>
       <c r="G33" t="n">
-        <v>227.5</v>
+        <v>233.9</v>
       </c>
       <c r="H33" t="n">
-        <v>98.7</v>
+        <v>53.5</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>74.17</v>
+        <v>-54.18</v>
       </c>
       <c r="K33" t="n">
-        <v>60</v>
+        <v>66.97</v>
       </c>
       <c r="L33" t="n">
-        <v>95.40000000000001</v>
+        <v>86.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:14:45</t>
+          <t>07:14:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.77</v>
+        <v>3.31</v>
       </c>
       <c r="F34" t="n">
-        <v>6.99</v>
+        <v>10.94</v>
       </c>
       <c r="G34" t="n">
-        <v>217.5</v>
+        <v>217.3</v>
       </c>
       <c r="H34" t="n">
-        <v>97.90000000000001</v>
+        <v>38</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-65.17</v>
+        <v>-49.49</v>
       </c>
       <c r="K34" t="n">
-        <v>-26.4</v>
+        <v>81.33</v>
       </c>
       <c r="L34" t="n">
-        <v>70.31999999999999</v>
+        <v>95.20999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:20:06</t>
+          <t>07:19:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
       <c r="F35" t="n">
-        <v>12.77</v>
+        <v>9.02</v>
       </c>
       <c r="G35" t="n">
-        <v>214.5</v>
+        <v>212.3</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-166.08</v>
+        <v>-105.51</v>
       </c>
       <c r="K35" t="n">
-        <v>124.81</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>207.75</v>
+        <v>125.03</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:21:39</t>
+          <t>07:21:42</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.29</v>
+        <v>3.11</v>
       </c>
       <c r="F36" t="n">
-        <v>12.62</v>
+        <v>12.74</v>
       </c>
       <c r="G36" t="n">
-        <v>215.4</v>
+        <v>215.1</v>
       </c>
       <c r="H36" t="n">
-        <v>93.3</v>
+        <v>31.4</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-181.36</v>
+        <v>94.28</v>
       </c>
       <c r="K36" t="n">
-        <v>-175.6</v>
+        <v>-39.77</v>
       </c>
       <c r="L36" t="n">
-        <v>252.44</v>
+        <v>102.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:23:48</t>
+          <t>07:22:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="F37" t="n">
-        <v>9.140000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>234.8</v>
+        <v>217.6</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>1.45</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-34.07</v>
+        <v>-25.98</v>
       </c>
       <c r="L37" t="n">
-        <v>34.1</v>
+        <v>96.45999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:29:29</t>
+          <t>07:26:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="F38" t="n">
-        <v>13.22</v>
+        <v>10.99</v>
       </c>
       <c r="G38" t="n">
-        <v>224.5</v>
+        <v>223.2</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>39.3</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-50.04</v>
+        <v>-126.85</v>
       </c>
       <c r="K38" t="n">
-        <v>-195.12</v>
+        <v>149.18</v>
       </c>
       <c r="L38" t="n">
-        <v>201.44</v>
+        <v>195.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:30:50</t>
+          <t>07:29:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.13</v>
+        <v>3.86</v>
       </c>
       <c r="F39" t="n">
-        <v>8.25</v>
+        <v>9.82</v>
       </c>
       <c r="G39" t="n">
-        <v>223.1</v>
+        <v>216.6</v>
       </c>
       <c r="H39" t="n">
-        <v>93.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-218.29</v>
+        <v>-186.49</v>
       </c>
       <c r="K39" t="n">
-        <v>-97.79000000000001</v>
+        <v>41.95</v>
       </c>
       <c r="L39" t="n">
-        <v>239.19</v>
+        <v>191.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:32:34</t>
+          <t>07:30:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.35</v>
+        <v>2.73</v>
       </c>
       <c r="F40" t="n">
-        <v>13.2</v>
+        <v>6.39</v>
       </c>
       <c r="G40" t="n">
-        <v>220.2</v>
+        <v>214.8</v>
       </c>
       <c r="H40" t="n">
-        <v>99.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-154.79</v>
+        <v>-124.76</v>
       </c>
       <c r="K40" t="n">
-        <v>-159.89</v>
+        <v>15.49</v>
       </c>
       <c r="L40" t="n">
-        <v>222.54</v>
+        <v>125.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:37:25</t>
+          <t>07:35:48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="F41" t="n">
-        <v>8.890000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="G41" t="n">
-        <v>207.5</v>
+        <v>224.9</v>
       </c>
       <c r="H41" t="n">
-        <v>97.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>331.53</v>
+        <v>-22.36</v>
       </c>
       <c r="K41" t="n">
-        <v>117.62</v>
+        <v>217.12</v>
       </c>
       <c r="L41" t="n">
-        <v>351.77</v>
+        <v>218.27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:39:55</t>
+          <t>07:37:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="F42" t="n">
-        <v>13.12</v>
+        <v>10.04</v>
       </c>
       <c r="G42" t="n">
-        <v>213</v>
+        <v>210.9</v>
       </c>
       <c r="H42" t="n">
-        <v>98.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>150.6</v>
+        <v>-52.27</v>
       </c>
       <c r="K42" t="n">
-        <v>-291.27</v>
+        <v>-259.66</v>
       </c>
       <c r="L42" t="n">
-        <v>327.9</v>
+        <v>264.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:41:29</t>
+          <t>07:38:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="F43" t="n">
-        <v>10.57</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>218.4</v>
+        <v>214.6</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>80.2</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-14.48</v>
+        <v>2.18</v>
       </c>
       <c r="K43" t="n">
-        <v>-422.36</v>
+        <v>-237.39</v>
       </c>
       <c r="L43" t="n">
-        <v>422.61</v>
+        <v>237.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:50:46</t>
+          <t>07:47:49</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="F44" t="n">
-        <v>10.46</v>
+        <v>11.68</v>
       </c>
       <c r="G44" t="n">
-        <v>224.1</v>
+        <v>218.8</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>69.2</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-57.89</v>
+        <v>-35.46</v>
       </c>
       <c r="K44" t="n">
-        <v>-61.69</v>
+        <v>-66.22</v>
       </c>
       <c r="L44" t="n">
-        <v>84.59999999999999</v>
+        <v>75.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:53:20</t>
+          <t>07:49:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.1</v>
+        <v>3.49</v>
       </c>
       <c r="F45" t="n">
-        <v>13.22</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>219.9</v>
+        <v>222.1</v>
       </c>
       <c r="H45" t="n">
-        <v>93.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>17.47</v>
+        <v>-62.22</v>
       </c>
       <c r="K45" t="n">
-        <v>13.98</v>
+        <v>10.61</v>
       </c>
       <c r="L45" t="n">
-        <v>22.38</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:54:14</t>
+          <t>07:51:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.59</v>
+        <v>2.76</v>
       </c>
       <c r="F46" t="n">
-        <v>9.93</v>
+        <v>10.47</v>
       </c>
       <c r="G46" t="n">
-        <v>215.1</v>
+        <v>220.4</v>
       </c>
       <c r="H46" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>7.44</v>
+        <v>-2.35</v>
       </c>
       <c r="K46" t="n">
-        <v>-70.64</v>
+        <v>-43.83</v>
       </c>
       <c r="L46" t="n">
-        <v>71.03</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:57:53</t>
+          <t>07:55:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="F47" t="n">
-        <v>11.88</v>
+        <v>13.2</v>
       </c>
       <c r="G47" t="n">
-        <v>215.6</v>
+        <v>205.7</v>
       </c>
       <c r="H47" t="n">
-        <v>89.59999999999999</v>
+        <v>46.3</v>
       </c>
       <c r="I47" t="n">
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-84.59999999999999</v>
+        <v>-74.86</v>
       </c>
       <c r="K47" t="n">
-        <v>-99</v>
+        <v>-2.85</v>
       </c>
       <c r="L47" t="n">
-        <v>130.22</v>
+        <v>74.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:00:11</t>
+          <t>07:56:21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="F48" t="n">
-        <v>10.29</v>
+        <v>13.22</v>
       </c>
       <c r="G48" t="n">
-        <v>222.6</v>
+        <v>225.6</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>-111.72</v>
+        <v>77.25</v>
       </c>
       <c r="K48" t="n">
-        <v>25.7</v>
+        <v>-43.71</v>
       </c>
       <c r="L48" t="n">
-        <v>114.64</v>
+        <v>88.76000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:02:15</t>
+          <t>07:57:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.06</v>
+        <v>3.51</v>
       </c>
       <c r="F49" t="n">
-        <v>11.32</v>
+        <v>8.73</v>
       </c>
       <c r="G49" t="n">
-        <v>229.3</v>
+        <v>222.4</v>
       </c>
       <c r="H49" t="n">
-        <v>99.3</v>
+        <v>47.4</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-107.95</v>
+        <v>-54.42</v>
       </c>
       <c r="K49" t="n">
-        <v>84.25</v>
+        <v>73.67</v>
       </c>
       <c r="L49" t="n">
-        <v>136.93</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:07:00</t>
+          <t>08:03:06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2140,31 +2140,31 @@
         <v>3.96</v>
       </c>
       <c r="F50" t="n">
-        <v>9.85</v>
+        <v>13.22</v>
       </c>
       <c r="G50" t="n">
-        <v>224.2</v>
+        <v>207.2</v>
       </c>
       <c r="H50" t="n">
-        <v>99</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-22.22</v>
+        <v>54.72</v>
       </c>
       <c r="K50" t="n">
-        <v>-196.18</v>
+        <v>-186.84</v>
       </c>
       <c r="L50" t="n">
-        <v>197.43</v>
+        <v>194.69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:09:18</t>
+          <t>08:04:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="F51" t="n">
-        <v>10.13</v>
+        <v>10.71</v>
       </c>
       <c r="G51" t="n">
-        <v>227.2</v>
+        <v>219.5</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>45.8</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-61.82</v>
+        <v>-73.05</v>
       </c>
       <c r="K51" t="n">
-        <v>-117.33</v>
+        <v>-3.03</v>
       </c>
       <c r="L51" t="n">
-        <v>132.62</v>
+        <v>73.11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:10:27</t>
+          <t>08:06:09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.24</v>
+        <v>3.74</v>
       </c>
       <c r="F52" t="n">
-        <v>12.17</v>
+        <v>11.47</v>
       </c>
       <c r="G52" t="n">
-        <v>228.7</v>
+        <v>211.5</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>69.3</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>239.49</v>
+        <v>-66.5</v>
       </c>
       <c r="K52" t="n">
-        <v>126.17</v>
+        <v>-90.45999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>270.69</v>
+        <v>112.27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:15:37</t>
+          <t>08:10:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.2</v>
+        <v>3.87</v>
       </c>
       <c r="F53" t="n">
-        <v>6.96</v>
+        <v>13.22</v>
       </c>
       <c r="G53" t="n">
-        <v>242.6</v>
+        <v>218.8</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>89.7</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>13.2</v>
+        <v>35.79</v>
       </c>
       <c r="K53" t="n">
-        <v>153.99</v>
+        <v>-157.23</v>
       </c>
       <c r="L53" t="n">
-        <v>154.55</v>
+        <v>161.25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:16:46</t>
+          <t>08:12:18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.17</v>
+        <v>2.92</v>
       </c>
       <c r="F54" t="n">
-        <v>13.22</v>
+        <v>12.85</v>
       </c>
       <c r="G54" t="n">
-        <v>210.9</v>
+        <v>226.6</v>
       </c>
       <c r="H54" t="n">
-        <v>97</v>
+        <v>74.3</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-221.65</v>
+        <v>-86.68000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>16.6</v>
+        <v>54.83</v>
       </c>
       <c r="L54" t="n">
-        <v>222.28</v>
+        <v>102.57</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:19:01</t>
+          <t>08:13:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.84</v>
+        <v>3.37</v>
       </c>
       <c r="F55" t="n">
-        <v>11.15</v>
+        <v>9.99</v>
       </c>
       <c r="G55" t="n">
-        <v>231.7</v>
+        <v>234.2</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>20.7</v>
+        <v>114.02</v>
       </c>
       <c r="K55" t="n">
-        <v>-308.58</v>
+        <v>-131.73</v>
       </c>
       <c r="L55" t="n">
-        <v>309.28</v>
+        <v>174.22</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:24:22</t>
+          <t>08:18:37</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.75</v>
+        <v>3.37</v>
       </c>
       <c r="F56" t="n">
-        <v>13.22</v>
+        <v>11.82</v>
       </c>
       <c r="G56" t="n">
-        <v>218.3</v>
+        <v>223.6</v>
       </c>
       <c r="H56" t="n">
-        <v>96.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>201.24</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-223.86</v>
+        <v>-259.51</v>
       </c>
       <c r="L56" t="n">
-        <v>301.01</v>
+        <v>274.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:25:44</t>
+          <t>08:20:51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="F57" t="n">
         <v>13.22</v>
       </c>
       <c r="G57" t="n">
-        <v>243.1</v>
+        <v>208.8</v>
       </c>
       <c r="H57" t="n">
-        <v>97.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>148.62</v>
+        <v>-46.94</v>
       </c>
       <c r="K57" t="n">
-        <v>-258.63</v>
+        <v>-193.69</v>
       </c>
       <c r="L57" t="n">
-        <v>298.29</v>
+        <v>199.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:27:09</t>
+          <t>08:21:34</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.76</v>
+        <v>4.07</v>
       </c>
       <c r="F58" t="n">
-        <v>10.97</v>
+        <v>13.22</v>
       </c>
       <c r="G58" t="n">
-        <v>235.2</v>
+        <v>218.4</v>
       </c>
       <c r="H58" t="n">
-        <v>97.8</v>
+        <v>58.9</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>43.28</v>
+        <v>-195.69</v>
       </c>
       <c r="K58" t="n">
-        <v>63.2</v>
+        <v>73.19</v>
       </c>
       <c r="L58" t="n">
-        <v>76.59999999999999</v>
+        <v>208.93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:35:13</t>
+          <t>08:34:18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="F59" t="n">
-        <v>13.22</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>222.2</v>
+        <v>222.1</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>46.4</v>
       </c>
       <c r="I59" t="n">
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>32.36</v>
+        <v>3.96</v>
       </c>
       <c r="K59" t="n">
-        <v>-96.45</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>101.74</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:36:43</t>
+          <t>08:35:41</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.08</v>
+        <v>3.39</v>
       </c>
       <c r="F60" t="n">
-        <v>13.22</v>
+        <v>8.85</v>
       </c>
       <c r="G60" t="n">
-        <v>222.3</v>
+        <v>226.9</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>2.3</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>41.43</v>
+        <v>46.18</v>
       </c>
       <c r="K60" t="n">
-        <v>64.28</v>
+        <v>38.63</v>
       </c>
       <c r="L60" t="n">
-        <v>76.47</v>
+        <v>60.21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:38:14</t>
+          <t>08:36:44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.47</v>
+        <v>3.69</v>
       </c>
       <c r="F61" t="n">
-        <v>9.51</v>
+        <v>11.71</v>
       </c>
       <c r="G61" t="n">
-        <v>225.3</v>
+        <v>214</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>58.8</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.37</v>
+        <v>58.3</v>
       </c>
       <c r="K61" t="n">
-        <v>-97.34</v>
+        <v>-57.42</v>
       </c>
       <c r="L61" t="n">
-        <v>98.12</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:43:19</t>
+          <t>08:42:35</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="F62" t="n">
-        <v>13.22</v>
+        <v>12.74</v>
       </c>
       <c r="G62" t="n">
-        <v>223.4</v>
+        <v>224.4</v>
       </c>
       <c r="H62" t="n">
-        <v>93.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>178.75</v>
+        <v>35.98</v>
       </c>
       <c r="K62" t="n">
-        <v>73.3</v>
+        <v>-86.15000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>193.19</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:45:21</t>
+          <t>08:43:47</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.94</v>
+        <v>3.23</v>
       </c>
       <c r="F63" t="n">
         <v>13.22</v>
       </c>
       <c r="G63" t="n">
-        <v>222.9</v>
+        <v>223.4</v>
       </c>
       <c r="H63" t="n">
-        <v>97.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.03</v>
+        <v>-109.27</v>
       </c>
       <c r="K63" t="n">
-        <v>33.55</v>
+        <v>52.86</v>
       </c>
       <c r="L63" t="n">
-        <v>36.36</v>
+        <v>121.38</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:47:21</t>
+          <t>08:45:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.48</v>
+        <v>3.29</v>
       </c>
       <c r="F64" t="n">
-        <v>11.9</v>
+        <v>13.22</v>
       </c>
       <c r="G64" t="n">
-        <v>234.5</v>
+        <v>213.9</v>
       </c>
       <c r="H64" t="n">
-        <v>92.2</v>
+        <v>31.1</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-122.01</v>
+        <v>-85.56999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.7</v>
+        <v>-40.71</v>
       </c>
       <c r="L64" t="n">
-        <v>122.89</v>
+        <v>94.76000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:52:49</t>
+          <t>08:49:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.88</v>
+        <v>2.93</v>
       </c>
       <c r="F65" t="n">
-        <v>11.78</v>
+        <v>10.77</v>
       </c>
       <c r="G65" t="n">
-        <v>216.8</v>
+        <v>225.2</v>
       </c>
       <c r="H65" t="n">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-21.19</v>
+        <v>-78.77</v>
       </c>
       <c r="K65" t="n">
-        <v>-153.4</v>
+        <v>-65.73</v>
       </c>
       <c r="L65" t="n">
-        <v>154.86</v>
+        <v>102.59</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:53:34</t>
+          <t>08:51:17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="F66" t="n">
-        <v>11.68</v>
+        <v>12.84</v>
       </c>
       <c r="G66" t="n">
-        <v>216.9</v>
+        <v>218</v>
       </c>
       <c r="H66" t="n">
-        <v>95.40000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>40.75</v>
+        <v>126.05</v>
       </c>
       <c r="K66" t="n">
-        <v>97.98999999999999</v>
+        <v>24</v>
       </c>
       <c r="L66" t="n">
-        <v>106.12</v>
+        <v>128.32</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:55:54</t>
+          <t>08:52:06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.72</v>
+        <v>3.32</v>
       </c>
       <c r="F67" t="n">
-        <v>13.22</v>
+        <v>11.84</v>
       </c>
       <c r="G67" t="n">
-        <v>233.4</v>
+        <v>207.6</v>
       </c>
       <c r="H67" t="n">
-        <v>91.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>7.56</v>
+        <v>-82.3</v>
       </c>
       <c r="K67" t="n">
-        <v>104.21</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>104.48</v>
+        <v>121.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:00:57</t>
+          <t>08:57:34</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="F68" t="n">
-        <v>12.06</v>
+        <v>13.12</v>
       </c>
       <c r="G68" t="n">
-        <v>216.1</v>
+        <v>214.6</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-226.65</v>
+        <v>-206.1</v>
       </c>
       <c r="K68" t="n">
-        <v>-64.36</v>
+        <v>-115.79</v>
       </c>
       <c r="L68" t="n">
-        <v>235.61</v>
+        <v>236.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:01:55</t>
+          <t>08:58:38</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.04</v>
+        <v>3.72</v>
       </c>
       <c r="F69" t="n">
-        <v>11.47</v>
+        <v>13.22</v>
       </c>
       <c r="G69" t="n">
-        <v>232.7</v>
+        <v>224.9</v>
       </c>
       <c r="H69" t="n">
-        <v>95.7</v>
+        <v>72.7</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-205.66</v>
+        <v>124.52</v>
       </c>
       <c r="K69" t="n">
-        <v>-53.88</v>
+        <v>176.61</v>
       </c>
       <c r="L69" t="n">
-        <v>212.6</v>
+        <v>216.09</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:03:01</t>
+          <t>09:00:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="F70" t="n">
-        <v>11.56</v>
+        <v>13.22</v>
       </c>
       <c r="G70" t="n">
-        <v>219.6</v>
+        <v>215.5</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>52.9</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-249.58</v>
+        <v>-105.2</v>
       </c>
       <c r="K70" t="n">
-        <v>-95.79000000000001</v>
+        <v>178.78</v>
       </c>
       <c r="L70" t="n">
-        <v>267.33</v>
+        <v>207.43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:07:59</t>
+          <t>09:04:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="F71" t="n">
         <v>13.22</v>
       </c>
       <c r="G71" t="n">
-        <v>217.1</v>
+        <v>227.5</v>
       </c>
       <c r="H71" t="n">
-        <v>99.09999999999999</v>
+        <v>49.2</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>67.97</v>
+        <v>-103.71</v>
       </c>
       <c r="K71" t="n">
-        <v>-313.22</v>
+        <v>-309.29</v>
       </c>
       <c r="L71" t="n">
-        <v>320.51</v>
+        <v>326.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:09:09</t>
+          <t>09:07:21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.29</v>
+        <v>3.98</v>
       </c>
       <c r="F72" t="n">
         <v>13.22</v>
       </c>
       <c r="G72" t="n">
-        <v>229.2</v>
+        <v>222.6</v>
       </c>
       <c r="H72" t="n">
-        <v>98.3</v>
+        <v>67.8</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>200.15</v>
+        <v>226.6</v>
       </c>
       <c r="K72" t="n">
-        <v>-205.6</v>
+        <v>-164.77</v>
       </c>
       <c r="L72" t="n">
-        <v>286.94</v>
+        <v>280.17</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:10:30</t>
+          <t>09:08:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.1</v>
+        <v>3.73</v>
       </c>
       <c r="F73" t="n">
-        <v>11.27</v>
+        <v>13.22</v>
       </c>
       <c r="G73" t="n">
-        <v>222.8</v>
+        <v>221.2</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>56.9</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-264.49</v>
+        <v>-320.11</v>
       </c>
       <c r="K73" t="n">
-        <v>139.82</v>
+        <v>-12.01</v>
       </c>
       <c r="L73" t="n">
-        <v>299.17</v>
+        <v>320.33</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:23:47</t>
+          <t>09:19:22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.63</v>
+        <v>3.44</v>
       </c>
       <c r="F74" t="n">
-        <v>13.22</v>
+        <v>12.28</v>
       </c>
       <c r="G74" t="n">
-        <v>219.4</v>
+        <v>212.6</v>
       </c>
       <c r="H74" t="n">
-        <v>100</v>
+        <v>85.5</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>87.66</v>
+        <v>-10.25</v>
       </c>
       <c r="K74" t="n">
-        <v>46.27</v>
+        <v>-65.51000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>99.12</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:24:44</t>
+          <t>09:20:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="F75" t="n">
-        <v>12.19</v>
+        <v>12.75</v>
       </c>
       <c r="G75" t="n">
-        <v>220.6</v>
+        <v>211.9</v>
       </c>
       <c r="H75" t="n">
-        <v>91.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-78.06999999999999</v>
+        <v>-82.5</v>
       </c>
       <c r="K75" t="n">
-        <v>31.25</v>
+        <v>-10.95</v>
       </c>
       <c r="L75" t="n">
-        <v>84.09</v>
+        <v>83.22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:26:50</t>
+          <t>09:23:17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="F76" t="n">
-        <v>8.800000000000001</v>
+        <v>12.73</v>
       </c>
       <c r="G76" t="n">
-        <v>211.9</v>
+        <v>212.6</v>
       </c>
       <c r="H76" t="n">
-        <v>94.5</v>
+        <v>92.2</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>82.5</v>
+        <v>-6.68</v>
       </c>
       <c r="K76" t="n">
-        <v>40.79</v>
+        <v>-40.62</v>
       </c>
       <c r="L76" t="n">
-        <v>92.04000000000001</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:32:55</t>
+          <t>09:28:56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="F77" t="n">
-        <v>13.22</v>
+        <v>11.43</v>
       </c>
       <c r="G77" t="n">
-        <v>229.2</v>
+        <v>211.3</v>
       </c>
       <c r="H77" t="n">
-        <v>99.2</v>
+        <v>10.6</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>120</v>
+        <v>84.39</v>
       </c>
       <c r="K77" t="n">
-        <v>-13.42</v>
+        <v>-81.29000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>120.75</v>
+        <v>117.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:34:24</t>
+          <t>09:31:19</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="F78" t="n">
-        <v>11.23</v>
+        <v>10.86</v>
       </c>
       <c r="G78" t="n">
-        <v>203.9</v>
+        <v>222.2</v>
       </c>
       <c r="H78" t="n">
-        <v>95.5</v>
+        <v>48</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-72.13</v>
+        <v>-32.07</v>
       </c>
       <c r="K78" t="n">
-        <v>55.67</v>
+        <v>-53.65</v>
       </c>
       <c r="L78" t="n">
-        <v>91.12</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:35:54</t>
+          <t>09:32:02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.27</v>
+        <v>4.01</v>
       </c>
       <c r="F79" t="n">
-        <v>12.8</v>
+        <v>13.22</v>
       </c>
       <c r="G79" t="n">
-        <v>205.7</v>
+        <v>220.6</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>56.2</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>141.74</v>
+        <v>-103.42</v>
       </c>
       <c r="K79" t="n">
-        <v>-31.94</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>145.29</v>
+        <v>103.73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:41:00</t>
+          <t>09:37:10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.65</v>
+        <v>4.07</v>
       </c>
       <c r="F80" t="n">
         <v>13.22</v>
       </c>
       <c r="G80" t="n">
-        <v>210.3</v>
+        <v>230.1</v>
       </c>
       <c r="H80" t="n">
-        <v>97.3</v>
+        <v>48.8</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-184.43</v>
+        <v>-191.17</v>
       </c>
       <c r="K80" t="n">
-        <v>-36.1</v>
+        <v>29.92</v>
       </c>
       <c r="L80" t="n">
-        <v>187.93</v>
+        <v>193.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:41:45</t>
+          <t>09:38:12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.37</v>
+        <v>4.28</v>
       </c>
       <c r="F81" t="n">
-        <v>9.98</v>
+        <v>13.22</v>
       </c>
       <c r="G81" t="n">
-        <v>205.1</v>
+        <v>206.5</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>122.78</v>
+        <v>30.56</v>
       </c>
       <c r="K81" t="n">
-        <v>39.43</v>
+        <v>-180.01</v>
       </c>
       <c r="L81" t="n">
-        <v>128.95</v>
+        <v>182.59</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:43:52</t>
+          <t>09:39:53</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.73</v>
+        <v>3.48</v>
       </c>
       <c r="F82" t="n">
-        <v>13.22</v>
+        <v>11.4</v>
       </c>
       <c r="G82" t="n">
-        <v>226.1</v>
+        <v>219.6</v>
       </c>
       <c r="H82" t="n">
-        <v>91.3</v>
+        <v>7.5</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>87.63</v>
+        <v>112.55</v>
       </c>
       <c r="K82" t="n">
-        <v>-102.55</v>
+        <v>-62.85</v>
       </c>
       <c r="L82" t="n">
-        <v>134.89</v>
+        <v>128.91</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:49:41</t>
+          <t>09:44:08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.96</v>
+        <v>3.39</v>
       </c>
       <c r="F83" t="n">
         <v>13.22</v>
       </c>
       <c r="G83" t="n">
-        <v>219.4</v>
+        <v>239.6</v>
       </c>
       <c r="H83" t="n">
-        <v>91.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>119.09</v>
+        <v>-159.86</v>
       </c>
       <c r="K83" t="n">
-        <v>92.78</v>
+        <v>-47.09</v>
       </c>
       <c r="L83" t="n">
-        <v>150.97</v>
+        <v>166.65</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:51:47</t>
+          <t>09:46:10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="F84" t="n">
-        <v>13.22</v>
+        <v>12.42</v>
       </c>
       <c r="G84" t="n">
-        <v>217.8</v>
+        <v>223.1</v>
       </c>
       <c r="H84" t="n">
-        <v>96</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-178.08</v>
+        <v>-139.37</v>
       </c>
       <c r="K84" t="n">
-        <v>-86.06</v>
+        <v>-268.98</v>
       </c>
       <c r="L84" t="n">
-        <v>197.78</v>
+        <v>302.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:53:42</t>
+          <t>09:46:54</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3610,31 +3610,31 @@
         <v>3.61</v>
       </c>
       <c r="F85" t="n">
-        <v>12.78</v>
+        <v>12.23</v>
       </c>
       <c r="G85" t="n">
-        <v>223.6</v>
+        <v>224</v>
       </c>
       <c r="H85" t="n">
-        <v>93.90000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.45</v>
+        <v>150.18</v>
       </c>
       <c r="K85" t="n">
-        <v>-205.68</v>
+        <v>198</v>
       </c>
       <c r="L85" t="n">
-        <v>206.12</v>
+        <v>248.51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:58:17</t>
+          <t>09:52:27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="F86" t="n">
-        <v>12.73</v>
+        <v>12.84</v>
       </c>
       <c r="G86" t="n">
-        <v>231.9</v>
+        <v>224.2</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>60.6</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-341.8</v>
+        <v>-298.13</v>
       </c>
       <c r="K86" t="n">
-        <v>140.98</v>
+        <v>-169.89</v>
       </c>
       <c r="L86" t="n">
-        <v>369.73</v>
+        <v>343.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:59:52</t>
+          <t>09:54:02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="F87" t="n">
-        <v>9.69</v>
+        <v>12.37</v>
       </c>
       <c r="G87" t="n">
-        <v>218</v>
+        <v>226.9</v>
       </c>
       <c r="H87" t="n">
-        <v>95.5</v>
+        <v>86.7</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>162.06</v>
+        <v>163.79</v>
       </c>
       <c r="K87" t="n">
-        <v>-210.98</v>
+        <v>-304.7</v>
       </c>
       <c r="L87" t="n">
-        <v>266.04</v>
+        <v>345.93</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:01:00</t>
+          <t>09:55:35</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.2</v>
+        <v>4.86</v>
       </c>
       <c r="F88" t="n">
-        <v>13.03</v>
+        <v>13.22</v>
       </c>
       <c r="G88" t="n">
-        <v>230.3</v>
+        <v>212.7</v>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>46.2</v>
       </c>
       <c r="I88" t="n">
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-85.05</v>
+        <v>-387.04</v>
       </c>
       <c r="K88" t="n">
-        <v>342.71</v>
+        <v>73.61</v>
       </c>
       <c r="L88" t="n">
-        <v>353.11</v>
+        <v>393.98</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.71</v>
+        <v>3.03</v>
       </c>
       <c r="F14" t="n">
-        <v>8.65</v>
+        <v>8.41</v>
       </c>
       <c r="G14" t="n">
-        <v>196.6</v>
+        <v>220.6</v>
       </c>
       <c r="H14" t="n">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-27.66</v>
+        <v>-56.35</v>
       </c>
       <c r="K14" t="n">
-        <v>46.21</v>
+        <v>-6.45</v>
       </c>
       <c r="L14" t="n">
-        <v>53.85</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:19:33</t>
+          <t>06:20:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>13.22</v>
+        <v>4.76</v>
       </c>
       <c r="G15" t="n">
-        <v>217.9</v>
+        <v>211.2</v>
       </c>
       <c r="H15" t="n">
-        <v>41.4</v>
+        <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-56.71</v>
+        <v>-75.81</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.09</v>
+        <v>-0.17</v>
       </c>
       <c r="L15" t="n">
-        <v>59.23</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:21:33</t>
+          <t>06:21:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.86</v>
+        <v>3.51</v>
       </c>
       <c r="F16" t="n">
-        <v>10.31</v>
+        <v>10.04</v>
       </c>
       <c r="G16" t="n">
-        <v>218.6</v>
+        <v>226.9</v>
       </c>
       <c r="H16" t="n">
-        <v>61.9</v>
+        <v>81.3</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J16" t="n">
-        <v>53.44</v>
+        <v>45.86</v>
       </c>
       <c r="K16" t="n">
-        <v>19.34</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>56.83</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:25:48</t>
+          <t>06:26:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,28 +751,28 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="F17" t="n">
-        <v>13.09</v>
+        <v>9.31</v>
       </c>
       <c r="G17" t="n">
-        <v>209.7</v>
+        <v>213.2</v>
       </c>
       <c r="H17" t="n">
-        <v>52.7</v>
+        <v>72.8</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>-114.31</v>
+        <v>84.09</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.21</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>114.35</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="18">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="F18" t="n">
-        <v>11.69</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>52.9</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-34.85</v>
+        <v>32.48</v>
       </c>
       <c r="K18" t="n">
-        <v>-9.140000000000001</v>
+        <v>-58.01</v>
       </c>
       <c r="L18" t="n">
-        <v>36.03</v>
+        <v>66.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:28:37</t>
+          <t>06:28:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="F19" t="n">
-        <v>11.7</v>
+        <v>8.68</v>
       </c>
       <c r="G19" t="n">
-        <v>222.6</v>
+        <v>228.4</v>
       </c>
       <c r="H19" t="n">
-        <v>61.6</v>
+        <v>46.1</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-48.21</v>
+        <v>-43.46</v>
       </c>
       <c r="K19" t="n">
-        <v>-84.90000000000001</v>
+        <v>41.08</v>
       </c>
       <c r="L19" t="n">
-        <v>97.63</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:33:19</t>
+          <t>06:32:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.58</v>
+        <v>3.01</v>
       </c>
       <c r="F20" t="n">
-        <v>13.18</v>
+        <v>13.22</v>
       </c>
       <c r="G20" t="n">
-        <v>214.3</v>
+        <v>222.9</v>
       </c>
       <c r="H20" t="n">
-        <v>50.2</v>
+        <v>34.9</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-148.01</v>
+        <v>-66.7</v>
       </c>
       <c r="K20" t="n">
-        <v>53.43</v>
+        <v>-76.56</v>
       </c>
       <c r="L20" t="n">
-        <v>157.36</v>
+        <v>101.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:34:40</t>
+          <t>06:34:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="F21" t="n">
-        <v>5.94</v>
+        <v>13.22</v>
       </c>
       <c r="G21" t="n">
-        <v>220</v>
+        <v>236.7</v>
       </c>
       <c r="H21" t="n">
-        <v>53.6</v>
+        <v>27.1</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>62.41</v>
+        <v>-9.77</v>
       </c>
       <c r="K21" t="n">
-        <v>-80.90000000000001</v>
+        <v>-115.8</v>
       </c>
       <c r="L21" t="n">
-        <v>102.17</v>
+        <v>116.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:36:01</t>
+          <t>06:35:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.72</v>
+        <v>3.49</v>
       </c>
       <c r="F22" t="n">
-        <v>9.81</v>
+        <v>13.12</v>
       </c>
       <c r="G22" t="n">
-        <v>205.4</v>
+        <v>233.1</v>
       </c>
       <c r="H22" t="n">
-        <v>44.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-112.88</v>
+        <v>-15.35</v>
       </c>
       <c r="K22" t="n">
-        <v>73.08</v>
+        <v>102.96</v>
       </c>
       <c r="L22" t="n">
-        <v>134.47</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:41:54</t>
+          <t>06:40:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="F23" t="n">
-        <v>13.22</v>
+        <v>7.65</v>
       </c>
       <c r="G23" t="n">
-        <v>217</v>
+        <v>226.4</v>
       </c>
       <c r="H23" t="n">
-        <v>82.8</v>
+        <v>61.6</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-101.28</v>
+        <v>-228.9</v>
       </c>
       <c r="K23" t="n">
-        <v>123.26</v>
+        <v>116.15</v>
       </c>
       <c r="L23" t="n">
-        <v>159.53</v>
+        <v>256.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:43:11</t>
+          <t>06:43:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.57</v>
+        <v>3.15</v>
       </c>
       <c r="F24" t="n">
-        <v>11.27</v>
+        <v>12.93</v>
       </c>
       <c r="G24" t="n">
-        <v>214</v>
+        <v>225.2</v>
       </c>
       <c r="H24" t="n">
-        <v>48.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-107.57</v>
+        <v>-22.57</v>
       </c>
       <c r="K24" t="n">
-        <v>-102.88</v>
+        <v>-165.71</v>
       </c>
       <c r="L24" t="n">
-        <v>148.85</v>
+        <v>167.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:44:43</t>
+          <t>06:44:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="F25" t="n">
-        <v>12.32</v>
+        <v>10.39</v>
       </c>
       <c r="G25" t="n">
-        <v>216.3</v>
+        <v>219.6</v>
       </c>
       <c r="H25" t="n">
-        <v>84.8</v>
+        <v>66.3</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>-54.41</v>
+        <v>171.44</v>
       </c>
       <c r="K25" t="n">
-        <v>-161.2</v>
+        <v>74.92</v>
       </c>
       <c r="L25" t="n">
-        <v>170.13</v>
+        <v>187.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:49:37</t>
+          <t>06:50:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="F26" t="n">
         <v>13.22</v>
       </c>
       <c r="G26" t="n">
-        <v>220.6</v>
+        <v>226.9</v>
       </c>
       <c r="H26" t="n">
-        <v>55.4</v>
+        <v>71.2</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>295.24</v>
+        <v>146.65</v>
       </c>
       <c r="K26" t="n">
-        <v>-69.06</v>
+        <v>-169.51</v>
       </c>
       <c r="L26" t="n">
-        <v>303.21</v>
+        <v>224.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:50:41</t>
+          <t>06:51:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.72</v>
+        <v>3.82</v>
       </c>
       <c r="F27" t="n">
-        <v>10.89</v>
+        <v>13.22</v>
       </c>
       <c r="G27" t="n">
-        <v>210.7</v>
+        <v>220</v>
       </c>
       <c r="H27" t="n">
-        <v>76.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>249.21</v>
+        <v>195.26</v>
       </c>
       <c r="K27" t="n">
-        <v>46.52</v>
+        <v>-100.44</v>
       </c>
       <c r="L27" t="n">
-        <v>253.51</v>
+        <v>219.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:52:57</t>
+          <t>06:53:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.22</v>
+        <v>3.51</v>
       </c>
       <c r="F28" t="n">
-        <v>9.76</v>
+        <v>10.71</v>
       </c>
       <c r="G28" t="n">
-        <v>211.6</v>
+        <v>222.3</v>
       </c>
       <c r="H28" t="n">
-        <v>51.8</v>
+        <v>57.9</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-216.37</v>
+        <v>87.37</v>
       </c>
       <c r="K28" t="n">
-        <v>167.16</v>
+        <v>224.91</v>
       </c>
       <c r="L28" t="n">
-        <v>273.42</v>
+        <v>241.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:03:33</t>
+          <t>07:03:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.56</v>
+        <v>3.72</v>
       </c>
       <c r="F29" t="n">
-        <v>10.07</v>
+        <v>13.01</v>
       </c>
       <c r="G29" t="n">
-        <v>210</v>
+        <v>223.9</v>
       </c>
       <c r="H29" t="n">
-        <v>58.3</v>
+        <v>67.8</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>18.37</v>
+        <v>7.53</v>
       </c>
       <c r="K29" t="n">
-        <v>30.74</v>
+        <v>-76.37</v>
       </c>
       <c r="L29" t="n">
-        <v>35.82</v>
+        <v>76.73999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:05:02</t>
+          <t>07:05:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>11.53</v>
+        <v>8.58</v>
       </c>
       <c r="G30" t="n">
-        <v>218.4</v>
+        <v>223</v>
       </c>
       <c r="H30" t="n">
-        <v>66.90000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-78.04000000000001</v>
+        <v>-46.37</v>
       </c>
       <c r="K30" t="n">
-        <v>-14.19</v>
+        <v>6.62</v>
       </c>
       <c r="L30" t="n">
-        <v>79.31999999999999</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:06:57</t>
+          <t>07:06:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="F31" t="n">
-        <v>8.44</v>
+        <v>10.64</v>
       </c>
       <c r="G31" t="n">
-        <v>220.1</v>
+        <v>222.5</v>
       </c>
       <c r="H31" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-37.83</v>
+        <v>-15.82</v>
       </c>
       <c r="K31" t="n">
-        <v>36.72</v>
+        <v>51.04</v>
       </c>
       <c r="L31" t="n">
-        <v>52.72</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:10:50</t>
+          <t>07:11:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="F32" t="n">
-        <v>9.880000000000001</v>
+        <v>6.23</v>
       </c>
       <c r="G32" t="n">
-        <v>226.8</v>
+        <v>223.8</v>
       </c>
       <c r="H32" t="n">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-35.43</v>
+        <v>51.39</v>
       </c>
       <c r="K32" t="n">
-        <v>-83.02</v>
+        <v>28.88</v>
       </c>
       <c r="L32" t="n">
-        <v>90.26000000000001</v>
+        <v>58.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:12:39</t>
+          <t>07:12:29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.71</v>
+        <v>3.25</v>
       </c>
       <c r="F33" t="n">
-        <v>12.41</v>
+        <v>10.88</v>
       </c>
       <c r="G33" t="n">
-        <v>233.9</v>
+        <v>225.6</v>
       </c>
       <c r="H33" t="n">
-        <v>53.5</v>
+        <v>37.9</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-54.18</v>
+        <v>-57.76</v>
       </c>
       <c r="K33" t="n">
-        <v>66.97</v>
+        <v>-47.79</v>
       </c>
       <c r="L33" t="n">
-        <v>86.14</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:14:37</t>
+          <t>07:13:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="F34" t="n">
-        <v>10.94</v>
+        <v>8.93</v>
       </c>
       <c r="G34" t="n">
-        <v>217.3</v>
+        <v>218</v>
       </c>
       <c r="H34" t="n">
-        <v>38</v>
+        <v>62.5</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>-49.49</v>
+        <v>3.07</v>
       </c>
       <c r="K34" t="n">
-        <v>81.33</v>
+        <v>32.98</v>
       </c>
       <c r="L34" t="n">
-        <v>95.20999999999999</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:19:46</t>
+          <t>07:17:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="F35" t="n">
-        <v>9.02</v>
+        <v>11.3</v>
       </c>
       <c r="G35" t="n">
-        <v>212.3</v>
+        <v>226.2</v>
       </c>
       <c r="H35" t="n">
-        <v>66.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-105.51</v>
+        <v>-26.24</v>
       </c>
       <c r="K35" t="n">
-        <v>67.06999999999999</v>
+        <v>-94.97</v>
       </c>
       <c r="L35" t="n">
-        <v>125.03</v>
+        <v>98.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:21:42</t>
+          <t>07:20:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.11</v>
+        <v>3.78</v>
       </c>
       <c r="F36" t="n">
-        <v>12.74</v>
+        <v>12.2</v>
       </c>
       <c r="G36" t="n">
-        <v>215.1</v>
+        <v>216.8</v>
       </c>
       <c r="H36" t="n">
-        <v>31.4</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>94.28</v>
+        <v>-65.20999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-39.77</v>
+        <v>-146.26</v>
       </c>
       <c r="L36" t="n">
-        <v>102.33</v>
+        <v>160.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:22:51</t>
+          <t>07:21:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.78</v>
+        <v>3.54</v>
       </c>
       <c r="F37" t="n">
-        <v>8.630000000000001</v>
+        <v>13.22</v>
       </c>
       <c r="G37" t="n">
-        <v>217.6</v>
+        <v>204.3</v>
       </c>
       <c r="H37" t="n">
-        <v>57</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>92.90000000000001</v>
+        <v>118.29</v>
       </c>
       <c r="K37" t="n">
-        <v>-25.98</v>
+        <v>-86.56999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>96.45999999999999</v>
+        <v>146.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:26:48</t>
+          <t>07:25:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1636,31 +1636,31 @@
         <v>2.89</v>
       </c>
       <c r="F38" t="n">
-        <v>10.99</v>
+        <v>8.91</v>
       </c>
       <c r="G38" t="n">
-        <v>223.2</v>
+        <v>214.4</v>
       </c>
       <c r="H38" t="n">
-        <v>39.3</v>
+        <v>67.7</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-126.85</v>
+        <v>98.44</v>
       </c>
       <c r="K38" t="n">
-        <v>149.18</v>
+        <v>-180.37</v>
       </c>
       <c r="L38" t="n">
-        <v>195.82</v>
+        <v>205.48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:29:14</t>
+          <t>07:26:44</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.86</v>
+        <v>3.27</v>
       </c>
       <c r="F39" t="n">
-        <v>9.82</v>
+        <v>6.69</v>
       </c>
       <c r="G39" t="n">
-        <v>216.6</v>
+        <v>219.8</v>
       </c>
       <c r="H39" t="n">
-        <v>88.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-186.49</v>
+        <v>61.46</v>
       </c>
       <c r="K39" t="n">
-        <v>41.95</v>
+        <v>-187.86</v>
       </c>
       <c r="L39" t="n">
-        <v>191.15</v>
+        <v>197.66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:30:22</t>
+          <t>07:28:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.73</v>
+        <v>3.11</v>
       </c>
       <c r="F40" t="n">
-        <v>6.39</v>
+        <v>12.47</v>
       </c>
       <c r="G40" t="n">
-        <v>214.8</v>
+        <v>235.7</v>
       </c>
       <c r="H40" t="n">
-        <v>92.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>-124.76</v>
+        <v>-185.87</v>
       </c>
       <c r="K40" t="n">
-        <v>15.49</v>
+        <v>-29.57</v>
       </c>
       <c r="L40" t="n">
-        <v>125.72</v>
+        <v>188.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:35:48</t>
+          <t>07:34:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.83</v>
+        <v>4.09</v>
       </c>
       <c r="F41" t="n">
-        <v>8.09</v>
+        <v>13.22</v>
       </c>
       <c r="G41" t="n">
-        <v>224.9</v>
+        <v>222.3</v>
       </c>
       <c r="H41" t="n">
-        <v>82.2</v>
+        <v>59.1</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.36</v>
+        <v>-55.59</v>
       </c>
       <c r="K41" t="n">
-        <v>217.12</v>
+        <v>-347.88</v>
       </c>
       <c r="L41" t="n">
-        <v>218.27</v>
+        <v>352.29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:37:53</t>
+          <t>07:36:05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="F42" t="n">
-        <v>10.04</v>
+        <v>13.22</v>
       </c>
       <c r="G42" t="n">
-        <v>210.9</v>
+        <v>224</v>
       </c>
       <c r="H42" t="n">
-        <v>76</v>
+        <v>29.6</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-52.27</v>
+        <v>33.9</v>
       </c>
       <c r="K42" t="n">
-        <v>-259.66</v>
+        <v>281.78</v>
       </c>
       <c r="L42" t="n">
-        <v>264.87</v>
+        <v>283.81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:38:53</t>
+          <t>07:38:21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="F43" t="n">
-        <v>9.630000000000001</v>
+        <v>12.15</v>
       </c>
       <c r="G43" t="n">
-        <v>214.6</v>
+        <v>226.7</v>
       </c>
       <c r="H43" t="n">
-        <v>80.2</v>
+        <v>70.8</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>2.18</v>
+        <v>-87.09</v>
       </c>
       <c r="K43" t="n">
-        <v>-237.39</v>
+        <v>-118.58</v>
       </c>
       <c r="L43" t="n">
-        <v>237.4</v>
+        <v>147.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:47:49</t>
+          <t>07:46:57</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="F44" t="n">
-        <v>11.68</v>
+        <v>9.4</v>
       </c>
       <c r="G44" t="n">
-        <v>218.8</v>
+        <v>208.7</v>
       </c>
       <c r="H44" t="n">
-        <v>69.2</v>
+        <v>47.2</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-35.46</v>
+        <v>-43.72</v>
       </c>
       <c r="K44" t="n">
-        <v>-66.22</v>
+        <v>3.5</v>
       </c>
       <c r="L44" t="n">
-        <v>75.12</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:49:32</t>
+          <t>07:48:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="F45" t="n">
-        <v>8.390000000000001</v>
+        <v>13.22</v>
       </c>
       <c r="G45" t="n">
-        <v>222.1</v>
+        <v>224.8</v>
       </c>
       <c r="H45" t="n">
-        <v>88.90000000000001</v>
+        <v>32.7</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>-62.22</v>
+        <v>-53.01</v>
       </c>
       <c r="K45" t="n">
-        <v>10.61</v>
+        <v>-34.86</v>
       </c>
       <c r="L45" t="n">
-        <v>63.12</v>
+        <v>63.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:51:01</t>
+          <t>07:50:17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="F46" t="n">
-        <v>10.47</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>220.4</v>
+        <v>205.1</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>53.4</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.35</v>
+        <v>20.04</v>
       </c>
       <c r="K46" t="n">
-        <v>-43.83</v>
+        <v>-37.12</v>
       </c>
       <c r="L46" t="n">
-        <v>43.9</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:55:11</t>
+          <t>07:55:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="F47" t="n">
-        <v>13.2</v>
+        <v>11.29</v>
       </c>
       <c r="G47" t="n">
-        <v>205.7</v>
+        <v>222.5</v>
       </c>
       <c r="H47" t="n">
-        <v>46.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-74.86</v>
+        <v>17.42</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.85</v>
+        <v>55.94</v>
       </c>
       <c r="L47" t="n">
-        <v>74.91</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:56:21</t>
+          <t>07:57:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.35</v>
+        <v>2.48</v>
       </c>
       <c r="F48" t="n">
-        <v>13.22</v>
+        <v>7.41</v>
       </c>
       <c r="G48" t="n">
-        <v>225.6</v>
+        <v>233.6</v>
       </c>
       <c r="H48" t="n">
-        <v>21</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>77.25</v>
+        <v>-17.85</v>
       </c>
       <c r="K48" t="n">
-        <v>-43.71</v>
+        <v>-57.75</v>
       </c>
       <c r="L48" t="n">
-        <v>88.76000000000001</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:57:43</t>
+          <t>07:59:24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.51</v>
+        <v>3.99</v>
       </c>
       <c r="F49" t="n">
-        <v>8.73</v>
+        <v>13.22</v>
       </c>
       <c r="G49" t="n">
-        <v>222.4</v>
+        <v>219.5</v>
       </c>
       <c r="H49" t="n">
-        <v>47.4</v>
+        <v>40</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>-54.42</v>
+        <v>-34.84</v>
       </c>
       <c r="K49" t="n">
-        <v>73.67</v>
+        <v>76.19</v>
       </c>
       <c r="L49" t="n">
-        <v>91.59999999999999</v>
+        <v>83.78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:03:06</t>
+          <t>08:03:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="F50" t="n">
         <v>13.22</v>
       </c>
       <c r="G50" t="n">
-        <v>207.2</v>
+        <v>211.2</v>
       </c>
       <c r="H50" t="n">
-        <v>67.59999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>54.72</v>
+        <v>137.65</v>
       </c>
       <c r="K50" t="n">
-        <v>-186.84</v>
+        <v>50.78</v>
       </c>
       <c r="L50" t="n">
-        <v>194.69</v>
+        <v>146.72</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:04:28</t>
+          <t>08:05:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.72</v>
+        <v>2.47</v>
       </c>
       <c r="F51" t="n">
-        <v>10.71</v>
+        <v>10.99</v>
       </c>
       <c r="G51" t="n">
-        <v>219.5</v>
+        <v>231.3</v>
       </c>
       <c r="H51" t="n">
-        <v>45.8</v>
+        <v>40.2</v>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-73.05</v>
+        <v>-55.88</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.03</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>73.11</v>
+        <v>110.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:06:09</t>
+          <t>08:06:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.74</v>
+        <v>2.8</v>
       </c>
       <c r="F52" t="n">
-        <v>11.47</v>
+        <v>7.96</v>
       </c>
       <c r="G52" t="n">
-        <v>211.5</v>
+        <v>220.3</v>
       </c>
       <c r="H52" t="n">
-        <v>69.3</v>
+        <v>78.5</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-66.5</v>
+        <v>-88.31999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-90.45999999999999</v>
+        <v>33.12</v>
       </c>
       <c r="L52" t="n">
-        <v>112.27</v>
+        <v>94.33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:10:23</t>
+          <t>08:11:39</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.87</v>
+        <v>3.5</v>
       </c>
       <c r="F53" t="n">
-        <v>13.22</v>
+        <v>12.01</v>
       </c>
       <c r="G53" t="n">
-        <v>218.8</v>
+        <v>222.2</v>
       </c>
       <c r="H53" t="n">
-        <v>89.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>35.79</v>
+        <v>37.46</v>
       </c>
       <c r="K53" t="n">
-        <v>-157.23</v>
+        <v>-216.38</v>
       </c>
       <c r="L53" t="n">
-        <v>161.25</v>
+        <v>219.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:12:18</t>
+          <t>08:12:57</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.92</v>
+        <v>3.46</v>
       </c>
       <c r="F54" t="n">
-        <v>12.85</v>
+        <v>11.84</v>
       </c>
       <c r="G54" t="n">
-        <v>226.6</v>
+        <v>226.8</v>
       </c>
       <c r="H54" t="n">
-        <v>74.3</v>
+        <v>79</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-86.68000000000001</v>
+        <v>186.26</v>
       </c>
       <c r="K54" t="n">
-        <v>54.83</v>
+        <v>93.66</v>
       </c>
       <c r="L54" t="n">
-        <v>102.57</v>
+        <v>208.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:13:35</t>
+          <t>08:14:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="F55" t="n">
-        <v>9.99</v>
+        <v>13.22</v>
       </c>
       <c r="G55" t="n">
-        <v>234.2</v>
+        <v>228</v>
       </c>
       <c r="H55" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="I55" t="n">
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>114.02</v>
+        <v>169.67</v>
       </c>
       <c r="K55" t="n">
-        <v>-131.73</v>
+        <v>108.1</v>
       </c>
       <c r="L55" t="n">
-        <v>174.22</v>
+        <v>201.18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:18:37</t>
+          <t>08:20:38</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.37</v>
+        <v>3.63</v>
       </c>
       <c r="F56" t="n">
-        <v>11.82</v>
+        <v>13.22</v>
       </c>
       <c r="G56" t="n">
-        <v>223.6</v>
+        <v>220.8</v>
       </c>
       <c r="H56" t="n">
-        <v>64.59999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>88.51000000000001</v>
+        <v>30.36</v>
       </c>
       <c r="K56" t="n">
-        <v>-259.51</v>
+        <v>-249.94</v>
       </c>
       <c r="L56" t="n">
-        <v>274.19</v>
+        <v>251.78</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:20:51</t>
+          <t>08:21:50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="F57" t="n">
-        <v>13.22</v>
+        <v>11.96</v>
       </c>
       <c r="G57" t="n">
-        <v>208.8</v>
+        <v>219.3</v>
       </c>
       <c r="H57" t="n">
-        <v>95.8</v>
+        <v>15.6</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-46.94</v>
+        <v>-210.89</v>
       </c>
       <c r="K57" t="n">
-        <v>-193.69</v>
+        <v>52.74</v>
       </c>
       <c r="L57" t="n">
-        <v>199.3</v>
+        <v>217.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:21:34</t>
+          <t>08:23:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.07</v>
+        <v>3.1</v>
       </c>
       <c r="F58" t="n">
-        <v>13.22</v>
+        <v>8.81</v>
       </c>
       <c r="G58" t="n">
-        <v>218.4</v>
+        <v>219.9</v>
       </c>
       <c r="H58" t="n">
-        <v>58.9</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>-195.69</v>
+        <v>168.64</v>
       </c>
       <c r="K58" t="n">
-        <v>73.19</v>
+        <v>91.97</v>
       </c>
       <c r="L58" t="n">
-        <v>208.93</v>
+        <v>192.09</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:34:18</t>
+          <t>08:34:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.64</v>
+        <v>3.26</v>
       </c>
       <c r="F59" t="n">
-        <v>9.789999999999999</v>
+        <v>13.02</v>
       </c>
       <c r="G59" t="n">
-        <v>222.1</v>
+        <v>209.8</v>
       </c>
       <c r="H59" t="n">
-        <v>46.4</v>
+        <v>60.9</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>3.96</v>
+        <v>-51.09</v>
       </c>
       <c r="K59" t="n">
-        <v>77.95999999999999</v>
+        <v>-38.94</v>
       </c>
       <c r="L59" t="n">
-        <v>78.06</v>
+        <v>64.23999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:35:41</t>
+          <t>08:36:12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.39</v>
+        <v>4.58</v>
       </c>
       <c r="F60" t="n">
-        <v>8.85</v>
+        <v>13.22</v>
       </c>
       <c r="G60" t="n">
-        <v>226.9</v>
+        <v>211.8</v>
       </c>
       <c r="H60" t="n">
-        <v>2.3</v>
+        <v>83</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>46.18</v>
+        <v>-47.24</v>
       </c>
       <c r="K60" t="n">
-        <v>38.63</v>
+        <v>-64.92</v>
       </c>
       <c r="L60" t="n">
-        <v>60.21</v>
+        <v>80.29000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:36:44</t>
+          <t>08:37:49</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.69</v>
+        <v>4.16</v>
       </c>
       <c r="F61" t="n">
-        <v>11.71</v>
+        <v>13.22</v>
       </c>
       <c r="G61" t="n">
-        <v>214</v>
+        <v>235.9</v>
       </c>
       <c r="H61" t="n">
-        <v>58.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J61" t="n">
-        <v>58.3</v>
+        <v>-88.23</v>
       </c>
       <c r="K61" t="n">
-        <v>-57.42</v>
+        <v>-37.27</v>
       </c>
       <c r="L61" t="n">
-        <v>81.83</v>
+        <v>95.78</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:42:35</t>
+          <t>08:43:07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="F62" t="n">
-        <v>12.74</v>
+        <v>10.1</v>
       </c>
       <c r="G62" t="n">
-        <v>224.4</v>
+        <v>208.2</v>
       </c>
       <c r="H62" t="n">
-        <v>52.2</v>
+        <v>54.9</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>35.98</v>
+        <v>-36.61</v>
       </c>
       <c r="K62" t="n">
-        <v>-86.15000000000001</v>
+        <v>-95.45999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>93.37</v>
+        <v>102.24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:43:47</t>
+          <t>08:45:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="F63" t="n">
-        <v>13.22</v>
+        <v>10.17</v>
       </c>
       <c r="G63" t="n">
-        <v>223.4</v>
+        <v>224.6</v>
       </c>
       <c r="H63" t="n">
-        <v>78.09999999999999</v>
+        <v>36.1</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-109.27</v>
+        <v>-72.43000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>52.86</v>
+        <v>-60</v>
       </c>
       <c r="L63" t="n">
-        <v>121.38</v>
+        <v>94.05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:45:52</t>
+          <t>08:46:31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.29</v>
+        <v>3.78</v>
       </c>
       <c r="F64" t="n">
-        <v>13.22</v>
+        <v>12.2</v>
       </c>
       <c r="G64" t="n">
-        <v>213.9</v>
+        <v>226.5</v>
       </c>
       <c r="H64" t="n">
-        <v>31.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-85.56999999999999</v>
+        <v>-83.78</v>
       </c>
       <c r="K64" t="n">
-        <v>-40.71</v>
+        <v>-63.02</v>
       </c>
       <c r="L64" t="n">
-        <v>94.76000000000001</v>
+        <v>104.84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:49:59</t>
+          <t>08:51:16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.93</v>
+        <v>3.68</v>
       </c>
       <c r="F65" t="n">
-        <v>10.77</v>
+        <v>13.22</v>
       </c>
       <c r="G65" t="n">
-        <v>225.2</v>
+        <v>224.2</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-78.77</v>
+        <v>93.34</v>
       </c>
       <c r="K65" t="n">
-        <v>-65.73</v>
+        <v>-118.7</v>
       </c>
       <c r="L65" t="n">
-        <v>102.59</v>
+        <v>151</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:51:17</t>
+          <t>08:53:19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.76</v>
+        <v>4.16</v>
       </c>
       <c r="F66" t="n">
-        <v>12.84</v>
+        <v>13.22</v>
       </c>
       <c r="G66" t="n">
-        <v>218</v>
+        <v>223.1</v>
       </c>
       <c r="H66" t="n">
-        <v>62.6</v>
+        <v>64.5</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>126.05</v>
+        <v>-120.32</v>
       </c>
       <c r="K66" t="n">
-        <v>24</v>
+        <v>-68.63</v>
       </c>
       <c r="L66" t="n">
-        <v>128.32</v>
+        <v>138.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:52:06</t>
+          <t>08:55:12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="F67" t="n">
-        <v>11.84</v>
+        <v>10.55</v>
       </c>
       <c r="G67" t="n">
-        <v>207.6</v>
+        <v>231</v>
       </c>
       <c r="H67" t="n">
-        <v>74.5</v>
+        <v>74.2</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J67" t="n">
-        <v>-82.3</v>
+        <v>-108.24</v>
       </c>
       <c r="K67" t="n">
-        <v>-89.09999999999999</v>
+        <v>60.47</v>
       </c>
       <c r="L67" t="n">
-        <v>121.3</v>
+        <v>123.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:57:34</t>
+          <t>08:59:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.59</v>
+        <v>4.01</v>
       </c>
       <c r="F68" t="n">
-        <v>13.12</v>
+        <v>12.9</v>
       </c>
       <c r="G68" t="n">
-        <v>214.6</v>
+        <v>235.5</v>
       </c>
       <c r="H68" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-206.1</v>
+        <v>-188.2</v>
       </c>
       <c r="K68" t="n">
-        <v>-115.79</v>
+        <v>-262.11</v>
       </c>
       <c r="L68" t="n">
-        <v>236.4</v>
+        <v>322.68</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:58:38</t>
+          <t>09:00:49</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="F69" t="n">
         <v>13.22</v>
       </c>
       <c r="G69" t="n">
-        <v>224.9</v>
+        <v>229.8</v>
       </c>
       <c r="H69" t="n">
-        <v>72.7</v>
+        <v>62.3</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>124.52</v>
+        <v>16.08</v>
       </c>
       <c r="K69" t="n">
-        <v>176.61</v>
+        <v>158.84</v>
       </c>
       <c r="L69" t="n">
-        <v>216.09</v>
+        <v>159.65</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:00:53</t>
+          <t>09:02:48</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.44</v>
+        <v>3.97</v>
       </c>
       <c r="F70" t="n">
-        <v>13.22</v>
+        <v>12.35</v>
       </c>
       <c r="G70" t="n">
-        <v>215.5</v>
+        <v>237.2</v>
       </c>
       <c r="H70" t="n">
-        <v>52.9</v>
+        <v>60.5</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-105.2</v>
+        <v>66.28</v>
       </c>
       <c r="K70" t="n">
-        <v>178.78</v>
+        <v>-264.83</v>
       </c>
       <c r="L70" t="n">
-        <v>207.43</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:04:54</t>
+          <t>09:07:06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.87</v>
+        <v>4.11</v>
       </c>
       <c r="F71" t="n">
         <v>13.22</v>
       </c>
       <c r="G71" t="n">
-        <v>227.5</v>
+        <v>207.7</v>
       </c>
       <c r="H71" t="n">
-        <v>49.2</v>
+        <v>89</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-103.71</v>
+        <v>-328.15</v>
       </c>
       <c r="K71" t="n">
-        <v>-309.29</v>
+        <v>-0.03</v>
       </c>
       <c r="L71" t="n">
-        <v>326.22</v>
+        <v>328.15</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:07:21</t>
+          <t>09:08:58</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="F72" t="n">
-        <v>13.22</v>
+        <v>12.74</v>
       </c>
       <c r="G72" t="n">
-        <v>222.6</v>
+        <v>237.8</v>
       </c>
       <c r="H72" t="n">
-        <v>67.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>226.6</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-164.77</v>
+        <v>-183.34</v>
       </c>
       <c r="L72" t="n">
-        <v>280.17</v>
+        <v>205.96</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:08:27</t>
+          <t>09:10:39</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.73</v>
+        <v>3.18</v>
       </c>
       <c r="F73" t="n">
         <v>13.22</v>
       </c>
       <c r="G73" t="n">
-        <v>221.2</v>
+        <v>213.8</v>
       </c>
       <c r="H73" t="n">
-        <v>56.9</v>
+        <v>75.8</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>-320.11</v>
+        <v>-53.91</v>
       </c>
       <c r="K73" t="n">
-        <v>-12.01</v>
+        <v>208.36</v>
       </c>
       <c r="L73" t="n">
-        <v>320.33</v>
+        <v>215.22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:19:22</t>
+          <t>09:21:16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.44</v>
+        <v>4.08</v>
       </c>
       <c r="F74" t="n">
-        <v>12.28</v>
+        <v>13.22</v>
       </c>
       <c r="G74" t="n">
-        <v>212.6</v>
+        <v>219.4</v>
       </c>
       <c r="H74" t="n">
-        <v>85.5</v>
+        <v>40.1</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>-10.25</v>
+        <v>-78.84</v>
       </c>
       <c r="K74" t="n">
-        <v>-65.51000000000001</v>
+        <v>-16.92</v>
       </c>
       <c r="L74" t="n">
-        <v>66.3</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:20:47</t>
+          <t>09:22:11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.76</v>
+        <v>3.47</v>
       </c>
       <c r="F75" t="n">
-        <v>12.75</v>
+        <v>13.22</v>
       </c>
       <c r="G75" t="n">
-        <v>211.9</v>
+        <v>212.5</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-82.5</v>
+        <v>-66.68000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-10.95</v>
+        <v>-10.55</v>
       </c>
       <c r="L75" t="n">
-        <v>83.22</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:23:17</t>
+          <t>09:24:11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="F76" t="n">
-        <v>12.73</v>
+        <v>13.22</v>
       </c>
       <c r="G76" t="n">
-        <v>212.6</v>
+        <v>246.8</v>
       </c>
       <c r="H76" t="n">
-        <v>92.2</v>
+        <v>77.7</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.68</v>
+        <v>30.48</v>
       </c>
       <c r="K76" t="n">
-        <v>-40.62</v>
+        <v>-41.27</v>
       </c>
       <c r="L76" t="n">
-        <v>41.17</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:28:56</t>
+          <t>09:29:42</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.74</v>
+        <v>3.59</v>
       </c>
       <c r="F77" t="n">
-        <v>11.43</v>
+        <v>13.22</v>
       </c>
       <c r="G77" t="n">
-        <v>211.3</v>
+        <v>233.9</v>
       </c>
       <c r="H77" t="n">
-        <v>10.6</v>
+        <v>96.7</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>84.39</v>
+        <v>-25.54</v>
       </c>
       <c r="K77" t="n">
-        <v>-81.29000000000001</v>
+        <v>81.02</v>
       </c>
       <c r="L77" t="n">
-        <v>117.17</v>
+        <v>84.95999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:31:19</t>
+          <t>09:31:21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.15</v>
+        <v>4.19</v>
       </c>
       <c r="F78" t="n">
-        <v>10.86</v>
+        <v>13.22</v>
       </c>
       <c r="G78" t="n">
-        <v>222.2</v>
+        <v>225.7</v>
       </c>
       <c r="H78" t="n">
-        <v>48</v>
+        <v>70.3</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.07</v>
+        <v>49.07</v>
       </c>
       <c r="K78" t="n">
-        <v>-53.65</v>
+        <v>71.3</v>
       </c>
       <c r="L78" t="n">
-        <v>62.5</v>
+        <v>86.56</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:32:02</t>
+          <t>09:33:40</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="F79" t="n">
-        <v>13.22</v>
+        <v>12.93</v>
       </c>
       <c r="G79" t="n">
-        <v>220.6</v>
+        <v>225</v>
       </c>
       <c r="H79" t="n">
-        <v>56.2</v>
+        <v>33.4</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J79" t="n">
-        <v>-103.42</v>
+        <v>28.04</v>
       </c>
       <c r="K79" t="n">
-        <v>-8.029999999999999</v>
+        <v>-92.13</v>
       </c>
       <c r="L79" t="n">
-        <v>103.73</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:37:10</t>
+          <t>09:39:04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="F80" t="n">
         <v>13.22</v>
       </c>
       <c r="G80" t="n">
-        <v>230.1</v>
+        <v>217.3</v>
       </c>
       <c r="H80" t="n">
-        <v>48.8</v>
+        <v>57.3</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-191.17</v>
+        <v>131.1</v>
       </c>
       <c r="K80" t="n">
-        <v>29.92</v>
+        <v>-83.84</v>
       </c>
       <c r="L80" t="n">
-        <v>193.5</v>
+        <v>155.61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:38:12</t>
+          <t>09:39:58</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.28</v>
+        <v>3.96</v>
       </c>
       <c r="F81" t="n">
-        <v>13.22</v>
+        <v>12.65</v>
       </c>
       <c r="G81" t="n">
-        <v>206.5</v>
+        <v>218</v>
       </c>
       <c r="H81" t="n">
-        <v>65.90000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>30.56</v>
+        <v>-55.45</v>
       </c>
       <c r="K81" t="n">
-        <v>-180.01</v>
+        <v>72.87</v>
       </c>
       <c r="L81" t="n">
-        <v>182.59</v>
+        <v>91.56999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:39:53</t>
+          <t>09:41:22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="F82" t="n">
-        <v>11.4</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>219.6</v>
+        <v>228</v>
       </c>
       <c r="H82" t="n">
-        <v>7.5</v>
+        <v>78.5</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J82" t="n">
-        <v>112.55</v>
+        <v>-38.3</v>
       </c>
       <c r="K82" t="n">
-        <v>-62.85</v>
+        <v>130.05</v>
       </c>
       <c r="L82" t="n">
-        <v>128.91</v>
+        <v>135.57</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:44:08</t>
+          <t>09:45:39</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.39</v>
+        <v>3.65</v>
       </c>
       <c r="F83" t="n">
-        <v>13.22</v>
+        <v>10.26</v>
       </c>
       <c r="G83" t="n">
-        <v>239.6</v>
+        <v>219</v>
       </c>
       <c r="H83" t="n">
-        <v>88.09999999999999</v>
+        <v>28.3</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-159.86</v>
+        <v>-163.39</v>
       </c>
       <c r="K83" t="n">
-        <v>-47.09</v>
+        <v>170.39</v>
       </c>
       <c r="L83" t="n">
-        <v>166.65</v>
+        <v>236.07</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:46:10</t>
+          <t>09:47:48</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.05</v>
+        <v>4.49</v>
       </c>
       <c r="F84" t="n">
-        <v>12.42</v>
+        <v>13.22</v>
       </c>
       <c r="G84" t="n">
-        <v>223.1</v>
+        <v>224.4</v>
       </c>
       <c r="H84" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-139.37</v>
+        <v>157.95</v>
       </c>
       <c r="K84" t="n">
-        <v>-268.98</v>
+        <v>-242.64</v>
       </c>
       <c r="L84" t="n">
-        <v>302.94</v>
+        <v>289.52</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:46:54</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="F85" t="n">
-        <v>12.23</v>
+        <v>13.22</v>
       </c>
       <c r="G85" t="n">
-        <v>224</v>
+        <v>223.4</v>
       </c>
       <c r="H85" t="n">
-        <v>56.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J85" t="n">
-        <v>150.18</v>
+        <v>-223.39</v>
       </c>
       <c r="K85" t="n">
-        <v>198</v>
+        <v>155.87</v>
       </c>
       <c r="L85" t="n">
-        <v>248.51</v>
+        <v>272.39</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:52:27</t>
+          <t>09:53:12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.94</v>
+        <v>3.47</v>
       </c>
       <c r="F86" t="n">
-        <v>12.84</v>
+        <v>13.22</v>
       </c>
       <c r="G86" t="n">
-        <v>224.2</v>
+        <v>213.9</v>
       </c>
       <c r="H86" t="n">
-        <v>60.6</v>
+        <v>31.1</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-298.13</v>
+        <v>-257.41</v>
       </c>
       <c r="K86" t="n">
-        <v>-169.89</v>
+        <v>-82.47</v>
       </c>
       <c r="L86" t="n">
-        <v>343.14</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:54:02</t>
+          <t>09:55:22</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="F87" t="n">
-        <v>12.37</v>
+        <v>11.67</v>
       </c>
       <c r="G87" t="n">
-        <v>226.9</v>
+        <v>225.2</v>
       </c>
       <c r="H87" t="n">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>163.79</v>
+        <v>159.37</v>
       </c>
       <c r="K87" t="n">
-        <v>-304.7</v>
+        <v>129.3</v>
       </c>
       <c r="L87" t="n">
-        <v>345.93</v>
+        <v>205.23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:55:35</t>
+          <t>09:57:55</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.86</v>
+        <v>3.26</v>
       </c>
       <c r="F88" t="n">
-        <v>13.22</v>
+        <v>13.02</v>
       </c>
       <c r="G88" t="n">
-        <v>212.7</v>
+        <v>218.8</v>
       </c>
       <c r="H88" t="n">
-        <v>46.2</v>
+        <v>62.4</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J88" t="n">
-        <v>-387.04</v>
+        <v>-228.66</v>
       </c>
       <c r="K88" t="n">
-        <v>73.61</v>
+        <v>158.53</v>
       </c>
       <c r="L88" t="n">
-        <v>393.98</v>
+        <v>278.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="K14" t="n">
-        <v>-41.67</v>
+        <v>-50.04</v>
       </c>
       <c r="L14" t="n">
-        <v>41.68</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.54</v>
+        <v>-1.76</v>
       </c>
       <c r="K15" t="n">
-        <v>-73.95</v>
+        <v>-84.23</v>
       </c>
       <c r="L15" t="n">
-        <v>73.95999999999999</v>
+        <v>84.25</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.81</v>
+        <v>-47.04</v>
       </c>
       <c r="K16" t="n">
-        <v>-35.61</v>
+        <v>-41.05</v>
       </c>
       <c r="L16" t="n">
-        <v>54.16</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>23.29</v>
+        <v>24.87</v>
       </c>
       <c r="K17" t="n">
-        <v>102.78</v>
+        <v>109.72</v>
       </c>
       <c r="L17" t="n">
-        <v>105.38</v>
+        <v>112.51</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>87.81</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-56.39</v>
+        <v>-62.81</v>
       </c>
       <c r="L18" t="n">
-        <v>104.36</v>
+        <v>116.25</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>82.19</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10.69</v>
       </c>
       <c r="L19" t="n">
-        <v>82.70999999999999</v>
+        <v>95.04000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.64</v>
+        <v>-19.89</v>
       </c>
       <c r="K20" t="n">
-        <v>-110.54</v>
+        <v>-132.13</v>
       </c>
       <c r="L20" t="n">
-        <v>111.78</v>
+        <v>133.62</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-107.94</v>
+        <v>-123.79</v>
       </c>
       <c r="K21" t="n">
-        <v>142.55</v>
+        <v>163.49</v>
       </c>
       <c r="L21" t="n">
-        <v>178.81</v>
+        <v>205.07</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-104.33</v>
+        <v>-120.36</v>
       </c>
       <c r="K22" t="n">
-        <v>103.17</v>
+        <v>119.02</v>
       </c>
       <c r="L22" t="n">
-        <v>146.73</v>
+        <v>169.27</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-104.49</v>
+        <v>-136.28</v>
       </c>
       <c r="K23" t="n">
-        <v>50.58</v>
+        <v>65.97</v>
       </c>
       <c r="L23" t="n">
-        <v>116.09</v>
+        <v>151.4</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>18.69</v>
+        <v>24.42</v>
       </c>
       <c r="K24" t="n">
-        <v>-120.43</v>
+        <v>-157.4</v>
       </c>
       <c r="L24" t="n">
-        <v>121.87</v>
+        <v>159.28</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-194.73</v>
+        <v>-236.28</v>
       </c>
       <c r="K25" t="n">
-        <v>75.08</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>208.7</v>
+        <v>253.23</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>109.16</v>
+        <v>133.73</v>
       </c>
       <c r="K26" t="n">
-        <v>-243.14</v>
+        <v>-297.88</v>
       </c>
       <c r="L26" t="n">
-        <v>266.52</v>
+        <v>326.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-14.36</v>
+        <v>-20.26</v>
       </c>
       <c r="K27" t="n">
-        <v>-146.18</v>
+        <v>-206.25</v>
       </c>
       <c r="L27" t="n">
-        <v>146.88</v>
+        <v>207.24</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-167.4</v>
+        <v>-232.63</v>
       </c>
       <c r="K28" t="n">
-        <v>-22.76</v>
+        <v>-31.62</v>
       </c>
       <c r="L28" t="n">
-        <v>168.94</v>
+        <v>234.77</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>57.26</v>
+        <v>62.3</v>
       </c>
       <c r="K29" t="n">
-        <v>-49.02</v>
+        <v>-53.33</v>
       </c>
       <c r="L29" t="n">
-        <v>75.37</v>
+        <v>82.01000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>49.31</v>
+        <v>56.15</v>
       </c>
       <c r="K30" t="n">
-        <v>57.41</v>
+        <v>65.38</v>
       </c>
       <c r="L30" t="n">
-        <v>75.67</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>12.33</v>
+        <v>13.73</v>
       </c>
       <c r="K31" t="n">
-        <v>66.44</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>67.58</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>33.1</v>
+        <v>38.19</v>
       </c>
       <c r="K32" t="n">
-        <v>-81.86</v>
+        <v>-94.45</v>
       </c>
       <c r="L32" t="n">
-        <v>88.3</v>
+        <v>101.88</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>62.18</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>50.05</v>
+        <v>59.69</v>
       </c>
       <c r="L33" t="n">
-        <v>79.81999999999999</v>
+        <v>95.19</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-63.67</v>
+        <v>-77.89</v>
       </c>
       <c r="K34" t="n">
-        <v>-23.24</v>
+        <v>-28.43</v>
       </c>
       <c r="L34" t="n">
-        <v>67.78</v>
+        <v>82.92</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-123.12</v>
+        <v>-142.8</v>
       </c>
       <c r="K35" t="n">
-        <v>108.34</v>
+        <v>125.66</v>
       </c>
       <c r="L35" t="n">
-        <v>164.01</v>
+        <v>190.22</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-131.22</v>
+        <v>-146.61</v>
       </c>
       <c r="K36" t="n">
-        <v>-125.52</v>
+        <v>-140.25</v>
       </c>
       <c r="L36" t="n">
-        <v>181.59</v>
+        <v>202.89</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>21.74</v>
+        <v>28.39</v>
       </c>
       <c r="K37" t="n">
-        <v>-16.08</v>
+        <v>-21</v>
       </c>
       <c r="L37" t="n">
-        <v>27.04</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-14.23</v>
+        <v>-18.78</v>
       </c>
       <c r="K38" t="n">
-        <v>-150.26</v>
+        <v>-198.25</v>
       </c>
       <c r="L38" t="n">
-        <v>150.93</v>
+        <v>199.14</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-209.17</v>
+        <v>-247.39</v>
       </c>
       <c r="K39" t="n">
-        <v>-86.12</v>
+        <v>-101.85</v>
       </c>
       <c r="L39" t="n">
-        <v>226.21</v>
+        <v>267.53</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-115.64</v>
+        <v>-151.25</v>
       </c>
       <c r="K40" t="n">
-        <v>-113.14</v>
+        <v>-147.98</v>
       </c>
       <c r="L40" t="n">
-        <v>161.78</v>
+        <v>211.6</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>277.58</v>
+        <v>332.66</v>
       </c>
       <c r="K41" t="n">
-        <v>127.87</v>
+        <v>153.24</v>
       </c>
       <c r="L41" t="n">
-        <v>305.61</v>
+        <v>366.26</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>141.86</v>
+        <v>193.56</v>
       </c>
       <c r="K42" t="n">
-        <v>-167.47</v>
+        <v>-228.5</v>
       </c>
       <c r="L42" t="n">
-        <v>219.48</v>
+        <v>299.47</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>8.44</v>
+        <v>10.43</v>
       </c>
       <c r="K43" t="n">
-        <v>-300.64</v>
+        <v>-371.56</v>
       </c>
       <c r="L43" t="n">
-        <v>300.76</v>
+        <v>371.71</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.86</v>
+        <v>-56.22</v>
       </c>
       <c r="K44" t="n">
-        <v>-51.9</v>
+        <v>-59.72</v>
       </c>
       <c r="L44" t="n">
-        <v>71.28</v>
+        <v>82.02</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>17.02</v>
+        <v>21.17</v>
       </c>
       <c r="K45" t="n">
-        <v>13.6</v>
+        <v>16.92</v>
       </c>
       <c r="L45" t="n">
-        <v>21.78</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>8.18</v>
+        <v>9.74</v>
       </c>
       <c r="K46" t="n">
-        <v>-67.92</v>
+        <v>-80.88</v>
       </c>
       <c r="L46" t="n">
-        <v>68.41</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-59.48</v>
+        <v>-67.91</v>
       </c>
       <c r="K47" t="n">
-        <v>-70.17</v>
+        <v>-80.11</v>
       </c>
       <c r="L47" t="n">
-        <v>91.98999999999999</v>
+        <v>105.02</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-97.77</v>
+        <v>-110.34</v>
       </c>
       <c r="K48" t="n">
-        <v>25.35</v>
+        <v>28.61</v>
       </c>
       <c r="L48" t="n">
-        <v>101</v>
+        <v>113.99</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-79.20999999999999</v>
+        <v>-89.06</v>
       </c>
       <c r="K49" t="n">
-        <v>64.88</v>
+        <v>72.94</v>
       </c>
       <c r="L49" t="n">
-        <v>102.39</v>
+        <v>115.11</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.02</v>
+        <v>-12.74</v>
       </c>
       <c r="K50" t="n">
-        <v>-170.51</v>
+        <v>-197.18</v>
       </c>
       <c r="L50" t="n">
-        <v>170.87</v>
+        <v>197.6</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-38.6</v>
+        <v>-48.87</v>
       </c>
       <c r="K51" t="n">
-        <v>-87.98999999999999</v>
+        <v>-111.39</v>
       </c>
       <c r="L51" t="n">
-        <v>96.08</v>
+        <v>121.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>171.53</v>
+        <v>185.7</v>
       </c>
       <c r="K52" t="n">
-        <v>92.33</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>194.8</v>
+        <v>210.89</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>57.94</v>
+        <v>77.16</v>
       </c>
       <c r="K53" t="n">
-        <v>129.43</v>
+        <v>172.37</v>
       </c>
       <c r="L53" t="n">
-        <v>141.81</v>
+        <v>188.85</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-163.19</v>
+        <v>-212.11</v>
       </c>
       <c r="K54" t="n">
-        <v>53.72</v>
+        <v>69.83</v>
       </c>
       <c r="L54" t="n">
-        <v>171.8</v>
+        <v>223.3</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>32.25</v>
+        <v>37.3</v>
       </c>
       <c r="K55" t="n">
-        <v>-232.68</v>
+        <v>-269.13</v>
       </c>
       <c r="L55" t="n">
-        <v>234.91</v>
+        <v>271.71</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>225.38</v>
+        <v>325.41</v>
       </c>
       <c r="K56" t="n">
-        <v>-155.67</v>
+        <v>-224.75</v>
       </c>
       <c r="L56" t="n">
-        <v>273.92</v>
+        <v>395.48</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>170.52</v>
+        <v>219.22</v>
       </c>
       <c r="K57" t="n">
-        <v>-205.76</v>
+        <v>-264.53</v>
       </c>
       <c r="L57" t="n">
-        <v>267.23</v>
+        <v>343.56</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>156.1</v>
+        <v>225.46</v>
       </c>
       <c r="K58" t="n">
-        <v>105.43</v>
+        <v>152.28</v>
       </c>
       <c r="L58" t="n">
-        <v>188.37</v>
+        <v>272.07</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>23.16</v>
+        <v>26.75</v>
       </c>
       <c r="K59" t="n">
-        <v>-65.86</v>
+        <v>-76.09</v>
       </c>
       <c r="L59" t="n">
-        <v>69.81</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>32.71</v>
+        <v>39.1</v>
       </c>
       <c r="K60" t="n">
-        <v>50.83</v>
+        <v>60.75</v>
       </c>
       <c r="L60" t="n">
-        <v>60.45</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.02</v>
+        <v>-10.32</v>
       </c>
       <c r="K61" t="n">
-        <v>-76.53</v>
+        <v>-87.48999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>77.06</v>
+        <v>88.09</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>156.06</v>
+        <v>166.26</v>
       </c>
       <c r="K62" t="n">
-        <v>64.7</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>168.94</v>
+        <v>179.98</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.02</v>
+        <v>-6.4</v>
       </c>
       <c r="K63" t="n">
-        <v>33.94</v>
+        <v>43.32</v>
       </c>
       <c r="L63" t="n">
-        <v>34.31</v>
+        <v>43.79</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-117.33</v>
+        <v>-128.61</v>
       </c>
       <c r="K64" t="n">
-        <v>-13.76</v>
+        <v>-15.09</v>
       </c>
       <c r="L64" t="n">
-        <v>118.13</v>
+        <v>129.49</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.81</v>
+        <v>-15.38</v>
       </c>
       <c r="K65" t="n">
-        <v>-142.81</v>
+        <v>-171.43</v>
       </c>
       <c r="L65" t="n">
-        <v>143.38</v>
+        <v>172.12</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>44.39</v>
+        <v>58.55</v>
       </c>
       <c r="K66" t="n">
-        <v>84.23999999999999</v>
+        <v>111.12</v>
       </c>
       <c r="L66" t="n">
-        <v>95.22</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>35.78</v>
+        <v>46.98</v>
       </c>
       <c r="K67" t="n">
-        <v>80.06999999999999</v>
+        <v>105.14</v>
       </c>
       <c r="L67" t="n">
-        <v>87.70999999999999</v>
+        <v>115.16</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-202.27</v>
+        <v>-242.87</v>
       </c>
       <c r="K68" t="n">
-        <v>-36.83</v>
+        <v>-44.22</v>
       </c>
       <c r="L68" t="n">
-        <v>205.6</v>
+        <v>246.86</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-179.31</v>
+        <v>-223.24</v>
       </c>
       <c r="K69" t="n">
-        <v>-39.11</v>
+        <v>-48.7</v>
       </c>
       <c r="L69" t="n">
-        <v>183.53</v>
+        <v>228.49</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-230.98</v>
+        <v>-268.81</v>
       </c>
       <c r="K70" t="n">
-        <v>-75.40000000000001</v>
+        <v>-87.75</v>
       </c>
       <c r="L70" t="n">
-        <v>242.98</v>
+        <v>282.77</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>88.23</v>
+        <v>120.65</v>
       </c>
       <c r="K71" t="n">
-        <v>-206.16</v>
+        <v>-281.92</v>
       </c>
       <c r="L71" t="n">
-        <v>224.25</v>
+        <v>306.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>189.21</v>
+        <v>244.84</v>
       </c>
       <c r="K72" t="n">
-        <v>-129.9</v>
+        <v>-168.09</v>
       </c>
       <c r="L72" t="n">
-        <v>229.51</v>
+        <v>296.99</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-183.46</v>
+        <v>-230.94</v>
       </c>
       <c r="K73" t="n">
-        <v>141.25</v>
+        <v>177.81</v>
       </c>
       <c r="L73" t="n">
-        <v>231.53</v>
+        <v>291.46</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>64.86</v>
+        <v>73.91</v>
       </c>
       <c r="K74" t="n">
-        <v>34.94</v>
+        <v>39.82</v>
       </c>
       <c r="L74" t="n">
-        <v>73.67</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-54.76</v>
+        <v>-65.55</v>
       </c>
       <c r="K75" t="n">
-        <v>23.54</v>
+        <v>28.17</v>
       </c>
       <c r="L75" t="n">
-        <v>59.61</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>58.85</v>
+        <v>66.72</v>
       </c>
       <c r="K76" t="n">
-        <v>29.72</v>
+        <v>33.7</v>
       </c>
       <c r="L76" t="n">
-        <v>65.93000000000001</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>113.32</v>
+        <v>125.43</v>
       </c>
       <c r="K77" t="n">
-        <v>-10.64</v>
+        <v>-11.77</v>
       </c>
       <c r="L77" t="n">
-        <v>113.82</v>
+        <v>125.98</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-60.7</v>
+        <v>-71.48999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>50.64</v>
+        <v>59.64</v>
       </c>
       <c r="L78" t="n">
-        <v>79.05</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>94.12</v>
+        <v>103.7</v>
       </c>
       <c r="K79" t="n">
-        <v>-18.69</v>
+        <v>-20.6</v>
       </c>
       <c r="L79" t="n">
-        <v>95.95999999999999</v>
+        <v>105.73</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-132.15</v>
+        <v>-157.39</v>
       </c>
       <c r="K80" t="n">
-        <v>-15.51</v>
+        <v>-18.47</v>
       </c>
       <c r="L80" t="n">
-        <v>133.06</v>
+        <v>158.47</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>106.14</v>
+        <v>128.45</v>
       </c>
       <c r="K81" t="n">
-        <v>46.92</v>
+        <v>56.78</v>
       </c>
       <c r="L81" t="n">
-        <v>116.05</v>
+        <v>140.44</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>95.18000000000001</v>
+        <v>118</v>
       </c>
       <c r="K82" t="n">
-        <v>-84.37</v>
+        <v>-104.6</v>
       </c>
       <c r="L82" t="n">
-        <v>127.19</v>
+        <v>157.69</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>106.02</v>
+        <v>140.99</v>
       </c>
       <c r="K83" t="n">
-        <v>89.84</v>
+        <v>119.48</v>
       </c>
       <c r="L83" t="n">
-        <v>138.97</v>
+        <v>184.81</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-137.75</v>
+        <v>-183.92</v>
       </c>
       <c r="K84" t="n">
-        <v>-40.66</v>
+        <v>-54.29</v>
       </c>
       <c r="L84" t="n">
-        <v>143.62</v>
+        <v>191.76</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>22.5</v>
+        <v>29.21</v>
       </c>
       <c r="K85" t="n">
-        <v>-136.35</v>
+        <v>-176.97</v>
       </c>
       <c r="L85" t="n">
-        <v>138.19</v>
+        <v>179.36</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-219.34</v>
+        <v>-290.01</v>
       </c>
       <c r="K86" t="n">
-        <v>128.31</v>
+        <v>169.65</v>
       </c>
       <c r="L86" t="n">
-        <v>254.11</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>169.71</v>
+        <v>214.22</v>
       </c>
       <c r="K87" t="n">
-        <v>-158.94</v>
+        <v>-200.62</v>
       </c>
       <c r="L87" t="n">
-        <v>232.52</v>
+        <v>293.49</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-44.62</v>
+        <v>-53.57</v>
       </c>
       <c r="K88" t="n">
-        <v>299.6</v>
+        <v>359.74</v>
       </c>
       <c r="L88" t="n">
-        <v>302.9</v>
+        <v>363.71</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-11.xlsx
+++ b/output/2025-04-11.xlsx
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.76</v>
+        <v>-1.85</v>
       </c>
       <c r="K15" t="n">
-        <v>-84.23</v>
+        <v>-88.65000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>84.25</v>
+        <v>88.67</v>
       </c>
     </row>
     <row r="16">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>97.81999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="K18" t="n">
-        <v>-62.81</v>
+        <v>-63.76</v>
       </c>
       <c r="L18" t="n">
-        <v>116.25</v>
+        <v>118.01</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>94.43000000000001</v>
+        <v>98.78</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.69</v>
+        <v>-11.18</v>
       </c>
       <c r="L19" t="n">
-        <v>95.04000000000001</v>
+        <v>99.41</v>
       </c>
     </row>
     <row r="20">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>56.15</v>
+        <v>59.77</v>
       </c>
       <c r="K30" t="n">
-        <v>65.38</v>
+        <v>69.59</v>
       </c>
       <c r="L30" t="n">
-        <v>86.18000000000001</v>
+        <v>91.73999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>74.15000000000001</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>59.69</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>95.19</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="34">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.22</v>
+        <v>-56.78</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.72</v>
+        <v>-60.32</v>
       </c>
       <c r="L44" t="n">
-        <v>82.02</v>
+        <v>82.84</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>21.17</v>
+        <v>26.05</v>
       </c>
       <c r="K45" t="n">
-        <v>16.92</v>
+        <v>20.82</v>
       </c>
       <c r="L45" t="n">
-        <v>27.1</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>9.74</v>
+        <v>10.8</v>
       </c>
       <c r="K46" t="n">
-        <v>-80.88</v>
+        <v>-89.72</v>
       </c>
       <c r="L46" t="n">
-        <v>81.47</v>
+        <v>90.37</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-67.91</v>
+        <v>-71.73999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-80.11</v>
+        <v>-84.63</v>
       </c>
       <c r="L47" t="n">
-        <v>105.02</v>
+        <v>110.94</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-110.34</v>
+        <v>-114.79</v>
       </c>
       <c r="K48" t="n">
-        <v>28.61</v>
+        <v>29.76</v>
       </c>
       <c r="L48" t="n">
-        <v>113.99</v>
+        <v>118.58</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-89.06</v>
+        <v>-89.5</v>
       </c>
       <c r="K49" t="n">
-        <v>72.94</v>
+        <v>73.31</v>
       </c>
       <c r="L49" t="n">
-        <v>115.11</v>
+        <v>115.69</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>26.75</v>
+        <v>29.03</v>
       </c>
       <c r="K59" t="n">
-        <v>-76.09</v>
+        <v>-82.58</v>
       </c>
       <c r="L59" t="n">
-        <v>80.65000000000001</v>
+        <v>87.53</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>39.1</v>
+        <v>47.92</v>
       </c>
       <c r="K60" t="n">
-        <v>60.75</v>
+        <v>74.47</v>
       </c>
       <c r="L60" t="n">
-        <v>72.25</v>
+        <v>88.55</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.32</v>
+        <v>-11.18</v>
       </c>
       <c r="K61" t="n">
-        <v>-87.48999999999999</v>
+        <v>-94.76000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>88.09</v>
+        <v>95.42</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>166.26</v>
+        <v>190.7</v>
       </c>
       <c r="K62" t="n">
-        <v>68.93000000000001</v>
+        <v>79.06</v>
       </c>
       <c r="L62" t="n">
-        <v>179.98</v>
+        <v>206.44</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.4</v>
+        <v>-7.28</v>
       </c>
       <c r="K63" t="n">
-        <v>43.32</v>
+        <v>49.23</v>
       </c>
       <c r="L63" t="n">
-        <v>43.79</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-128.61</v>
+        <v>-136.44</v>
       </c>
       <c r="K64" t="n">
-        <v>-15.09</v>
+        <v>-16.01</v>
       </c>
       <c r="L64" t="n">
-        <v>129.49</v>
+        <v>137.38</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>73.91</v>
+        <v>82.64</v>
       </c>
       <c r="K74" t="n">
-        <v>39.82</v>
+        <v>44.52</v>
       </c>
       <c r="L74" t="n">
-        <v>83.95</v>
+        <v>93.87</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-65.55</v>
+        <v>-74.5</v>
       </c>
       <c r="K75" t="n">
-        <v>28.17</v>
+        <v>32.02</v>
       </c>
       <c r="L75" t="n">
-        <v>71.34999999999999</v>
+        <v>81.09</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>66.72</v>
+        <v>69.08</v>
       </c>
       <c r="K76" t="n">
-        <v>33.7</v>
+        <v>34.89</v>
       </c>
       <c r="L76" t="n">
-        <v>74.75</v>
+        <v>77.39</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>125.43</v>
+        <v>148.38</v>
       </c>
       <c r="K77" t="n">
-        <v>-11.77</v>
+        <v>-13.92</v>
       </c>
       <c r="L77" t="n">
-        <v>125.98</v>
+        <v>149.03</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-71.48999999999999</v>
+        <v>-71.92</v>
       </c>
       <c r="K78" t="n">
-        <v>59.64</v>
+        <v>60</v>
       </c>
       <c r="L78" t="n">
-        <v>93.09999999999999</v>
+        <v>93.66</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>103.7</v>
+        <v>106.87</v>
       </c>
       <c r="K79" t="n">
-        <v>-20.6</v>
+        <v>-21.22</v>
       </c>
       <c r="L79" t="n">
-        <v>105.73</v>
+        <v>108.96</v>
       </c>
     </row>
     <row r="80">
